--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7BD996-09F2-4FFC-A8B4-16334B484CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4338F6-35BB-4123-974A-A2774C2FEBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,9 @@
     <sheet name="Assets" sheetId="3" r:id="rId4"/>
     <sheet name="Findings" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$525</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="1205">
   <si>
     <t>Name</t>
   </si>
@@ -780,9 +783,6 @@
     <t>VOE_FrequencyCheck</t>
   </si>
   <si>
-    <t xml:space="preserve">Presently Employed has been listed as No on the Verification of Employment. Needs additional review. </t>
-  </si>
-  <si>
     <t>VOE_PresentlyEmployedCheck</t>
   </si>
   <si>
@@ -867,9 +867,6 @@
     <t>VOE_CommissionsBonusTipsPopulated</t>
   </si>
   <si>
-    <t>Commission, bonuses, tips, other amount has been populated. Needs additional review.</t>
-  </si>
-  <si>
     <t>OL_SalariedPayRateCheck</t>
   </si>
   <si>
@@ -1698,9 +1695,6 @@
     <t>SSBL_OverPayment</t>
   </si>
   <si>
-    <t>Manual review required, overpayment detected on SS/SSI benefit letter.</t>
-  </si>
-  <si>
     <t>Asset Self Certification</t>
   </si>
   <si>
@@ -1806,9 +1800,6 @@
     <t>EDC_hourly_and_paycheck</t>
   </si>
   <si>
-    <t>Newly added</t>
-  </si>
-  <si>
     <t>AS_HouseholdMemAbsent</t>
   </si>
   <si>
@@ -1842,24 +1833,12 @@
     <t>MID_MinorLessThan50Percent</t>
   </si>
   <si>
-    <t>A minor will live in the household less than 50% of the time. Manual review required.</t>
-  </si>
-  <si>
-    <t>The applicant has indicated all household contains all students by selecting 2 or 3 to Part A on the Student Certification. Manual review required.</t>
-  </si>
-  <si>
     <t>Raluca removed this check</t>
   </si>
   <si>
     <t>VOE_PayIncrease</t>
   </si>
   <si>
-    <t>Anticipated increase in the base pay over the next 12 months. Manual review required.</t>
-  </si>
-  <si>
-    <t>Raluca updated this check</t>
-  </si>
-  <si>
     <t>ICW_LiveInAttendant</t>
   </si>
   <si>
@@ -1950,9 +1929,6 @@
     <t>FailureEmailBodyActionReq</t>
   </si>
   <si>
-    <t>Income type included that cannot be validated with automation. Manual review required.</t>
-  </si>
-  <si>
     <t>SD_LLMExtractionJSONsFolder</t>
   </si>
   <si>
@@ -2019,9 +1995,6 @@
     <t>SCNE_EmploymentDocumented</t>
   </si>
   <si>
-    <t>Currently employment has been documented on the Self-Certification of Non-Employment. Manual review required.</t>
-  </si>
-  <si>
     <t>HHD_IsSigned</t>
   </si>
   <si>
@@ -2094,9 +2067,6 @@
     <t>VOE_Exists</t>
   </si>
   <si>
-    <t>Verification of Employment email receipt and clarification verification require manual review.</t>
-  </si>
-  <si>
     <t>PS_PayIncreaseAcrossPS</t>
   </si>
   <si>
@@ -2142,18 +2112,9 @@
     <t>SSBL_Incomplete</t>
   </si>
   <si>
-    <t xml:space="preserve">Assets exceed the asset limit, manual review required. </t>
-  </si>
-  <si>
-    <t>Applicant is a Dominium employee, manual review required.</t>
-  </si>
-  <si>
     <t>household member is temporarily absent, needs manual review.</t>
   </si>
   <si>
-    <t>Regular pay rate has increase across paystubs. Manual review required.</t>
-  </si>
-  <si>
     <t>Student Certification has inconsistent information. Please review answers in Part A to Part B for consistency.</t>
   </si>
   <si>
@@ -2163,12 +2124,6 @@
     <t>ICW_ZeroAnnualIncome</t>
   </si>
   <si>
-    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review required.</t>
-  </si>
-  <si>
-    <t>Applicant is a Dominium employee. Manual review required.</t>
-  </si>
-  <si>
     <t>Yardi_States</t>
   </si>
   <si>
@@ -2256,9 +2211,6 @@
     <t>CSEI_Qstn3IsYes</t>
   </si>
   <si>
-    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes, manual review is required.</t>
-  </si>
-  <si>
     <t>CSEI_Qstn4Check</t>
   </si>
   <si>
@@ -2400,9 +2352,6 @@
     <t>Highest Calculated Income on the Day Calculator does not match Verified Income on the ICW.</t>
   </si>
   <si>
-    <t>Multiple employment documents provided for same employment. Can't determine which employment document to use to validate Day Calculator. Manual review required.</t>
-  </si>
-  <si>
     <t>Employee Name listed on the Offer Letter, Day Calculator, and ICW do not match.</t>
   </si>
   <si>
@@ -2577,9 +2526,6 @@
     <t>ICW_Section811</t>
   </si>
   <si>
-    <t xml:space="preserve">This application is a Section 811 unit, manual review is required. </t>
-  </si>
-  <si>
     <t>Employee Name listed on Verification Services, Day Calculator, and ICW do not match.</t>
   </si>
   <si>
@@ -2646,15 +2592,9 @@
     <t>PS_PerfectAttendanceCAmount</t>
   </si>
   <si>
-    <t>Paystub lists YTD pay that is not in the current paystub so we cannot accurately predict income. Manual review required.</t>
-  </si>
-  <si>
     <t>ASC_GA_NoAssets</t>
   </si>
   <si>
-    <t xml:space="preserve">Checkbox documents household has no assets. Manual review required. </t>
-  </si>
-  <si>
     <t>ASC_GA_AssetsDisposedUnaswered</t>
   </si>
   <si>
@@ -2778,9 +2718,6 @@
     <t>CSS_HouseholdInitial</t>
   </si>
   <si>
-    <t>Documented that no household members are part of the original qualifying household. Manual review required.</t>
-  </si>
-  <si>
     <t>CSS_FirstLineCheck</t>
   </si>
   <si>
@@ -2871,9 +2808,6 @@
     <t>BSExists</t>
   </si>
   <si>
-    <t xml:space="preserve">Bank Statements are present in the application, manual review required. </t>
-  </si>
-  <si>
     <t>BS_FindingError</t>
   </si>
   <si>
@@ -3075,15 +3009,9 @@
     <t>Application Review Process_Performer</t>
   </si>
   <si>
-    <t>Employment Verification email receipt and clarification verification require manual review.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Employee Name across the Employment Verification, Day Calculator, and ICW do not match. </t>
   </si>
   <si>
-    <t>Presently Employed has been listed as No on the Employment Verification. Needs manual review.  </t>
-  </si>
-  <si>
     <t>Presently Employed was documented as Yes on the Employment Verification but no Date First Employed was provided. </t>
   </si>
   <si>
@@ -3153,9 +3081,6 @@
     <t>EV_TX_SeasonOrSporadic</t>
   </si>
   <si>
-    <t>Season or Sporadic work has been documented on the Employment Verification. Manual review required.  </t>
-  </si>
-  <si>
     <t>ACNFAExists</t>
   </si>
   <si>
@@ -3267,21 +3192,12 @@
     <t>CSC_120days</t>
   </si>
   <si>
-    <t>Both 120 days of pay history available and 120 days of pay history not available data is populated on the Child Support Calcs. Achie cannot determine which data to use, manual review is required. </t>
-  </si>
-  <si>
     <t>CSC_ConsistentPayments</t>
   </si>
   <si>
-    <t>The consistent payments data is populated on Child Support Calcs but additional data tables are populated as well. Archie cannot determine which data to use, manual review is required. </t>
-  </si>
-  <si>
     <t>CSC_FindingError</t>
   </si>
   <si>
-    <t>Social Security Benefits Letter is missing at least one page. Manual Review is required.</t>
-  </si>
-  <si>
     <t>Asset Certification of Net Family Assets</t>
   </si>
   <si>
@@ -3291,9 +3207,6 @@
     <t>Paystubs do not match Day Calculator with Employee Name, End date and Gross pay</t>
   </si>
   <si>
-    <t>The Annual Income is listed as zero. Manual review required.</t>
-  </si>
-  <si>
     <t>DC_YTDIncome</t>
   </si>
   <si>
@@ -3372,105 +3285,6 @@
     <t>Regular Contributions Verification email receipt requires manual review.</t>
   </si>
   <si>
-    <t>Unable to validate Housing History Disclosure. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income Calculation Worksheet. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Application Summary. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Member Information Document. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income &amp; Asset Questionnaire. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Self Certification &amp; Worksheet. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Affidavit of Student Financial Assistance. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Student Certification. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate VAWA Acknowledgement. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Screening Document. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Paystub. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Employment. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Offer Letter. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Work Number. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self-Employment Certification. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Payment History. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Calcs. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Supplemental Security Income Letter. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Reccurring Cash Contribution. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Housing Demographic Reporting Form. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Self-Employment Income. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Profit/Loss Statement. Manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Household Asset Breakdown. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Employment Verification. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate the Certification of Student Status. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Regular Contributions Verification. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Bank Statements. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Leave and Earnings Statement. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self Certification of Non Employment. Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Annual Student Certification since there is Home unit . Needs manual review.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Zero Income. Needs manual review.</t>
-  </si>
-  <si>
     <t>EV_TX_ApplicantName</t>
   </si>
   <si>
@@ -3576,9 +3390,6 @@
     <t>The 1040 tax form was not dated.</t>
   </si>
   <si>
-    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Needs manual review.</t>
-  </si>
-  <si>
     <t>EV_NameNotMatchingIAQ</t>
   </si>
   <si>
@@ -3618,21 +3429,9 @@
     <t xml:space="preserve">Veterans benefits have been indicated, but not all VA Benefits Letters have not been provided. </t>
   </si>
   <si>
-    <t>Unable to validate findings for Release and Consent Form. Needs manual review. </t>
-  </si>
-  <si>
-    <t>Unable to validate the Tenant Rights and Resource Guide (TRRG). Manual review required. </t>
-  </si>
-  <si>
     <t>Unable to validate the TSAHC. Manual review required. </t>
   </si>
   <si>
-    <t>Unable to validate findings for Verification Services. Needs manual review. </t>
-  </si>
-  <si>
-    <t>Unable to validate findings for Asset Certification of Net Family Assets. Needs manual review. </t>
-  </si>
-  <si>
     <t>FindAllBusinessNmeMatches_Threshold</t>
   </si>
   <si>
@@ -3651,13 +3450,214 @@
     <t>YardiReviewer</t>
   </si>
   <si>
-    <t>Business asked to remove.</t>
-  </si>
-  <si>
     <t>ASFAExists</t>
   </si>
   <si>
     <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Updated by Raluca</t>
+  </si>
+  <si>
+    <t>Assets exceed HUD asset limit. Third party verification of all assets is required.</t>
+  </si>
+  <si>
+    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant is a Dominium employee. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Income type included that cannot be validated with automation. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Annual income is listed as zero. Confirm this is accurate and ensure the Certification of Zero Income is present in the file.</t>
+  </si>
+  <si>
+    <t>This application is a Section 811 unit. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Application Summary. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant reported a minor will live in the household less than 50% of the time. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Member Information Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Income &amp; Asset Questionnaire. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Current employment has been documented on the Self-Certification of Non-Employment. Verification of employment is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self Certification of Non Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant has reported they have no assets. If applicant has income, confirm how the income is paid.</t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Self Certification &amp; Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Affidavit of Student Financial Assistance. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Annual Student Certification since there is Home unit . Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Zero Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate VAWA Acknowledgement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Screening Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Raluca removed the check as per business requirement</t>
+  </si>
+  <si>
+    <t>Multiple sources of verification included for same income. Remove verification documents that are not being used in the calculation of income.</t>
+  </si>
+  <si>
+    <t>Regular pay rate has increased across paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Paystubs list YTD pay that is not paid on a current paystub so annual income cannot be accurately predicted. Clarify, with the employer, the pay type and how often it is received.</t>
+  </si>
+  <si>
+    <t>Unable to validate paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Verification of Employment - manual review is needed to ensure document was received via 3rd party.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Commission, bonuses, tips, other amount has been populated. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Anticipated wage increase indicated on employment verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Offer Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>WN_TotalMatchSum</t>
+  </si>
+  <si>
+    <t>Total Pay listed on the Work Number does not match the sum of each pay type on the Work Number.</t>
+  </si>
+  <si>
+    <t>Unable to validate Work Number. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self-Employment Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Payment History. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Both 120 days of pay history available and 120 days of pay history not available data sections are populated on the Child Support Calculator. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
+  </si>
+  <si>
+    <t>The consistent payments data is populated on Child Support Calcs but additional data tables are populated as well. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Calcs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Social Security Benefits Letter is missing at least one page. Upload missing page with final signed documents.</t>
+  </si>
+  <si>
+    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Reccurring Cash Contribution. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Self-Employment Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Profit/Loss Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Household Asset Breakdown. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Employment Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Season or Sporadic work has been documented on the Employment Verification. Manual review is needed.  </t>
+  </si>
+  <si>
+    <t>Applicant marked that no household members are part of the original qualifying household. Please have the applicant correct.</t>
+  </si>
+  <si>
+    <t>Unable to validate the Certification of Student Status. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Regular Contributions Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Bank statements are included in the file. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Bank Statements. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Leave and Earnings Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Release and Consent Form. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
 </sst>
 </file>
@@ -4093,7 +4093,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1199</v>
+        <v>1131</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -4114,7 +4114,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>1010</v>
+        <v>987</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -4126,12 +4126,12 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1198</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B8" t="s">
         <v>207</v>
@@ -4156,10 +4156,10 @@
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>1096</v>
+        <v>1066</v>
       </c>
       <c r="B12" t="s">
-        <v>1104</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -4167,7 +4167,7 @@
         <v>208</v>
       </c>
       <c r="B13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
@@ -4180,10 +4180,10 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B15" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
@@ -4191,7 +4191,7 @@
         <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
@@ -4199,7 +4199,7 @@
         <v>211</v>
       </c>
       <c r="B17" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
@@ -4207,7 +4207,7 @@
         <v>212</v>
       </c>
       <c r="B18" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C18" t="s">
         <v>227</v>
@@ -4229,7 +4229,7 @@
         <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C20" t="s">
         <v>229</v>
@@ -4240,7 +4240,7 @@
         <v>215</v>
       </c>
       <c r="B21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C21" t="s">
         <v>230</v>
@@ -4251,7 +4251,7 @@
         <v>216</v>
       </c>
       <c r="B22" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
@@ -4259,7 +4259,7 @@
         <v>217</v>
       </c>
       <c r="B23" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
@@ -4267,7 +4267,7 @@
         <v>218</v>
       </c>
       <c r="B24" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
@@ -4275,12 +4275,12 @@
         <v>219</v>
       </c>
       <c r="B25" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B26" t="s">
         <v>228</v>
@@ -4291,50 +4291,50 @@
         <v>232</v>
       </c>
       <c r="B27" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1">
@@ -4347,221 +4347,221 @@
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1">
       <c r="A35" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B36" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1">
       <c r="A38" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B38" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B39" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
       <c r="A41" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B43" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="B44" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="B45" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>803</v>
+        <v>785</v>
       </c>
       <c r="B46" t="s">
-        <v>804</v>
+        <v>786</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
       <c r="B47" t="s">
-        <v>814</v>
+        <v>796</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="B48" t="s">
-        <v>816</v>
+        <v>798</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>842</v>
+        <v>824</v>
       </c>
       <c r="B49" t="s">
-        <v>843</v>
+        <v>825</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>879</v>
+        <v>858</v>
       </c>
       <c r="B50" t="s">
-        <v>880</v>
+        <v>859</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>936</v>
+        <v>914</v>
       </c>
       <c r="B51" t="s">
-        <v>937</v>
+        <v>915</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>997</v>
+        <v>974</v>
       </c>
       <c r="B52" t="s">
-        <v>998</v>
+        <v>975</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>999</v>
+        <v>976</v>
       </c>
       <c r="B53" t="s">
-        <v>1000</v>
+        <v>977</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1001</v>
+        <v>978</v>
       </c>
       <c r="B54" t="s">
-        <v>1002</v>
+        <v>979</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1">
       <c r="A55" t="s">
-        <v>1003</v>
+        <v>980</v>
       </c>
       <c r="B55" t="s">
-        <v>1004</v>
+        <v>981</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" t="s">
-        <v>1005</v>
+        <v>982</v>
       </c>
       <c r="B56" t="s">
-        <v>1005</v>
+        <v>982</v>
       </c>
       <c r="C56" t="s">
-        <v>1006</v>
+        <v>983</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" t="s">
-        <v>1007</v>
+        <v>984</v>
       </c>
       <c r="B57" t="s">
-        <v>1007</v>
+        <v>984</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1">
       <c r="A58" t="s">
-        <v>1008</v>
+        <v>985</v>
       </c>
       <c r="B58" t="s">
-        <v>1085</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" t="s">
-        <v>1090</v>
+        <v>1060</v>
       </c>
       <c r="B59" t="s">
-        <v>1091</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" t="s">
-        <v>1081</v>
+        <v>1052</v>
       </c>
       <c r="B60" t="s">
-        <v>1080</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
@@ -5527,10 +5527,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5538,15 +5538,15 @@
         <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5554,15 +5554,15 @@
         <v>226</v>
       </c>
       <c r="B4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5570,15 +5570,15 @@
         <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5586,15 +5586,15 @@
         <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B9" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5602,15 +5602,15 @@
         <v>223</v>
       </c>
       <c r="B10" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5626,47 +5626,47 @@
         <v>221</v>
       </c>
       <c r="B13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B14" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B15" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B16" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B17" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B18" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5674,7 +5674,7 @@
         <v>230</v>
       </c>
       <c r="B19" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5682,23 +5682,23 @@
         <v>227</v>
       </c>
       <c r="B20" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B21" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B22" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5706,7 +5706,7 @@
         <v>228</v>
       </c>
       <c r="B23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5714,55 +5714,55 @@
         <v>229</v>
       </c>
       <c r="B24" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B25" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B26" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B30" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5770,95 +5770,95 @@
         <v>1040</v>
       </c>
       <c r="B31" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B32" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B33" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B34" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B35" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B37" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B38" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B39" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B40" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B41" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="B42" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="B20" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
@@ -6069,23 +6069,23 @@
         <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="B22" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B23" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="B3" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -7260,90 +7260,90 @@
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B15" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B16" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B17" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B18" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B19" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B20" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B21" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>1086</v>
+        <v>1056</v>
       </c>
       <c r="B22" t="s">
-        <v>1086</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B23" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
@@ -7380,218 +7380,218 @@
     </row>
     <row r="28" spans="1:2" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.25" customHeight="1">
       <c r="A30" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B31" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B32" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B34" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B35" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B36" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B37" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1">
       <c r="A38" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B38" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B39" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="B40" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
       <c r="A41" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B41" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B42" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="B43" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="B44" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>938</v>
+        <v>916</v>
       </c>
       <c r="B45" t="s">
-        <v>938</v>
+        <v>916</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>939</v>
+        <v>917</v>
       </c>
       <c r="B46" t="s">
-        <v>939</v>
+        <v>917</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>940</v>
+        <v>918</v>
       </c>
       <c r="B47" t="s">
-        <v>940</v>
+        <v>918</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>941</v>
+        <v>919</v>
       </c>
       <c r="B48" t="s">
-        <v>941</v>
+        <v>919</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>1087</v>
+        <v>1057</v>
       </c>
       <c r="B49" t="s">
-        <v>1087</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1088</v>
+        <v>1058</v>
       </c>
       <c r="B50" t="s">
-        <v>1088</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>1197</v>
+        <v>1129</v>
       </c>
       <c r="B51" t="s">
-        <v>1197</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1200</v>
+        <v>1132</v>
       </c>
       <c r="B52" t="s">
-        <v>1200</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1201</v>
+        <v>1133</v>
       </c>
       <c r="B53" t="s">
-        <v>1201</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1202</v>
+        <v>1134</v>
       </c>
       <c r="B54" t="s">
-        <v>1202</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8562,7 +8562,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C524"/>
+  <dimension ref="A1:C525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -8588,87 +8588,87 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1094</v>
+        <v>1064</v>
       </c>
       <c r="B5" t="s">
-        <v>1095</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B7" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="C7" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="B8" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C8" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="B9" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="C9" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="B10" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="C10" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="B11" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C11" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="B12" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="C12" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="B13" t="s">
-        <v>1110</v>
+        <v>1137</v>
       </c>
       <c r="C13" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8676,7 +8676,7 @@
         <v>174</v>
       </c>
       <c r="B15" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -8700,7 +8700,7 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>1148</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8711,94 +8711,100 @@
         <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B20" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B21" t="s">
-        <v>700</v>
+        <v>1139</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B22" t="s">
-        <v>707</v>
+        <v>1140</v>
       </c>
       <c r="C22" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B23" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C23" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B24" t="s">
-        <v>708</v>
+        <v>1141</v>
       </c>
       <c r="C24" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B25" t="s">
-        <v>636</v>
+        <v>1142</v>
       </c>
       <c r="C25" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="B26" t="s">
-        <v>1083</v>
+        <v>1143</v>
       </c>
       <c r="C26" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>844</v>
+        <v>826</v>
       </c>
       <c r="B27" t="s">
-        <v>845</v>
+        <v>1144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B28" t="s">
-        <v>1111</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8819,10 +8825,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B32" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8838,7 +8844,7 @@
         <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>1149</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -8846,7 +8852,7 @@
         <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -8854,7 +8860,7 @@
         <v>190</v>
       </c>
       <c r="B36" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -8891,48 +8897,48 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B41" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B42" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B43" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C43" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="B44" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="C44" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B45" t="s">
-        <v>1112</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -8948,7 +8954,7 @@
         <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>1150</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -8999,7 +9005,7 @@
         <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -9012,45 +9018,48 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B56" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="B57" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>1065</v>
+        <v>1039</v>
       </c>
       <c r="B58" t="s">
-        <v>1066</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B59" t="s">
-        <v>600</v>
+        <v>1147</v>
       </c>
       <c r="C59" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s">
-        <v>1113</v>
+        <v>1148</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9058,7 +9067,7 @@
         <v>178</v>
       </c>
       <c r="B62" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -9069,7 +9078,7 @@
         <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -9080,7 +9089,7 @@
         <v>112</v>
       </c>
       <c r="C64" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -9091,7 +9100,7 @@
         <v>114</v>
       </c>
       <c r="C65" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -9102,7 +9111,7 @@
         <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -9113,7 +9122,7 @@
         <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -9124,7 +9133,7 @@
         <v>106</v>
       </c>
       <c r="C68" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -9132,7 +9141,7 @@
         <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>1151</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -9140,7 +9149,7 @@
         <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -9148,77 +9157,77 @@
         <v>196</v>
       </c>
       <c r="B71" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="C71" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B72" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B73" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s">
-        <v>1152</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>488</v>
+        <v>639</v>
       </c>
       <c r="B75" t="s">
-        <v>1114</v>
+        <v>638</v>
+      </c>
+      <c r="C75" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>648</v>
+        <v>1090</v>
       </c>
       <c r="B76" t="s">
-        <v>647</v>
-      </c>
-      <c r="C76" t="s">
-        <v>598</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>1153</v>
+        <v>1083</v>
       </c>
       <c r="B77" t="s">
-        <v>1154</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>1146</v>
+        <v>1092</v>
       </c>
       <c r="B78" t="s">
-        <v>1147</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>1155</v>
+        <v>486</v>
       </c>
       <c r="B79" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9234,7 +9243,7 @@
         <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -9247,62 +9256,62 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B84" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="B85" t="s">
-        <v>659</v>
+        <v>1150</v>
       </c>
       <c r="C85" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="B86" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C86" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="B87" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="C87" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="B88" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C88" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B89" t="s">
-        <v>1140</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9310,29 +9319,29 @@
         <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>1009</v>
+        <v>986</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="B92" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="C92" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="B93" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C93" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -9356,7 +9365,7 @@
         <v>132</v>
       </c>
       <c r="B96" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -9364,7 +9373,7 @@
         <v>133</v>
       </c>
       <c r="B97" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -9372,7 +9381,7 @@
         <v>134</v>
       </c>
       <c r="B98" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -9380,7 +9389,7 @@
         <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -9388,10 +9397,10 @@
         <v>136</v>
       </c>
       <c r="B100" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C100" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -9399,10 +9408,10 @@
         <v>137</v>
       </c>
       <c r="B101" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C101" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -9410,121 +9419,124 @@
         <v>138</v>
       </c>
       <c r="B102" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C102" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B103" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="B104" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C104" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>873</v>
+        <v>852</v>
       </c>
       <c r="B105" t="s">
-        <v>874</v>
+        <v>853</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="B106" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="C106" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="B107" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="C107" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="B108" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="C108" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>486</v>
+        <v>849</v>
       </c>
       <c r="B109" t="s">
-        <v>1115</v>
+        <v>1152</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>869</v>
+        <v>850</v>
       </c>
       <c r="B110" t="s">
-        <v>870</v>
+        <v>851</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="B111" t="s">
-        <v>872</v>
+        <v>856</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>876</v>
+        <v>857</v>
       </c>
       <c r="B112" t="s">
-        <v>877</v>
+        <v>854</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>878</v>
+        <v>484</v>
       </c>
       <c r="B113" t="s">
-        <v>875</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>1204</v>
+        <v>1135</v>
       </c>
       <c r="B115" t="s">
-        <v>1205</v>
+        <v>1136</v>
       </c>
       <c r="C115" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -9535,7 +9547,7 @@
         <v>144</v>
       </c>
       <c r="C116" t="s">
-        <v>1203</v>
+        <v>587</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -9546,7 +9558,7 @@
         <v>145</v>
       </c>
       <c r="C117" t="s">
-        <v>1203</v>
+        <v>587</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -9557,7 +9569,7 @@
         <v>146</v>
       </c>
       <c r="C118" t="s">
-        <v>1203</v>
+        <v>587</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -9565,21 +9577,21 @@
         <v>139</v>
       </c>
       <c r="B119" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C119" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B120" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C120" t="s">
-        <v>1203</v>
+        <v>587</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -9590,7 +9602,7 @@
         <v>123</v>
       </c>
       <c r="C121" t="s">
-        <v>1203</v>
+        <v>587</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -9598,10 +9610,10 @@
         <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C122" t="s">
-        <v>1203</v>
+        <v>587</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -9612,26 +9624,26 @@
         <v>124</v>
       </c>
       <c r="C123" t="s">
-        <v>1203</v>
+        <v>587</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B124" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C124" t="s">
-        <v>1203</v>
+        <v>587</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B125" t="s">
-        <v>1116</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9668,13 +9680,13 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="B131" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="C131" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -9695,62 +9707,62 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B134" t="s">
-        <v>601</v>
+        <v>1155</v>
       </c>
       <c r="C134" t="s">
-        <v>605</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B135" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="B136" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C136" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B137" t="s">
-        <v>1117</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B139" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C139" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B140" t="s">
-        <v>1141</v>
+        <v>1157</v>
       </c>
       <c r="C140" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -9782,45 +9794,45 @@
         <v>156</v>
       </c>
       <c r="B145" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B146" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="C146" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>1089</v>
+        <v>1059</v>
       </c>
       <c r="B147" t="s">
-        <v>1097</v>
+        <v>1067</v>
       </c>
       <c r="C147" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B148" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B149" t="s">
-        <v>1142</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9849,29 +9861,29 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B154" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B155" t="s">
-        <v>1118</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B156" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="C156" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -9890,7 +9902,7 @@
         <v>166</v>
       </c>
       <c r="C159" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -9901,7 +9913,7 @@
         <v>167</v>
       </c>
       <c r="C160" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -9912,7 +9924,7 @@
         <v>168</v>
       </c>
       <c r="C161" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -9939,119 +9951,122 @@
         <v>171</v>
       </c>
       <c r="C164" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B165" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B166" t="s">
-        <v>1119</v>
+        <v>1160</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>1144</v>
+        <v>1081</v>
       </c>
       <c r="B168" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
       <c r="C168" t="s">
-        <v>1145</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B169" t="s">
-        <v>848</v>
+        <v>829</v>
       </c>
       <c r="C169" t="s">
-        <v>588</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="B170" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="C170" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="B171" t="s">
-        <v>849</v>
+        <v>830</v>
       </c>
       <c r="C171" t="s">
-        <v>598</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>716</v>
+        <v>700</v>
       </c>
       <c r="B172" t="s">
-        <v>850</v>
+        <v>831</v>
       </c>
       <c r="C172" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="B173" t="s">
-        <v>701</v>
+        <v>1141</v>
       </c>
       <c r="C173" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>1084</v>
+        <v>1054</v>
       </c>
       <c r="B174" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="C174" t="s">
-        <v>1157</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B176" t="s">
-        <v>1158</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>1098</v>
+        <v>1068</v>
       </c>
       <c r="B177" t="s">
-        <v>1099</v>
+        <v>1069</v>
       </c>
       <c r="C177" t="s">
-        <v>1100</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -10059,10 +10074,10 @@
         <v>233</v>
       </c>
       <c r="B178" t="s">
-        <v>851</v>
+        <v>832</v>
       </c>
       <c r="C178" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -10070,7 +10085,7 @@
         <v>234</v>
       </c>
       <c r="B179" t="s">
-        <v>852</v>
+        <v>833</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -10078,21 +10093,21 @@
         <v>242</v>
       </c>
       <c r="B180" t="s">
-        <v>853</v>
+        <v>834</v>
       </c>
       <c r="C180" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="B181" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="C181" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -10105,10 +10120,10 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B183" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -10116,10 +10131,10 @@
         <v>237</v>
       </c>
       <c r="B184" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="C184" t="s">
-        <v>1159</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -10127,7 +10142,7 @@
         <v>238</v>
       </c>
       <c r="B185" t="s">
-        <v>856</v>
+        <v>837</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -10135,7 +10150,7 @@
         <v>239</v>
       </c>
       <c r="B186" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -10143,7 +10158,7 @@
         <v>240</v>
       </c>
       <c r="B187" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -10151,107 +10166,116 @@
         <v>241</v>
       </c>
       <c r="B188" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B189" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="C189" t="s">
-        <v>1159</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B190" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B191" t="s">
-        <v>1082</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B192" t="s">
-        <v>786</v>
+        <v>1162</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="B193" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C193" t="s">
-        <v>598</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="B194" t="s">
-        <v>703</v>
+        <v>1163</v>
       </c>
       <c r="C194" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>867</v>
+        <v>848</v>
       </c>
       <c r="B195" t="s">
-        <v>868</v>
+        <v>1164</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>470</v>
+        <v>1097</v>
       </c>
       <c r="B196" t="s">
-        <v>1120</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>1160</v>
+        <v>468</v>
       </c>
       <c r="B197" t="s">
-        <v>1161</v>
+        <v>1165</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="B199" t="s">
-        <v>684</v>
+        <v>1166</v>
       </c>
       <c r="C199" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B200" t="s">
-        <v>1162</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -10259,10 +10283,10 @@
         <v>243</v>
       </c>
       <c r="B201" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="C201" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.5" customHeight="1">
@@ -10270,10 +10294,10 @@
         <v>245</v>
       </c>
       <c r="B202" t="s">
-        <v>860</v>
+        <v>841</v>
       </c>
       <c r="C202" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -10281,2481 +10305,2619 @@
         <v>244</v>
       </c>
       <c r="B203" t="s">
-        <v>821</v>
+        <v>803</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B204" t="s">
-        <v>246</v>
+        <v>1167</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
+        <v>247</v>
+      </c>
+      <c r="B205" t="s">
         <v>248</v>
-      </c>
-      <c r="B205" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B206" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C206" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B207" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B208" t="s">
-        <v>823</v>
+        <v>805</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
+        <v>252</v>
+      </c>
+      <c r="B209" t="s">
         <v>253</v>
-      </c>
-      <c r="B209" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B210" t="s">
-        <v>824</v>
+        <v>806</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B211" t="s">
-        <v>825</v>
+        <v>807</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B212" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="C212" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B213" t="s">
-        <v>826</v>
+        <v>808</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B214" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="C214" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B215" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
+        <v>269</v>
+      </c>
+      <c r="B216" t="s">
         <v>270</v>
-      </c>
-      <c r="B216" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B217" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="C217" t="s">
-        <v>1159</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B218" t="s">
-        <v>275</v>
+        <v>1168</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B219" t="s">
-        <v>786</v>
+        <v>1162</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>481</v>
+        <v>597</v>
       </c>
       <c r="B220" t="s">
-        <v>1121</v>
+        <v>1169</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>603</v>
+        <v>479</v>
       </c>
       <c r="B221" t="s">
-        <v>604</v>
+        <v>1170</v>
       </c>
       <c r="C221" t="s">
-        <v>598</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B223" t="s">
-        <v>1163</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B224" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
       <c r="A225" t="s">
+        <v>267</v>
+      </c>
+      <c r="B225" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" t="s">
         <v>268</v>
       </c>
-      <c r="B225" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
-      <c r="A226" t="s">
-        <v>269</v>
-      </c>
       <c r="B226" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B227" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
       <c r="A228" t="s">
+        <v>274</v>
+      </c>
+      <c r="B228" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" t="s">
         <v>276</v>
       </c>
-      <c r="B228" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2">
-      <c r="A229" t="s">
-        <v>278</v>
-      </c>
       <c r="B229" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B230" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2">
+        <v>1162</v>
+      </c>
+      <c r="C230" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B231" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2">
+        <v>1171</v>
+      </c>
+      <c r="C231" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B233" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B234" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
       <c r="A235" t="s">
+        <v>279</v>
+      </c>
+      <c r="B235" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" t="s">
+        <v>280</v>
+      </c>
+      <c r="B236" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" t="s">
         <v>281</v>
       </c>
-      <c r="B235" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2">
-      <c r="A236" t="s">
-        <v>282</v>
-      </c>
-      <c r="B236" t="s">
+      <c r="B237" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" t="s">
+        <v>283</v>
+      </c>
+      <c r="B238" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="237" spans="1:2">
-      <c r="A237" t="s">
-        <v>283</v>
-      </c>
-      <c r="B237" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2">
-      <c r="A238" t="s">
+      <c r="B239" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" t="s">
         <v>285</v>
       </c>
-      <c r="B238" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2">
-      <c r="A239" t="s">
-        <v>286</v>
-      </c>
-      <c r="B239" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2">
-      <c r="A240" t="s">
-        <v>287</v>
-      </c>
       <c r="B240" t="s">
-        <v>784</v>
+        <v>767</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B241" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B242" t="s">
-        <v>786</v>
+        <v>1162</v>
+      </c>
+      <c r="C242" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>479</v>
+        <v>1172</v>
       </c>
       <c r="B243" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245" t="s">
-        <v>466</v>
-      </c>
-      <c r="B245" t="s">
-        <v>1165</v>
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" t="s">
+        <v>477</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="B246" t="s">
-        <v>294</v>
-      </c>
-      <c r="C246" t="s">
-        <v>527</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B247" t="s">
-        <v>512</v>
+        <v>292</v>
+      </c>
+      <c r="C247" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>292</v>
+        <v>454</v>
       </c>
       <c r="B248" t="s">
-        <v>863</v>
-      </c>
-      <c r="C248" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B249" t="s">
-        <v>846</v>
+        <v>844</v>
+      </c>
+      <c r="C249" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>449</v>
+        <v>291</v>
       </c>
       <c r="B250" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>295</v>
+        <v>447</v>
       </c>
       <c r="B251" t="s">
-        <v>855</v>
-      </c>
-      <c r="C251" t="s">
-        <v>1166</v>
+        <v>828</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B252" t="s">
-        <v>864</v>
+        <v>836</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1103</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B253" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B254" t="s">
-        <v>866</v>
+        <v>846</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B255" t="s">
-        <v>785</v>
+        <v>847</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>611</v>
+        <v>297</v>
       </c>
       <c r="B256" t="s">
-        <v>786</v>
+        <v>768</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="B257" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" t="s">
-        <v>644</v>
-      </c>
-      <c r="B259" t="s">
-        <v>645</v>
-      </c>
-      <c r="C259" t="s">
-        <v>598</v>
+        <v>1162</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
+        <v>476</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C258" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>495</v>
+        <v>635</v>
       </c>
       <c r="B260" t="s">
-        <v>498</v>
+        <v>636</v>
       </c>
       <c r="C260" t="s">
-        <v>525</v>
+        <v>594</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
+        <v>493</v>
+      </c>
+      <c r="B261" t="s">
         <v>496</v>
       </c>
-      <c r="B261" t="s">
-        <v>497</v>
-      </c>
       <c r="C261" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
+        <v>494</v>
+      </c>
+      <c r="B262" t="s">
+        <v>495</v>
+      </c>
+      <c r="C262" t="s">
         <v>524</v>
-      </c>
-      <c r="B262" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>316</v>
+        <v>522</v>
       </c>
       <c r="B263" t="s">
-        <v>302</v>
+        <v>536</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B264" t="s">
-        <v>303</v>
-      </c>
-      <c r="C264" t="s">
-        <v>527</v>
+        <v>300</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>457</v>
+        <v>315</v>
       </c>
       <c r="B265" t="s">
-        <v>513</v>
+        <v>301</v>
+      </c>
+      <c r="C265" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>318</v>
+        <v>455</v>
       </c>
       <c r="B266" t="s">
-        <v>304</v>
+        <v>511</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B267" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B268" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B269" t="s">
-        <v>307</v>
-      </c>
-      <c r="C269" t="s">
-        <v>527</v>
+        <v>304</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B270" t="s">
-        <v>308</v>
+        <v>305</v>
+      </c>
+      <c r="C270" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B271" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B272" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B273" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B274" t="s">
-        <v>312</v>
-      </c>
-      <c r="C274" t="s">
-        <v>527</v>
+        <v>309</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B275" t="s">
-        <v>313</v>
+        <v>310</v>
+      </c>
+      <c r="C275" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B276" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B277" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>477</v>
+        <v>327</v>
       </c>
       <c r="B278" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" t="s">
-        <v>542</v>
-      </c>
-      <c r="B280" t="s">
-        <v>543</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" t="s">
+        <v>475</v>
+      </c>
+      <c r="B279" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C279" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>336</v>
+        <v>540</v>
       </c>
       <c r="B281" t="s">
-        <v>354</v>
+        <v>541</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B282" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B283" t="s">
-        <v>352</v>
-      </c>
-      <c r="C283" t="s">
-        <v>527</v>
+        <v>349</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>458</v>
+        <v>336</v>
       </c>
       <c r="B284" t="s">
-        <v>514</v>
+        <v>350</v>
+      </c>
+      <c r="C284" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>355</v>
+        <v>456</v>
       </c>
       <c r="B285" t="s">
-        <v>353</v>
-      </c>
-      <c r="C285" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B286" t="s">
-        <v>345</v>
+        <v>351</v>
+      </c>
+      <c r="C286" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="B287" t="s">
-        <v>346</v>
-      </c>
-      <c r="C287" t="s">
-        <v>504</v>
+        <v>343</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B288" t="s">
-        <v>347</v>
+        <v>344</v>
+      </c>
+      <c r="C288" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B289" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B290" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B291" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B292" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>1067</v>
+        <v>342</v>
       </c>
       <c r="B293" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C293" t="s">
-        <v>1069</v>
+        <v>345</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>1070</v>
+        <v>1041</v>
       </c>
       <c r="B294" t="s">
-        <v>1071</v>
+        <v>1042</v>
       </c>
       <c r="C294" t="s">
-        <v>1069</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>1072</v>
+        <v>1044</v>
       </c>
       <c r="B295" t="s">
-        <v>1073</v>
+        <v>1045</v>
       </c>
       <c r="C295" t="s">
-        <v>1069</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>476</v>
+        <v>1046</v>
       </c>
       <c r="B296" t="s">
-        <v>1126</v>
+        <v>1047</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1043</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1167</v>
+        <v>1104</v>
       </c>
       <c r="B297" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3">
-      <c r="A299" t="s">
-        <v>646</v>
-      </c>
-      <c r="B299" t="s">
-        <v>664</v>
-      </c>
-      <c r="C299" t="s">
-        <v>598</v>
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" t="s">
+        <v>474</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C298" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>1074</v>
+        <v>637</v>
       </c>
       <c r="B300" t="s">
-        <v>1075</v>
+        <v>654</v>
       </c>
       <c r="C300" t="s">
-        <v>1069</v>
+        <v>594</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="B301" t="s">
-        <v>1077</v>
+        <v>1178</v>
       </c>
       <c r="C301" t="s">
-        <v>1069</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>1078</v>
+        <v>1049</v>
       </c>
       <c r="B302" t="s">
-        <v>1127</v>
+        <v>1179</v>
       </c>
       <c r="C302" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3">
-      <c r="A304" t="s">
-        <v>642</v>
-      </c>
-      <c r="B304" t="s">
-        <v>643</v>
-      </c>
-      <c r="C304" t="s">
-        <v>598</v>
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C303" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>467</v>
+        <v>633</v>
       </c>
       <c r="B305" t="s">
-        <v>468</v>
+        <v>634</v>
+      </c>
+      <c r="C305" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>362</v>
+        <v>465</v>
       </c>
       <c r="B306" t="s">
-        <v>373</v>
+        <v>466</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B307" t="s">
-        <v>374</v>
-      </c>
-      <c r="C307" t="s">
-        <v>527</v>
+        <v>371</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>515</v>
+        <v>361</v>
       </c>
       <c r="B308" t="s">
-        <v>516</v>
+        <v>372</v>
+      </c>
+      <c r="C308" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>364</v>
+        <v>513</v>
       </c>
       <c r="B309" t="s">
-        <v>375</v>
-      </c>
-      <c r="C309" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B310" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C310" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B311" t="s">
-        <v>528</v>
+        <v>374</v>
+      </c>
+      <c r="C311" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B312" t="s">
-        <v>377</v>
+        <v>526</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B313" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B314" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B315" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B316" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B317" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>699</v>
+        <v>370</v>
       </c>
       <c r="B318" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C318" t="s">
-        <v>598</v>
+        <v>380</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>1092</v>
+        <v>688</v>
       </c>
       <c r="B319" t="s">
-        <v>1093</v>
+        <v>1181</v>
+      </c>
+      <c r="C319" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>474</v>
+        <v>1062</v>
       </c>
       <c r="B320" t="s">
-        <v>1128</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B321" t="s">
-        <v>552</v>
+        <v>1182</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>1169</v>
+        <v>1106</v>
       </c>
       <c r="B322" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3">
-      <c r="A324" t="s">
-        <v>469</v>
-      </c>
-      <c r="B324" t="s">
-        <v>468</v>
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" t="s">
+        <v>472</v>
+      </c>
+      <c r="B323" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C323" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>389</v>
+        <v>467</v>
       </c>
       <c r="B325" t="s">
-        <v>400</v>
+        <v>466</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B326" t="s">
-        <v>401</v>
-      </c>
-      <c r="C326" t="s">
-        <v>527</v>
+        <v>398</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>459</v>
+        <v>388</v>
       </c>
       <c r="B327" t="s">
-        <v>517</v>
+        <v>399</v>
+      </c>
+      <c r="C327" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>391</v>
+        <v>457</v>
       </c>
       <c r="B328" t="s">
-        <v>402</v>
-      </c>
-      <c r="C328" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B329" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C329" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B330" t="s">
-        <v>529</v>
+        <v>401</v>
+      </c>
+      <c r="C330" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B331" t="s">
-        <v>377</v>
+        <v>527</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B332" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B333" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B334" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B335" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B336" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>473</v>
+        <v>397</v>
       </c>
       <c r="B337" t="s">
-        <v>1128</v>
+        <v>380</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B338" t="s">
-        <v>552</v>
+        <v>1182</v>
+      </c>
+      <c r="C338" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>1171</v>
+        <v>1108</v>
       </c>
       <c r="B339" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3">
-      <c r="A341" t="s">
-        <v>640</v>
-      </c>
-      <c r="B341" t="s">
-        <v>641</v>
-      </c>
-      <c r="C341" t="s">
-        <v>598</v>
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" t="s">
+        <v>471</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C340" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>383</v>
+        <v>631</v>
       </c>
       <c r="B342" t="s">
-        <v>559</v>
+        <v>632</v>
+      </c>
+      <c r="C342" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B343" t="s">
-        <v>560</v>
-      </c>
-      <c r="C343" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>460</v>
+        <v>382</v>
       </c>
       <c r="B344" t="s">
-        <v>561</v>
+        <v>557</v>
+      </c>
+      <c r="C344" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>385</v>
+        <v>458</v>
       </c>
       <c r="B345" t="s">
-        <v>586</v>
+        <v>558</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B346" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B347" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>1106</v>
+        <v>385</v>
       </c>
       <c r="B348" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1173</v>
+        <v>560</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>472</v>
+        <v>1076</v>
       </c>
       <c r="B349" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3">
-      <c r="A351" t="s">
-        <v>712</v>
-      </c>
-      <c r="B351" t="s">
-        <v>713</v>
-      </c>
-      <c r="C351" t="s">
-        <v>598</v>
+        <v>1077</v>
+      </c>
+      <c r="C349" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" t="s">
+        <v>470</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C350" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
+        <v>696</v>
+      </c>
+      <c r="B352" t="s">
+        <v>697</v>
+      </c>
+      <c r="C352" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" t="s">
+        <v>698</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C353" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" t="s">
+        <v>704</v>
+      </c>
+      <c r="B355" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" t="s">
+        <v>706</v>
+      </c>
+      <c r="B356" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" t="s">
+        <v>708</v>
+      </c>
+      <c r="B357" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358" t="s">
+        <v>710</v>
+      </c>
+      <c r="B358" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359" t="s">
+        <v>712</v>
+      </c>
+      <c r="B359" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360" t="s">
         <v>714</v>
       </c>
-      <c r="B352" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C352" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="354" spans="1:2">
-      <c r="A354" t="s">
+      <c r="B360" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" t="s">
+        <v>716</v>
+      </c>
+      <c r="B361" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" t="s">
+        <v>718</v>
+      </c>
+      <c r="B362" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363" t="s">
         <v>720</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B363" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="355" spans="1:2">
-      <c r="A355" t="s">
+      <c r="B364" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C364" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365" t="s">
         <v>722</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B365" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="356" spans="1:2">
-      <c r="A356" t="s">
+    <row r="366" spans="1:3">
+      <c r="A366" t="s">
         <v>724</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B366" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="357" spans="1:2">
-      <c r="A357" t="s">
+    <row r="367" spans="1:3">
+      <c r="A367" t="s">
         <v>726</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B367" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
-      <c r="A358" t="s">
+    <row r="368" spans="1:3">
+      <c r="A368" t="s">
         <v>728</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B368" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
-      <c r="A359" t="s">
+    <row r="369" spans="1:3">
+      <c r="A369" t="s">
         <v>730</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B369" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
-      <c r="A360" t="s">
+    <row r="370" spans="1:3">
+      <c r="A370" t="s">
         <v>732</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B370" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
-      <c r="A361" t="s">
+    <row r="371" spans="1:3">
+      <c r="A371" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372" t="s">
         <v>734</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B372" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="362" spans="1:2">
-      <c r="A362" t="s">
+    <row r="373" spans="1:3">
+      <c r="A373" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C374" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" t="s">
         <v>736</v>
       </c>
-      <c r="B362" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
-      <c r="A363" t="s">
+      <c r="B376" t="s">
         <v>737</v>
       </c>
-      <c r="B363" t="s">
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="364" spans="1:2">
-      <c r="A364" t="s">
+      <c r="B377" t="s">
         <v>739</v>
       </c>
-      <c r="B364" t="s">
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="365" spans="1:2">
-      <c r="A365" t="s">
+      <c r="B378" t="s">
         <v>741</v>
       </c>
-      <c r="B365" t="s">
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="366" spans="1:2">
-      <c r="A366" t="s">
+      <c r="B379" t="s">
         <v>743</v>
       </c>
-      <c r="B366" t="s">
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="A367" t="s">
+      <c r="B380" t="s">
         <v>745</v>
       </c>
-      <c r="B367" t="s">
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" t="s">
+      <c r="B381" t="s">
         <v>747</v>
       </c>
-      <c r="B368" t="s">
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" t="s">
+      <c r="B382" t="s">
         <v>749</v>
       </c>
-      <c r="B369" t="s">
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B370" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2">
-      <c r="A371" t="s">
+      <c r="B383" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384" t="s">
         <v>751</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B384" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
-      <c r="A372" t="s">
-        <v>1105</v>
-      </c>
-      <c r="B372" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="373" spans="1:2">
-      <c r="A373" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B373" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2">
-      <c r="A375" t="s">
+    <row r="385" spans="1:3">
+      <c r="A385" t="s">
         <v>753</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B385" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
-      <c r="A376" t="s">
+    <row r="386" spans="1:3">
+      <c r="A386" t="s">
         <v>755</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B386" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="377" spans="1:2">
-      <c r="A377" t="s">
+    <row r="387" spans="1:3">
+      <c r="A387" t="s">
         <v>757</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B387" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C387" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="378" spans="1:2">
-      <c r="A378" t="s">
+      <c r="B389" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" t="s">
         <v>759</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B390" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="379" spans="1:2">
-      <c r="A379" t="s">
+    <row r="391" spans="1:3">
+      <c r="A391" t="s">
         <v>761</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B391" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="380" spans="1:2">
-      <c r="A380" t="s">
-        <v>763</v>
-      </c>
-      <c r="B380" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="381" spans="1:2">
-      <c r="A381" t="s">
-        <v>765</v>
-      </c>
-      <c r="B381" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2">
-      <c r="A382" t="s">
-        <v>767</v>
-      </c>
-      <c r="B382" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2">
-      <c r="A383" t="s">
-        <v>768</v>
-      </c>
-      <c r="B383" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="384" spans="1:2">
-      <c r="A384" t="s">
-        <v>770</v>
-      </c>
-      <c r="B384" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="385" spans="1:2">
-      <c r="A385" t="s">
-        <v>772</v>
-      </c>
-      <c r="B385" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="386" spans="1:2">
-      <c r="A386" t="s">
+      <c r="B392" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" t="s">
+        <v>783</v>
+      </c>
+      <c r="B394" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" t="s">
+        <v>782</v>
+      </c>
+      <c r="B395" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396" t="s">
+        <v>776</v>
+      </c>
+      <c r="B396" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397" t="s">
         <v>774</v>
       </c>
-      <c r="B386" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="388" spans="1:2">
-      <c r="A388" t="s">
+      <c r="B397" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398" t="s">
         <v>775</v>
       </c>
-      <c r="B388" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="389" spans="1:2">
-      <c r="A389" t="s">
-        <v>776</v>
-      </c>
-      <c r="B389" t="s">
+      <c r="B398" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399" t="s">
+        <v>780</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C399" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" t="s">
+        <v>787</v>
+      </c>
+      <c r="B401" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" t="s">
+        <v>794</v>
+      </c>
+      <c r="B402" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" t="s">
+        <v>788</v>
+      </c>
+      <c r="B403" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="390" spans="1:2">
-      <c r="A390" t="s">
+    <row r="404" spans="1:3">
+      <c r="A404" t="s">
+        <v>789</v>
+      </c>
+      <c r="B404" t="s">
         <v>778</v>
       </c>
-      <c r="B390" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="391" spans="1:2">
-      <c r="A391" t="s">
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405" t="s">
+        <v>790</v>
+      </c>
+      <c r="B405" t="s">
         <v>779</v>
       </c>
-      <c r="B391" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="393" spans="1:2">
-      <c r="A393" t="s">
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" t="s">
+        <v>791</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C406" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" t="s">
+        <v>799</v>
+      </c>
+      <c r="B408" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409" t="s">
         <v>801</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B409" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3">
+      <c r="A410" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="394" spans="1:2">
-      <c r="A394" t="s">
-        <v>800</v>
-      </c>
-      <c r="B394" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="395" spans="1:2">
-      <c r="A395" t="s">
-        <v>794</v>
-      </c>
-      <c r="B395" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="396" spans="1:2">
-      <c r="A396" t="s">
-        <v>792</v>
-      </c>
-      <c r="B396" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="397" spans="1:2">
-      <c r="A397" t="s">
-        <v>793</v>
-      </c>
-      <c r="B397" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="398" spans="1:2">
-      <c r="A398" t="s">
-        <v>798</v>
-      </c>
-      <c r="B398" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="400" spans="1:2">
-      <c r="A400" t="s">
-        <v>805</v>
-      </c>
-      <c r="B400" t="s">
+      <c r="B410" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3">
+      <c r="A411" t="s">
+        <v>804</v>
+      </c>
+      <c r="B411" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3">
+      <c r="A412" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="401" spans="1:2">
-      <c r="A401" t="s">
+      <c r="B412" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3">
+      <c r="A413" t="s">
+        <v>811</v>
+      </c>
+      <c r="B413" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3">
+      <c r="A414" t="s">
         <v>812</v>
       </c>
-      <c r="B401" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="402" spans="1:2">
-      <c r="A402" t="s">
-        <v>806</v>
-      </c>
-      <c r="B402" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="403" spans="1:2">
-      <c r="A403" t="s">
-        <v>807</v>
-      </c>
-      <c r="B403" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="404" spans="1:2">
-      <c r="A404" t="s">
-        <v>808</v>
-      </c>
-      <c r="B404" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="405" spans="1:2">
-      <c r="A405" t="s">
+      <c r="B414" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3">
+      <c r="A415" t="s">
+        <v>815</v>
+      </c>
+      <c r="B415" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416" t="s">
+        <v>816</v>
+      </c>
+      <c r="B416" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417" t="s">
+        <v>817</v>
+      </c>
+      <c r="B417" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3">
+      <c r="A418" t="s">
+        <v>818</v>
+      </c>
+      <c r="B418" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3">
+      <c r="A419" t="s">
+        <v>819</v>
+      </c>
+      <c r="B419" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3">
+      <c r="A420" t="s">
+        <v>820</v>
+      </c>
+      <c r="B420" t="s">
         <v>809</v>
       </c>
-      <c r="B405" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="407" spans="1:2">
-      <c r="A407" t="s">
-        <v>817</v>
-      </c>
-      <c r="B407" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="408" spans="1:2">
-      <c r="A408" t="s">
-        <v>819</v>
-      </c>
-      <c r="B408" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="409" spans="1:2">
-      <c r="A409" t="s">
-        <v>820</v>
-      </c>
-      <c r="B409" t="s">
+    </row>
+    <row r="421" spans="1:3">
+      <c r="A421" t="s">
+        <v>821</v>
+      </c>
+      <c r="B421" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3">
+      <c r="A422" t="s">
+        <v>822</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C422" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3">
+      <c r="A423" t="s">
+        <v>823</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C423" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3">
+      <c r="A424" t="s">
+        <v>814</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C424" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3">
+      <c r="A425" t="s">
+        <v>813</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C425" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3">
+      <c r="A426" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427" t="s">
+        <v>997</v>
+      </c>
+      <c r="B427" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3">
+      <c r="A428" t="s">
+        <v>999</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3">
+      <c r="A429" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3">
+      <c r="A430" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3">
+      <c r="A431" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3">
+      <c r="A432" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3">
+      <c r="A433" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3">
+      <c r="A434" t="s">
         <v>1011</v>
       </c>
-    </row>
-    <row r="410" spans="1:2">
-      <c r="A410" t="s">
-        <v>822</v>
-      </c>
-      <c r="B410" t="s">
+      <c r="B434" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C434" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437" t="s">
+        <v>860</v>
+      </c>
+      <c r="B437" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438" t="s">
+        <v>862</v>
+      </c>
+      <c r="B438" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3">
+      <c r="A439" t="s">
+        <v>864</v>
+      </c>
+      <c r="B439" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3">
+      <c r="A440" t="s">
+        <v>866</v>
+      </c>
+      <c r="B440" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3">
+      <c r="A441" t="s">
+        <v>868</v>
+      </c>
+      <c r="B441" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3">
+      <c r="A442" t="s">
+        <v>870</v>
+      </c>
+      <c r="B442" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3">
+      <c r="A443" t="s">
+        <v>872</v>
+      </c>
+      <c r="B443" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444" t="s">
+        <v>874</v>
+      </c>
+      <c r="B444" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3">
+      <c r="A445" t="s">
+        <v>876</v>
+      </c>
+      <c r="B445" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3">
+      <c r="A446" t="s">
+        <v>878</v>
+      </c>
+      <c r="B446" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447" t="s">
+        <v>880</v>
+      </c>
+      <c r="B447" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448" t="s">
+        <v>882</v>
+      </c>
+      <c r="B448" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449" t="s">
+        <v>884</v>
+      </c>
+      <c r="B449" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3">
+      <c r="A450" t="s">
+        <v>886</v>
+      </c>
+      <c r="B450" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3">
+      <c r="A451" t="s">
+        <v>888</v>
+      </c>
+      <c r="B451" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3">
+      <c r="A452" t="s">
+        <v>890</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C452" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3">
+      <c r="A453" t="s">
+        <v>891</v>
+      </c>
+      <c r="B453" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3">
+      <c r="A454" t="s">
+        <v>893</v>
+      </c>
+      <c r="B454" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3">
+      <c r="A455" t="s">
+        <v>895</v>
+      </c>
+      <c r="B455" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3">
+      <c r="A456" t="s">
+        <v>897</v>
+      </c>
+      <c r="B456" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3">
+      <c r="A457" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3">
+      <c r="A458" t="s">
+        <v>899</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C458" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3">
+      <c r="A460" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3">
+      <c r="A461" t="s">
+        <v>900</v>
+      </c>
+      <c r="B461" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3">
+      <c r="A462" t="s">
+        <v>902</v>
+      </c>
+      <c r="B462" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3">
+      <c r="A463" t="s">
+        <v>904</v>
+      </c>
+      <c r="B463" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3">
+      <c r="A464" t="s">
+        <v>906</v>
+      </c>
+      <c r="B464" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3">
+      <c r="A465" t="s">
+        <v>908</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3">
+      <c r="A466" t="s">
+        <v>909</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3">
+      <c r="A467" t="s">
+        <v>910</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3">
+      <c r="A468" t="s">
+        <v>911</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3">
+      <c r="A469" t="s">
+        <v>912</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3">
+      <c r="A470" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3">
+      <c r="A471" t="s">
+        <v>913</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C471" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3">
+      <c r="A473" t="s">
+        <v>920</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C473" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3">
+      <c r="A474" t="s">
+        <v>921</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3">
+      <c r="A476" t="s">
+        <v>922</v>
+      </c>
+      <c r="B476" t="s">
+        <v>923</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3">
+      <c r="A477" t="s">
+        <v>924</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3">
+      <c r="A479" t="s">
+        <v>925</v>
+      </c>
+      <c r="B479" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3">
+      <c r="A480" t="s">
+        <v>927</v>
+      </c>
+      <c r="B480" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3">
+      <c r="A481" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3">
+      <c r="A482" t="s">
+        <v>929</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484" t="s">
+        <v>930</v>
+      </c>
+      <c r="B484" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485" t="s">
+        <v>932</v>
+      </c>
+      <c r="B485" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3">
+      <c r="A486" t="s">
+        <v>934</v>
+      </c>
+      <c r="B486" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3">
+      <c r="A487" t="s">
+        <v>936</v>
+      </c>
+      <c r="B487" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3">
+      <c r="A488" t="s">
+        <v>938</v>
+      </c>
+      <c r="B488" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3">
+      <c r="A489" t="s">
+        <v>940</v>
+      </c>
+      <c r="B489" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3">
+      <c r="A490" t="s">
+        <v>942</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C490" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492" t="s">
+        <v>943</v>
+      </c>
+      <c r="B492" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3">
+      <c r="A493" t="s">
+        <v>945</v>
+      </c>
+      <c r="B493" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3">
+      <c r="A494" t="s">
+        <v>947</v>
+      </c>
+      <c r="B494" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3">
+      <c r="A495" t="s">
+        <v>949</v>
+      </c>
+      <c r="B495" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3">
+      <c r="A496" t="s">
+        <v>951</v>
+      </c>
+      <c r="B496" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3">
+      <c r="A497" t="s">
+        <v>953</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3">
+      <c r="A499" t="s">
+        <v>954</v>
+      </c>
+      <c r="B499" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3">
+      <c r="A500" t="s">
+        <v>956</v>
+      </c>
+      <c r="B500" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3">
+      <c r="A501" t="s">
+        <v>958</v>
+      </c>
+      <c r="B501" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3">
+      <c r="A502" t="s">
+        <v>960</v>
+      </c>
+      <c r="B502" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3">
+      <c r="A503" t="s">
+        <v>962</v>
+      </c>
+      <c r="B503" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3">
+      <c r="A504" t="s">
+        <v>964</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3">
+      <c r="A506" t="s">
+        <v>965</v>
+      </c>
+      <c r="B506" t="s">
+        <v>966</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3">
+      <c r="A507" t="s">
+        <v>967</v>
+      </c>
+      <c r="B507" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3">
+      <c r="A508" t="s">
+        <v>969</v>
+      </c>
+      <c r="B508" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3">
+      <c r="A509" t="s">
+        <v>971</v>
+      </c>
+      <c r="B509" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3">
+      <c r="A510" t="s">
+        <v>973</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3">
+      <c r="A512" t="s">
         <v>1012</v>
       </c>
-    </row>
-    <row r="411" spans="1:2">
-      <c r="A411" t="s">
-        <v>828</v>
-      </c>
-      <c r="B411" t="s">
+      <c r="B512" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="412" spans="1:2">
-      <c r="A412" t="s">
-        <v>829</v>
-      </c>
-      <c r="B412" t="s">
+    <row r="513" spans="1:3">
+      <c r="A513" t="s">
         <v>1014</v>
       </c>
-    </row>
-    <row r="413" spans="1:2">
-      <c r="A413" t="s">
-        <v>830</v>
-      </c>
-      <c r="B413" t="s">
+      <c r="B513" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="414" spans="1:2">
-      <c r="A414" t="s">
-        <v>833</v>
-      </c>
-      <c r="B414" t="s">
+    <row r="514" spans="1:3">
+      <c r="A514" t="s">
         <v>1016</v>
       </c>
-    </row>
-    <row r="415" spans="1:2">
-      <c r="A415" t="s">
-        <v>834</v>
-      </c>
-      <c r="B415" t="s">
+      <c r="B514" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="416" spans="1:2">
-      <c r="A416" t="s">
-        <v>835</v>
-      </c>
-      <c r="B416" t="s">
+    <row r="515" spans="1:3">
+      <c r="A515" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="417" spans="1:2">
-      <c r="A417" t="s">
-        <v>836</v>
-      </c>
-      <c r="B417" t="s">
+      <c r="B515" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="418" spans="1:2">
-      <c r="A418" t="s">
-        <v>837</v>
-      </c>
-      <c r="B418" t="s">
+    <row r="516" spans="1:3">
+      <c r="A516" t="s">
         <v>1020</v>
       </c>
-    </row>
-    <row r="419" spans="1:2">
-      <c r="A419" t="s">
-        <v>838</v>
-      </c>
-      <c r="B419" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="420" spans="1:2">
-      <c r="A420" t="s">
-        <v>839</v>
-      </c>
-      <c r="B420" t="s">
+      <c r="B516" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="421" spans="1:2">
-      <c r="A421" t="s">
-        <v>840</v>
-      </c>
-      <c r="B421" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="422" spans="1:2">
-      <c r="A422" t="s">
-        <v>841</v>
-      </c>
-      <c r="B422" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="423" spans="1:2">
-      <c r="A423" t="s">
-        <v>832</v>
-      </c>
-      <c r="B423" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="424" spans="1:2">
-      <c r="A424" t="s">
-        <v>831</v>
-      </c>
-      <c r="B424" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="425" spans="1:2">
-      <c r="A425" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B425" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="426" spans="1:2">
-      <c r="A426" t="s">
+    <row r="517" spans="1:3">
+      <c r="A517" t="s">
         <v>1022</v>
       </c>
-      <c r="B426" t="s">
+      <c r="B517" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="427" spans="1:2">
-      <c r="A427" t="s">
+    <row r="518" spans="1:3">
+      <c r="A518" t="s">
         <v>1024</v>
       </c>
-      <c r="B427" t="s">
+      <c r="B518" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="428" spans="1:2">
-      <c r="A428" t="s">
+    <row r="519" spans="1:3">
+      <c r="A519" t="s">
         <v>1026</v>
       </c>
-      <c r="B428" t="s">
+      <c r="B519" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="429" spans="1:2">
-      <c r="A429" t="s">
+    <row r="520" spans="1:3">
+      <c r="A520" t="s">
         <v>1028</v>
       </c>
-      <c r="B429" t="s">
+      <c r="B520" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="430" spans="1:2">
-      <c r="A430" t="s">
+    <row r="521" spans="1:3">
+      <c r="A521" t="s">
         <v>1030</v>
       </c>
-      <c r="B430" t="s">
+      <c r="B521" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="431" spans="1:2">
-      <c r="A431" t="s">
+    <row r="522" spans="1:3">
+      <c r="A522" t="s">
         <v>1032</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B522" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="432" spans="1:2">
-      <c r="A432" t="s">
+    <row r="523" spans="1:3">
+      <c r="A523" t="s">
         <v>1034</v>
       </c>
-      <c r="B432" t="s">
+      <c r="B523" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="433" spans="1:2">
-      <c r="A433" t="s">
+    <row r="524" spans="1:3">
+      <c r="A524" t="s">
         <v>1036</v>
       </c>
-      <c r="B433" t="s">
+      <c r="B524" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="434" spans="1:2">
-      <c r="A434" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B434" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="436" spans="1:2">
-      <c r="A436" t="s">
-        <v>881</v>
-      </c>
-      <c r="B436" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="437" spans="1:2">
-      <c r="A437" t="s">
-        <v>883</v>
-      </c>
-      <c r="B437" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="438" spans="1:2">
-      <c r="A438" t="s">
-        <v>885</v>
-      </c>
-      <c r="B438" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="439" spans="1:2">
-      <c r="A439" t="s">
-        <v>887</v>
-      </c>
-      <c r="B439" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="440" spans="1:2">
-      <c r="A440" t="s">
-        <v>889</v>
-      </c>
-      <c r="B440" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="441" spans="1:2">
-      <c r="A441" t="s">
-        <v>891</v>
-      </c>
-      <c r="B441" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="442" spans="1:2">
-      <c r="A442" t="s">
-        <v>893</v>
-      </c>
-      <c r="B442" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="443" spans="1:2">
-      <c r="A443" t="s">
-        <v>895</v>
-      </c>
-      <c r="B443" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="444" spans="1:2">
-      <c r="A444" t="s">
-        <v>897</v>
-      </c>
-      <c r="B444" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="445" spans="1:2">
-      <c r="A445" t="s">
-        <v>899</v>
-      </c>
-      <c r="B445" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="446" spans="1:2">
-      <c r="A446" t="s">
-        <v>901</v>
-      </c>
-      <c r="B446" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="447" spans="1:2">
-      <c r="A447" t="s">
-        <v>903</v>
-      </c>
-      <c r="B447" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="448" spans="1:2">
-      <c r="A448" t="s">
-        <v>905</v>
-      </c>
-      <c r="B448" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="449" spans="1:2">
-      <c r="A449" t="s">
-        <v>907</v>
-      </c>
-      <c r="B449" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="450" spans="1:2">
-      <c r="A450" t="s">
-        <v>909</v>
-      </c>
-      <c r="B450" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="451" spans="1:2">
-      <c r="A451" t="s">
-        <v>911</v>
-      </c>
-      <c r="B451" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="452" spans="1:2">
-      <c r="A452" t="s">
-        <v>913</v>
-      </c>
-      <c r="B452" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="453" spans="1:2">
-      <c r="A453" t="s">
-        <v>915</v>
-      </c>
-      <c r="B453" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="454" spans="1:2">
-      <c r="A454" t="s">
-        <v>917</v>
-      </c>
-      <c r="B454" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="455" spans="1:2">
-      <c r="A455" t="s">
-        <v>919</v>
-      </c>
-      <c r="B455" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="456" spans="1:2">
-      <c r="A456" t="s">
-        <v>921</v>
-      </c>
-      <c r="B456" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="457" spans="1:2">
-      <c r="A457" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B457" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="459" spans="1:2">
-      <c r="A459" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B459" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="460" spans="1:2">
-      <c r="A460" t="s">
-        <v>922</v>
-      </c>
-      <c r="B460" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="461" spans="1:2">
-      <c r="A461" t="s">
-        <v>924</v>
-      </c>
-      <c r="B461" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="462" spans="1:2">
-      <c r="A462" t="s">
-        <v>926</v>
-      </c>
-      <c r="B462" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="463" spans="1:2">
-      <c r="A463" t="s">
-        <v>928</v>
-      </c>
-      <c r="B463" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="464" spans="1:2">
-      <c r="A464" t="s">
-        <v>930</v>
-      </c>
-      <c r="B464" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="465" spans="1:2">
-      <c r="A465" t="s">
-        <v>931</v>
-      </c>
-      <c r="B465" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="466" spans="1:2">
-      <c r="A466" t="s">
-        <v>932</v>
-      </c>
-      <c r="B466" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="467" spans="1:2">
-      <c r="A467" t="s">
-        <v>933</v>
-      </c>
-      <c r="B467" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="468" spans="1:2">
-      <c r="A468" t="s">
-        <v>934</v>
-      </c>
-      <c r="B468" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="469" spans="1:2">
-      <c r="A469" t="s">
-        <v>935</v>
-      </c>
-      <c r="B469" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="470" spans="1:2">
-      <c r="A470" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B470" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="472" spans="1:2">
-      <c r="A472" t="s">
-        <v>942</v>
-      </c>
-      <c r="B472" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="473" spans="1:2">
-      <c r="A473" t="s">
-        <v>944</v>
-      </c>
-      <c r="B473" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="475" spans="1:2">
-      <c r="A475" t="s">
-        <v>945</v>
-      </c>
-      <c r="B475" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="476" spans="1:2">
-      <c r="A476" t="s">
-        <v>947</v>
-      </c>
-      <c r="B476" t="s">
+    <row r="525" spans="1:3">
+      <c r="A525" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C525" t="s">
         <v>1138</v>
       </c>
     </row>
-    <row r="478" spans="1:2">
-      <c r="A478" t="s">
-        <v>948</v>
-      </c>
-      <c r="B478" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="479" spans="1:2">
-      <c r="A479" t="s">
-        <v>950</v>
-      </c>
-      <c r="B479" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="480" spans="1:2">
-      <c r="A480" t="s">
-        <v>952</v>
-      </c>
-      <c r="B480" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="481" spans="1:2">
-      <c r="A481" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="483" spans="1:2">
-      <c r="A483" t="s">
-        <v>953</v>
-      </c>
-      <c r="B483" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="484" spans="1:2">
-      <c r="A484" t="s">
-        <v>955</v>
-      </c>
-      <c r="B484" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="485" spans="1:2">
-      <c r="A485" t="s">
-        <v>957</v>
-      </c>
-      <c r="B485" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="486" spans="1:2">
-      <c r="A486" t="s">
-        <v>959</v>
-      </c>
-      <c r="B486" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="487" spans="1:2">
-      <c r="A487" t="s">
-        <v>961</v>
-      </c>
-      <c r="B487" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="488" spans="1:2">
-      <c r="A488" t="s">
-        <v>963</v>
-      </c>
-      <c r="B488" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="489" spans="1:2">
-      <c r="A489" t="s">
-        <v>965</v>
-      </c>
-      <c r="B489" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="491" spans="1:2">
-      <c r="A491" t="s">
-        <v>966</v>
-      </c>
-      <c r="B491" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="492" spans="1:2">
-      <c r="A492" t="s">
-        <v>968</v>
-      </c>
-      <c r="B492" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="493" spans="1:2">
-      <c r="A493" t="s">
-        <v>970</v>
-      </c>
-      <c r="B493" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="494" spans="1:2">
-      <c r="A494" t="s">
-        <v>972</v>
-      </c>
-      <c r="B494" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="495" spans="1:2">
-      <c r="A495" t="s">
-        <v>974</v>
-      </c>
-      <c r="B495" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="496" spans="1:2">
-      <c r="A496" t="s">
-        <v>976</v>
-      </c>
-      <c r="B496" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="498" spans="1:2">
-      <c r="A498" t="s">
-        <v>977</v>
-      </c>
-      <c r="B498" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="499" spans="1:2">
-      <c r="A499" t="s">
-        <v>979</v>
-      </c>
-      <c r="B499" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="500" spans="1:2">
-      <c r="A500" t="s">
-        <v>981</v>
-      </c>
-      <c r="B500" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="501" spans="1:2">
-      <c r="A501" t="s">
-        <v>983</v>
-      </c>
-      <c r="B501" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="502" spans="1:2">
-      <c r="A502" t="s">
-        <v>985</v>
-      </c>
-      <c r="B502" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="503" spans="1:2">
-      <c r="A503" t="s">
-        <v>987</v>
-      </c>
-      <c r="B503" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="505" spans="1:2">
-      <c r="A505" t="s">
-        <v>988</v>
-      </c>
-      <c r="B505" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="506" spans="1:2">
-      <c r="A506" t="s">
-        <v>990</v>
-      </c>
-      <c r="B506" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="507" spans="1:2">
-      <c r="A507" t="s">
-        <v>992</v>
-      </c>
-      <c r="B507" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="508" spans="1:2">
-      <c r="A508" t="s">
-        <v>994</v>
-      </c>
-      <c r="B508" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="509" spans="1:2">
-      <c r="A509" t="s">
-        <v>996</v>
-      </c>
-      <c r="B509" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="511" spans="1:2">
-      <c r="A511" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B511" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="512" spans="1:2">
-      <c r="A512" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B512" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="513" spans="1:2">
-      <c r="A513" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B513" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="514" spans="1:2">
-      <c r="A514" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B514" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="515" spans="1:2">
-      <c r="A515" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B515" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="516" spans="1:2">
-      <c r="A516" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B516" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="517" spans="1:2">
-      <c r="A517" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="518" spans="1:2">
-      <c r="A518" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B518" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="519" spans="1:2">
-      <c r="A519" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B519" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="520" spans="1:2">
-      <c r="A520" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B520" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="521" spans="1:2">
-      <c r="A521" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B521" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="522" spans="1:2">
-      <c r="A522" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B522" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="523" spans="1:2">
-      <c r="A523" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="524" spans="1:2">
-      <c r="A524" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1196</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:C525" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
   <conditionalFormatting sqref="A478:A479 A475:A476 A460:A470 A472:A473 A481">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0918\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4338F6-35BB-4123-974A-A2774C2FEBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913C9FAB-7E65-4BD4-AAE6-0E543C6054C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3456,208 +3456,208 @@
     <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
   </si>
   <si>
-    <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Updated by Raluca</t>
   </si>
   <si>
     <t>Assets exceed HUD asset limit. Third party verification of all assets is required.</t>
   </si>
   <si>
-    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Applicant is a Dominium employee. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Income type included that cannot be validated with automation. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Annual income is listed as zero. Confirm this is accurate and ensure the Certification of Zero Income is present in the file.</t>
   </si>
   <si>
-    <t>This application is a Section 811 unit. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Income Calculation Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Application Summary. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Applicant reported a minor will live in the household less than 50% of the time. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Member Information Document. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income &amp; Asset Questionnaire. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Current employment has been documented on the Self-Certification of Non-Employment. Verification of employment is needed.</t>
   </si>
   <si>
-    <t>Unable to validate Self Certification of Non Employment. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Applicant has reported they have no assets. If applicant has income, confirm how the income is paid.</t>
   </si>
   <si>
-    <t>Unable to validate Asset Self Certification &amp; Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Affidavit of Student Financial Assistance. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Student Certification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Annual Student Certification since there is Home unit . Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Zero Income. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate VAWA Acknowledgement. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Screening Document. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Raluca removed the check as per business requirement</t>
   </si>
   <si>
     <t>Multiple sources of verification included for same income. Remove verification documents that are not being used in the calculation of income.</t>
   </si>
   <si>
-    <t>Regular pay rate has increased across paystubs. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Paystubs list YTD pay that is not paid on a current paystub so annual income cannot be accurately predicted. Clarify, with the employer, the pay type and how often it is received.</t>
   </si>
   <si>
-    <t>Unable to validate paystubs. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Verification of Employment - manual review is needed to ensure document was received via 3rd party.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Commission, bonuses, tips, other amount has been populated. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Anticipated wage increase indicated on employment verification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Employment. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Offer Letter. Manual review is needed.</t>
-  </si>
-  <si>
     <t>WN_TotalMatchSum</t>
   </si>
   <si>
     <t>Total Pay listed on the Work Number does not match the sum of each pay type on the Work Number.</t>
   </si>
   <si>
-    <t>Unable to validate Work Number. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self-Employment Certification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Payment History. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Both 120 days of pay history available and 120 days of pay history not available data sections are populated on the Child Support Calculator. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
   </si>
   <si>
     <t>The consistent payments data is populated on Child Support Calcs but additional data tables are populated as well. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
   </si>
   <si>
-    <t>Unable to validate Child Support Calcs. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Social Security Benefits Letter is missing at least one page. Upload missing page with final signed documents.</t>
   </si>
   <si>
-    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Reccurring Cash Contribution. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Self-Employment Income. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Profit/Loss Statement. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Household Asset Breakdown. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Employment Verification. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Season or Sporadic work has been documented on the Employment Verification. Manual review is needed.  </t>
   </si>
   <si>
     <t>Applicant marked that no household members are part of the original qualifying household. Please have the applicant correct.</t>
   </si>
   <si>
-    <t>Unable to validate the Certification of Student Status. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Regular Contributions Verification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Bank statements are included in the file. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Bank Statements. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Leave and Earnings Statement. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Release and Consent Form. Manual review is needed. </t>
-  </si>
-  <si>
     <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
   </si>
   <si>
-    <t>Unable to validate Verification Services. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
+    <t>Unable to validate Housing History Disclosure. manual review required.</t>
+  </si>
+  <si>
+    <t>Live-In Attendant documented on the Income Calculation Worksheet. manual review required.</t>
+  </si>
+  <si>
+    <t>Applicant is a Dominium employee. manual review required.</t>
+  </si>
+  <si>
+    <t>Income type included that cannot be validated with automation. manual review required.</t>
+  </si>
+  <si>
+    <t>This application is a Section 811 unit. manual review required. </t>
+  </si>
+  <si>
+    <t>Unable to validate Income Calculation Worksheet. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Application Summary. manual review required.</t>
+  </si>
+  <si>
+    <t>Applicant reported a minor will live in the household less than 50% of the time. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Member Information Document. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Income &amp; Asset Questionnaire. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self Certification of Non Employment. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Self Certification &amp; Worksheet. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Affidavit of Student Financial Assistance. manual review required.</t>
+  </si>
+  <si>
+    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Student Certification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Annual Student Certification since there is Home unit . manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Zero Income. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate VAWA Acknowledgement. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Screening Document. manual review required.</t>
+  </si>
+  <si>
+    <t>Regular pay rate has increased across paystubs. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate paystubs. manual review required.</t>
+  </si>
+  <si>
+    <t>Verification of Employment - manual review required to ensure document was received via 3rd party.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. manual review required.</t>
+  </si>
+  <si>
+    <t>Commission, bonuses, tips, other amount has been populated. manual review required.</t>
+  </si>
+  <si>
+    <t>Anticipated wage increase indicated on employment verification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Employment. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Offer Letter. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Work Number. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self-Employment Certification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Payment History. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Calcs. manual review required.</t>
+  </si>
+  <si>
+    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Supplemental Security Income Letter. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Reccurring Cash Contribution. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing Demographic Reporting Form. manual review required.</t>
+  </si>
+  <si>
+    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Self-Employment Income. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Profit/Loss Statement. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Applicant/Tenant Release and Consent. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Household Asset Breakdown. manual review required.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. manual review required. </t>
+  </si>
+  <si>
+    <t>Unable to validate Employment Verification. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate the Certification of Student Status. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Regular Contributions Verification. manual review required.</t>
+  </si>
+  <si>
+    <t>Bank statements are included in the file. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Bank Statements. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Leave and Earnings Statement. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Veterans Affairs Benefits Letter. manual review required.</t>
+  </si>
+  <si>
+    <t>Unable to validate Release and Consent Form. manual review required. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. manual review required. </t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Certification of Net Family Assets. manual review required. </t>
   </si>
 </sst>
 </file>
@@ -8665,10 +8665,10 @@
         <v>653</v>
       </c>
       <c r="B13" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C13" t="s">
         <v>1137</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8727,10 +8727,10 @@
         <v>590</v>
       </c>
       <c r="B21" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C21" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8738,10 +8738,10 @@
         <v>598</v>
       </c>
       <c r="B22" t="s">
-        <v>1140</v>
+        <v>1154</v>
       </c>
       <c r="C22" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8760,10 +8760,10 @@
         <v>623</v>
       </c>
       <c r="B24" t="s">
-        <v>1141</v>
+        <v>1155</v>
       </c>
       <c r="C24" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8771,10 +8771,10 @@
         <v>625</v>
       </c>
       <c r="B25" t="s">
-        <v>1142</v>
+        <v>1156</v>
       </c>
       <c r="C25" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8782,10 +8782,10 @@
         <v>692</v>
       </c>
       <c r="B26" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="C26" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8793,10 +8793,10 @@
         <v>826</v>
       </c>
       <c r="B27" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="C27" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8804,7 +8804,7 @@
         <v>473</v>
       </c>
       <c r="B28" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8938,7 +8938,7 @@
         <v>488</v>
       </c>
       <c r="B45" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9045,10 +9045,10 @@
         <v>595</v>
       </c>
       <c r="B59" t="s">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="C59" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -9056,10 +9056,10 @@
         <v>487</v>
       </c>
       <c r="B60" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="C60" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9227,7 +9227,7 @@
         <v>486</v>
       </c>
       <c r="B79" t="s">
-        <v>1149</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9267,10 +9267,10 @@
         <v>649</v>
       </c>
       <c r="B85" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="C85" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -9311,7 +9311,7 @@
         <v>485</v>
       </c>
       <c r="B89" t="s">
-        <v>1151</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9490,10 +9490,10 @@
         <v>849</v>
       </c>
       <c r="B109" t="s">
-        <v>1152</v>
+        <v>1141</v>
       </c>
       <c r="C109" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -9525,7 +9525,7 @@
         <v>484</v>
       </c>
       <c r="B113" t="s">
-        <v>1153</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -9643,7 +9643,7 @@
         <v>483</v>
       </c>
       <c r="B125" t="s">
-        <v>1154</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9710,10 +9710,10 @@
         <v>562</v>
       </c>
       <c r="B134" t="s">
-        <v>1155</v>
+        <v>1166</v>
       </c>
       <c r="C134" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -9740,7 +9740,7 @@
         <v>482</v>
       </c>
       <c r="B137" t="s">
-        <v>1156</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -9759,7 +9759,7 @@
         <v>609</v>
       </c>
       <c r="B140" t="s">
-        <v>1157</v>
+        <v>1168</v>
       </c>
       <c r="C140" t="s">
         <v>608</v>
@@ -9832,7 +9832,7 @@
         <v>481</v>
       </c>
       <c r="B149" t="s">
-        <v>1158</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9872,7 +9872,7 @@
         <v>480</v>
       </c>
       <c r="B155" t="s">
-        <v>1159</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -9967,10 +9967,10 @@
         <v>469</v>
       </c>
       <c r="B166" t="s">
-        <v>1160</v>
+        <v>1171</v>
       </c>
       <c r="C166" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -9992,7 +9992,7 @@
         <v>829</v>
       </c>
       <c r="C169" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -10014,7 +10014,7 @@
         <v>830</v>
       </c>
       <c r="C171" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -10033,10 +10033,10 @@
         <v>701</v>
       </c>
       <c r="B173" t="s">
-        <v>1141</v>
+        <v>1155</v>
       </c>
       <c r="C173" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -10201,10 +10201,10 @@
         <v>599</v>
       </c>
       <c r="B192" t="s">
-        <v>1162</v>
+        <v>1143</v>
       </c>
       <c r="C192" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -10215,7 +10215,7 @@
         <v>663</v>
       </c>
       <c r="C193" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -10223,10 +10223,10 @@
         <v>674</v>
       </c>
       <c r="B194" t="s">
-        <v>1163</v>
+        <v>1172</v>
       </c>
       <c r="C194" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -10234,10 +10234,10 @@
         <v>848</v>
       </c>
       <c r="B195" t="s">
-        <v>1164</v>
+        <v>1144</v>
       </c>
       <c r="C195" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -10253,10 +10253,10 @@
         <v>468</v>
       </c>
       <c r="B197" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="C197" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -10264,10 +10264,10 @@
         <v>673</v>
       </c>
       <c r="B199" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="C199" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -10313,10 +10313,10 @@
         <v>246</v>
       </c>
       <c r="B204" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="C204" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -10440,10 +10440,10 @@
         <v>273</v>
       </c>
       <c r="B218" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="C218" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -10451,10 +10451,10 @@
         <v>600</v>
       </c>
       <c r="B219" t="s">
-        <v>1162</v>
+        <v>1143</v>
       </c>
       <c r="C219" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -10462,10 +10462,10 @@
         <v>597</v>
       </c>
       <c r="B220" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="C220" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -10473,10 +10473,10 @@
         <v>479</v>
       </c>
       <c r="B221" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="C221" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -10540,10 +10540,10 @@
         <v>601</v>
       </c>
       <c r="B230" t="s">
-        <v>1162</v>
+        <v>1143</v>
       </c>
       <c r="C230" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -10551,10 +10551,10 @@
         <v>478</v>
       </c>
       <c r="B231" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="C231" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -10634,18 +10634,18 @@
         <v>602</v>
       </c>
       <c r="B242" t="s">
-        <v>1162</v>
+        <v>1143</v>
       </c>
       <c r="C242" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>1172</v>
+        <v>1145</v>
       </c>
       <c r="B243" t="s">
-        <v>1173</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -10653,10 +10653,10 @@
         <v>477</v>
       </c>
       <c r="B244" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="C244" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -10761,10 +10761,10 @@
         <v>603</v>
       </c>
       <c r="B257" t="s">
-        <v>1162</v>
+        <v>1143</v>
       </c>
       <c r="C257" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -10772,10 +10772,10 @@
         <v>476</v>
       </c>
       <c r="B258" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="C258" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -10953,10 +10953,10 @@
         <v>475</v>
       </c>
       <c r="B279" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="C279" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -11118,10 +11118,10 @@
         <v>474</v>
       </c>
       <c r="B298" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="C298" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -11140,10 +11140,10 @@
         <v>1048</v>
       </c>
       <c r="B301" t="s">
-        <v>1178</v>
+        <v>1147</v>
       </c>
       <c r="C301" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -11151,10 +11151,10 @@
         <v>1049</v>
       </c>
       <c r="B302" t="s">
-        <v>1179</v>
+        <v>1148</v>
       </c>
       <c r="C302" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -11162,10 +11162,10 @@
         <v>1050</v>
       </c>
       <c r="B303" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="C303" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -11297,10 +11297,10 @@
         <v>688</v>
       </c>
       <c r="B319" t="s">
-        <v>1181</v>
+        <v>1149</v>
       </c>
       <c r="C319" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -11316,10 +11316,10 @@
         <v>549</v>
       </c>
       <c r="B321" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="C321" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -11335,10 +11335,10 @@
         <v>472</v>
       </c>
       <c r="B323" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="C323" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -11459,10 +11459,10 @@
         <v>555</v>
       </c>
       <c r="B338" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="C338" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -11478,10 +11478,10 @@
         <v>471</v>
       </c>
       <c r="B340" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="C340" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -11562,10 +11562,10 @@
         <v>470</v>
       </c>
       <c r="B350" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="C350" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -11584,10 +11584,10 @@
         <v>698</v>
       </c>
       <c r="B353" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="C353" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -11667,10 +11667,10 @@
         <v>721</v>
       </c>
       <c r="B364" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C364" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -11750,10 +11750,10 @@
         <v>1075</v>
       </c>
       <c r="B374" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="C374" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -11849,10 +11849,10 @@
         <v>757</v>
       </c>
       <c r="B387" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="C387" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11932,10 +11932,10 @@
         <v>780</v>
       </c>
       <c r="B399" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="C399" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11983,10 +11983,10 @@
         <v>791</v>
       </c>
       <c r="B406" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="C406" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -12010,10 +12010,10 @@
         <v>802</v>
       </c>
       <c r="B410" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="C410" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -12029,10 +12029,10 @@
         <v>810</v>
       </c>
       <c r="B412" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="C412" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -12112,10 +12112,10 @@
         <v>822</v>
       </c>
       <c r="B422" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="C422" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -12123,10 +12123,10 @@
         <v>823</v>
       </c>
       <c r="B423" t="s">
-        <v>1162</v>
+        <v>1143</v>
       </c>
       <c r="C423" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -12134,10 +12134,10 @@
         <v>814</v>
       </c>
       <c r="B424" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="C424" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -12145,10 +12145,10 @@
         <v>813</v>
       </c>
       <c r="B425" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="C425" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -12220,10 +12220,10 @@
         <v>1011</v>
       </c>
       <c r="B434" t="s">
-        <v>1193</v>
+        <v>1150</v>
       </c>
       <c r="C434" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -12359,10 +12359,10 @@
         <v>890</v>
       </c>
       <c r="B452" t="s">
-        <v>1194</v>
+        <v>1151</v>
       </c>
       <c r="C452" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -12410,10 +12410,10 @@
         <v>899</v>
       </c>
       <c r="B458" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C458" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -12509,10 +12509,10 @@
         <v>913</v>
       </c>
       <c r="B471" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C471" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -12520,10 +12520,10 @@
         <v>920</v>
       </c>
       <c r="B473" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C473" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -12531,10 +12531,10 @@
         <v>921</v>
       </c>
       <c r="B474" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C474" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -12545,7 +12545,7 @@
         <v>923</v>
       </c>
       <c r="C476" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12553,10 +12553,10 @@
         <v>924</v>
       </c>
       <c r="B477" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C477" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12588,10 +12588,10 @@
         <v>929</v>
       </c>
       <c r="B482" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C482" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12647,10 +12647,10 @@
         <v>942</v>
       </c>
       <c r="B490" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C490" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12698,10 +12698,10 @@
         <v>953</v>
       </c>
       <c r="B497" t="s">
-        <v>1202</v>
+        <v>1152</v>
       </c>
       <c r="C497" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12752,7 +12752,7 @@
         <v>1128</v>
       </c>
       <c r="C504" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12763,7 +12763,7 @@
         <v>966</v>
       </c>
       <c r="C506" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12798,7 +12798,7 @@
         <v>1203</v>
       </c>
       <c r="C510" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12913,7 +12913,7 @@
         <v>1204</v>
       </c>
       <c r="C525" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\0918\Application-Review-Process_Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913C9FAB-7E65-4BD4-AAE6-0E543C6054C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64A1AE3-9C17-42F6-AFA6-C0CA098F4359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -3504,160 +3504,160 @@
     <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
   </si>
   <si>
-    <t>Unable to validate Housing History Disclosure. manual review required.</t>
-  </si>
-  <si>
-    <t>Live-In Attendant documented on the Income Calculation Worksheet. manual review required.</t>
-  </si>
-  <si>
-    <t>Applicant is a Dominium employee. manual review required.</t>
-  </si>
-  <si>
-    <t>Income type included that cannot be validated with automation. manual review required.</t>
-  </si>
-  <si>
-    <t>This application is a Section 811 unit. manual review required. </t>
-  </si>
-  <si>
-    <t>Unable to validate Income Calculation Worksheet. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Application Summary. manual review required.</t>
-  </si>
-  <si>
-    <t>Applicant reported a minor will live in the household less than 50% of the time. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Member Information Document. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income &amp; Asset Questionnaire. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self Certification of Non Employment. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Self Certification &amp; Worksheet. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Affidavit of Student Financial Assistance. manual review required.</t>
-  </si>
-  <si>
-    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Student Certification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Annual Student Certification since there is Home unit . manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Zero Income. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate VAWA Acknowledgement. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Screening Document. manual review required.</t>
-  </si>
-  <si>
-    <t>Regular pay rate has increased across paystubs. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate paystubs. manual review required.</t>
-  </si>
-  <si>
-    <t>Verification of Employment - manual review required to ensure document was received via 3rd party.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. manual review required.</t>
-  </si>
-  <si>
-    <t>Commission, bonuses, tips, other amount has been populated. manual review required.</t>
-  </si>
-  <si>
-    <t>Anticipated wage increase indicated on employment verification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Employment. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Offer Letter. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Work Number. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self-Employment Certification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Payment History. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Calcs. manual review required.</t>
-  </si>
-  <si>
-    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Supplemental Security Income Letter. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Reccurring Cash Contribution. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Housing Demographic Reporting Form. manual review required.</t>
-  </si>
-  <si>
-    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Self-Employment Income. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Profit/Loss Statement. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate findings for Applicant/Tenant Release and Consent. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Household Asset Breakdown. manual review required.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. manual review required. </t>
-  </si>
-  <si>
-    <t>Unable to validate Employment Verification. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate the Certification of Student Status. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Regular Contributions Verification. manual review required.</t>
-  </si>
-  <si>
-    <t>Bank statements are included in the file. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Bank Statements. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Leave and Earnings Statement. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Veterans Affairs Benefits Letter. manual review required.</t>
-  </si>
-  <si>
-    <t>Unable to validate Release and Consent Form. manual review required. </t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. manual review required. </t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Certification of Net Family Assets. manual review required. </t>
+    <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant is a Dominium employee. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Income type included that cannot be validated with automation. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>This application is a Section 811 unit. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Application Summary. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant reported a minor will live in the household less than 50% of the time. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Member Information Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Income &amp; Asset Questionnaire. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self Certification of Non Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Self Certification &amp; Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Affidavit of Student Financial Assistance. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Annual Student Certification since there is Home unit . Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Zero Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate VAWA Acknowledgement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Screening Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Regular pay rate has increased across paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Verification of Employment - manual review is needed to ensure document was received via 3rd party.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Commission, bonuses, tips, other amount has been populated. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Anticipated wage increase indicated on employment verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Offer Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Work Number. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self-Employment Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Payment History. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Calcs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Reccurring Cash Contribution. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Self-Employment Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Profit/Loss Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Household Asset Breakdown. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Employment Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate the Certification of Student Status. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Regular Contributions Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Bank statements are included in the file. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Bank Statements. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Leave and Earnings Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Release and Consent Form. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
   </si>
 </sst>
 </file>
@@ -8567,7 +8567,7 @@
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
     <col min="2" max="2" width="153.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="97" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64A1AE3-9C17-42F6-AFA6-C0CA098F4359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B501D39-4394-4090-9102-6ACE98159B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2838,9 +2838,6 @@
     <t>RCFExists</t>
   </si>
   <si>
-    <t xml:space="preserve">The Release and Consent for is missing from the application. </t>
-  </si>
-  <si>
     <t>RCF_ApplicantName</t>
   </si>
   <si>
@@ -3658,6 +3655,9 @@
   </si>
   <si>
     <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Release and Consent Form is missing from the application. </t>
   </si>
 </sst>
 </file>
@@ -4093,7 +4093,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -4114,7 +4114,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -4126,7 +4126,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -4156,10 +4156,10 @@
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B12" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -4491,77 +4491,77 @@
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1">
       <c r="A52" t="s">
+        <v>973</v>
+      </c>
+      <c r="B52" t="s">
         <v>974</v>
-      </c>
-      <c r="B52" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1">
       <c r="A53" t="s">
+        <v>975</v>
+      </c>
+      <c r="B53" t="s">
         <v>976</v>
-      </c>
-      <c r="B53" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1">
       <c r="A54" t="s">
+        <v>977</v>
+      </c>
+      <c r="B54" t="s">
         <v>978</v>
-      </c>
-      <c r="B54" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1">
       <c r="A55" t="s">
+        <v>979</v>
+      </c>
+      <c r="B55" t="s">
         <v>980</v>
-      </c>
-      <c r="B55" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" t="s">
+        <v>981</v>
+      </c>
+      <c r="B56" t="s">
+        <v>981</v>
+      </c>
+      <c r="C56" t="s">
         <v>982</v>
-      </c>
-      <c r="B56" t="s">
-        <v>982</v>
-      </c>
-      <c r="C56" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B57" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1">
       <c r="A58" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B58" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B59" t="s">
         <v>1060</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B60" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
@@ -7332,10 +7332,10 @@
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B22" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1">
@@ -7548,50 +7548,50 @@
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B49" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B50" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B51" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B52" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B53" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B54" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8588,10 +8588,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B5" t="s">
         <v>1064</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8665,10 +8665,10 @@
         <v>653</v>
       </c>
       <c r="B13" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C13" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8700,7 +8700,7 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8727,10 +8727,10 @@
         <v>590</v>
       </c>
       <c r="B21" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C21" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8738,10 +8738,10 @@
         <v>598</v>
       </c>
       <c r="B22" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C22" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8760,10 +8760,10 @@
         <v>623</v>
       </c>
       <c r="B24" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C24" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8771,10 +8771,10 @@
         <v>625</v>
       </c>
       <c r="B25" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C25" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8782,10 +8782,10 @@
         <v>692</v>
       </c>
       <c r="B26" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C26" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8793,10 +8793,10 @@
         <v>826</v>
       </c>
       <c r="B27" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C27" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8804,7 +8804,7 @@
         <v>473</v>
       </c>
       <c r="B28" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8844,7 +8844,7 @@
         <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -8938,7 +8938,7 @@
         <v>488</v>
       </c>
       <c r="B45" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -8954,7 +8954,7 @@
         <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9034,10 +9034,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B58" t="s">
         <v>1039</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -9045,10 +9045,10 @@
         <v>595</v>
       </c>
       <c r="B59" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C59" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -9056,10 +9056,10 @@
         <v>487</v>
       </c>
       <c r="B60" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C60" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9141,7 +9141,7 @@
         <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -9184,7 +9184,7 @@
         <v>497</v>
       </c>
       <c r="B74" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -9200,26 +9200,26 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B76" t="s">
         <v>1090</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B77" t="s">
         <v>1083</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B78" t="s">
         <v>1092</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -9227,7 +9227,7 @@
         <v>486</v>
       </c>
       <c r="B79" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9267,10 +9267,10 @@
         <v>649</v>
       </c>
       <c r="B85" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C85" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -9311,7 +9311,7 @@
         <v>485</v>
       </c>
       <c r="B89" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9319,7 +9319,7 @@
         <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -9490,10 +9490,10 @@
         <v>849</v>
       </c>
       <c r="B109" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C109" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -9525,15 +9525,15 @@
         <v>484</v>
       </c>
       <c r="B113" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B115" t="s">
         <v>1135</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1136</v>
       </c>
       <c r="C115" t="s">
         <v>594</v>
@@ -9643,7 +9643,7 @@
         <v>483</v>
       </c>
       <c r="B125" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9710,10 +9710,10 @@
         <v>562</v>
       </c>
       <c r="B134" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C134" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -9740,7 +9740,7 @@
         <v>482</v>
       </c>
       <c r="B137" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -9759,7 +9759,7 @@
         <v>609</v>
       </c>
       <c r="B140" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C140" t="s">
         <v>608</v>
@@ -9810,10 +9810,10 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B147" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C147" t="s">
         <v>594</v>
@@ -9832,7 +9832,7 @@
         <v>481</v>
       </c>
       <c r="B149" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9872,7 +9872,7 @@
         <v>480</v>
       </c>
       <c r="B155" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -9967,21 +9967,21 @@
         <v>469</v>
       </c>
       <c r="B166" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C166" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B168" t="s">
         <v>768</v>
       </c>
       <c r="C168" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -9992,7 +9992,7 @@
         <v>829</v>
       </c>
       <c r="C169" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -10014,7 +10014,7 @@
         <v>830</v>
       </c>
       <c r="C171" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -10033,21 +10033,21 @@
         <v>701</v>
       </c>
       <c r="B173" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C173" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B174" t="s">
         <v>836</v>
       </c>
       <c r="C174" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -10055,18 +10055,18 @@
         <v>460</v>
       </c>
       <c r="B176" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B177" t="s">
         <v>1068</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
         <v>1069</v>
-      </c>
-      <c r="C177" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -10134,7 +10134,7 @@
         <v>836</v>
       </c>
       <c r="C184" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -10177,7 +10177,7 @@
         <v>836</v>
       </c>
       <c r="C189" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -10193,7 +10193,7 @@
         <v>586</v>
       </c>
       <c r="B191" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -10201,10 +10201,10 @@
         <v>599</v>
       </c>
       <c r="B192" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C192" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -10215,7 +10215,7 @@
         <v>663</v>
       </c>
       <c r="C193" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -10223,10 +10223,10 @@
         <v>674</v>
       </c>
       <c r="B194" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C194" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -10234,18 +10234,18 @@
         <v>848</v>
       </c>
       <c r="B195" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C195" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B196" t="s">
         <v>1097</v>
-      </c>
-      <c r="B196" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -10253,10 +10253,10 @@
         <v>468</v>
       </c>
       <c r="B197" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C197" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -10264,10 +10264,10 @@
         <v>673</v>
       </c>
       <c r="B199" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C199" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -10275,7 +10275,7 @@
         <v>461</v>
       </c>
       <c r="B200" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -10313,10 +10313,10 @@
         <v>246</v>
       </c>
       <c r="B204" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C204" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -10432,7 +10432,7 @@
         <v>836</v>
       </c>
       <c r="C217" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -10440,10 +10440,10 @@
         <v>273</v>
       </c>
       <c r="B218" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C218" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -10451,10 +10451,10 @@
         <v>600</v>
       </c>
       <c r="B219" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C219" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -10462,10 +10462,10 @@
         <v>597</v>
       </c>
       <c r="B220" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C220" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -10473,10 +10473,10 @@
         <v>479</v>
       </c>
       <c r="B221" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C221" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -10484,7 +10484,7 @@
         <v>462</v>
       </c>
       <c r="B223" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -10540,10 +10540,10 @@
         <v>601</v>
       </c>
       <c r="B230" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C230" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -10551,10 +10551,10 @@
         <v>478</v>
       </c>
       <c r="B231" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C231" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -10562,7 +10562,7 @@
         <v>463</v>
       </c>
       <c r="B233" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -10634,18 +10634,18 @@
         <v>602</v>
       </c>
       <c r="B242" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C242" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B243" t="s">
         <v>1145</v>
-      </c>
-      <c r="B243" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -10653,10 +10653,10 @@
         <v>477</v>
       </c>
       <c r="B244" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C244" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -10664,7 +10664,7 @@
         <v>464</v>
       </c>
       <c r="B246" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -10721,7 +10721,7 @@
         <v>836</v>
       </c>
       <c r="C252" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -10761,10 +10761,10 @@
         <v>603</v>
       </c>
       <c r="B257" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C257" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -10772,10 +10772,10 @@
         <v>476</v>
       </c>
       <c r="B258" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C258" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -10953,10 +10953,10 @@
         <v>475</v>
       </c>
       <c r="B279" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C279" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -11074,43 +11074,43 @@
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B294" t="s">
         <v>1041</v>
       </c>
-      <c r="B294" t="s">
+      <c r="C294" t="s">
         <v>1042</v>
-      </c>
-      <c r="C294" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B295" t="s">
         <v>1044</v>
       </c>
-      <c r="B295" t="s">
-        <v>1045</v>
-      </c>
       <c r="C295" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B296" t="s">
         <v>1046</v>
       </c>
-      <c r="B296" t="s">
-        <v>1047</v>
-      </c>
       <c r="C296" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B297" t="s">
         <v>1104</v>
-      </c>
-      <c r="B297" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -11118,10 +11118,10 @@
         <v>474</v>
       </c>
       <c r="B298" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C298" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -11137,35 +11137,35 @@
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B301" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C301" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B302" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C302" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B303" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C303" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -11297,18 +11297,18 @@
         <v>688</v>
       </c>
       <c r="B319" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C319" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B320" t="s">
         <v>1062</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -11316,18 +11316,18 @@
         <v>549</v>
       </c>
       <c r="B321" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C321" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B322" t="s">
         <v>1106</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -11335,10 +11335,10 @@
         <v>472</v>
       </c>
       <c r="B323" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C323" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -11459,18 +11459,18 @@
         <v>555</v>
       </c>
       <c r="B338" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C338" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B339" t="s">
         <v>1108</v>
-      </c>
-      <c r="B339" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -11478,10 +11478,10 @@
         <v>471</v>
       </c>
       <c r="B340" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C340" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -11548,13 +11548,13 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B349" t="s">
         <v>1076</v>
       </c>
-      <c r="B349" t="s">
-        <v>1077</v>
-      </c>
       <c r="C349" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -11562,10 +11562,10 @@
         <v>470</v>
       </c>
       <c r="B350" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C350" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -11584,10 +11584,10 @@
         <v>698</v>
       </c>
       <c r="B353" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C353" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -11659,7 +11659,7 @@
         <v>720</v>
       </c>
       <c r="B363" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -11667,10 +11667,10 @@
         <v>721</v>
       </c>
       <c r="B364" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C364" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -11723,10 +11723,10 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B371" t="s">
         <v>1072</v>
-      </c>
-      <c r="B371" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -11739,21 +11739,21 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B373" t="s">
         <v>1112</v>
-      </c>
-      <c r="B373" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B374" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C374" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -11849,10 +11849,10 @@
         <v>757</v>
       </c>
       <c r="B387" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C387" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11884,7 +11884,7 @@
         <v>762</v>
       </c>
       <c r="B392" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -11932,10 +11932,10 @@
         <v>780</v>
       </c>
       <c r="B399" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C399" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11983,10 +11983,10 @@
         <v>791</v>
       </c>
       <c r="B406" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C406" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -12002,7 +12002,7 @@
         <v>801</v>
       </c>
       <c r="B409" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -12010,10 +12010,10 @@
         <v>802</v>
       </c>
       <c r="B410" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C410" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -12021,7 +12021,7 @@
         <v>804</v>
       </c>
       <c r="B411" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -12029,10 +12029,10 @@
         <v>810</v>
       </c>
       <c r="B412" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C412" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -12040,7 +12040,7 @@
         <v>811</v>
       </c>
       <c r="B413" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -12048,7 +12048,7 @@
         <v>812</v>
       </c>
       <c r="B414" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -12056,7 +12056,7 @@
         <v>815</v>
       </c>
       <c r="B415" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -12064,7 +12064,7 @@
         <v>816</v>
       </c>
       <c r="B416" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -12072,7 +12072,7 @@
         <v>817</v>
       </c>
       <c r="B417" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -12080,7 +12080,7 @@
         <v>818</v>
       </c>
       <c r="B418" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -12088,7 +12088,7 @@
         <v>819</v>
       </c>
       <c r="B419" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -12104,7 +12104,7 @@
         <v>821</v>
       </c>
       <c r="B421" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -12112,10 +12112,10 @@
         <v>822</v>
       </c>
       <c r="B422" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C422" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -12123,10 +12123,10 @@
         <v>823</v>
       </c>
       <c r="B423" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C423" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -12134,10 +12134,10 @@
         <v>814</v>
       </c>
       <c r="B424" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C424" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -12145,93 +12145,93 @@
         <v>813</v>
       </c>
       <c r="B425" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C425" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B426" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
+        <v>996</v>
+      </c>
+      <c r="B427" t="s">
         <v>997</v>
-      </c>
-      <c r="B427" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
+        <v>998</v>
+      </c>
+      <c r="B428" t="s">
         <v>999</v>
-      </c>
-      <c r="B428" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B429" t="s">
         <v>1001</v>
-      </c>
-      <c r="B429" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B430" t="s">
         <v>1003</v>
-      </c>
-      <c r="B430" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B431" t="s">
         <v>1005</v>
-      </c>
-      <c r="B431" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B432" t="s">
         <v>1007</v>
-      </c>
-      <c r="B432" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B433" t="s">
         <v>1009</v>
-      </c>
-      <c r="B433" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B434" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C434" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B435" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -12359,10 +12359,10 @@
         <v>890</v>
       </c>
       <c r="B452" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C452" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -12399,10 +12399,10 @@
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B457" t="s">
         <v>1117</v>
-      </c>
-      <c r="B457" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -12410,18 +12410,18 @@
         <v>899</v>
       </c>
       <c r="B458" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C458" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B460" t="s">
         <v>1078</v>
-      </c>
-      <c r="B460" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -12461,7 +12461,7 @@
         <v>908</v>
       </c>
       <c r="B465" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -12469,7 +12469,7 @@
         <v>909</v>
       </c>
       <c r="B466" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -12477,7 +12477,7 @@
         <v>910</v>
       </c>
       <c r="B467" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -12485,7 +12485,7 @@
         <v>911</v>
       </c>
       <c r="B468" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -12493,15 +12493,15 @@
         <v>912</v>
       </c>
       <c r="B469" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B470" t="s">
         <v>1124</v>
-      </c>
-      <c r="B470" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -12509,10 +12509,10 @@
         <v>913</v>
       </c>
       <c r="B471" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C471" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -12520,10 +12520,10 @@
         <v>920</v>
       </c>
       <c r="B473" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C473" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -12531,10 +12531,10 @@
         <v>921</v>
       </c>
       <c r="B474" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C474" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -12545,7 +12545,7 @@
         <v>923</v>
       </c>
       <c r="C476" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12553,10 +12553,10 @@
         <v>924</v>
       </c>
       <c r="B477" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C477" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12577,10 +12577,10 @@
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B481" t="s">
         <v>1126</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -12588,10 +12588,10 @@
         <v>929</v>
       </c>
       <c r="B482" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C482" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12599,321 +12599,321 @@
         <v>930</v>
       </c>
       <c r="B484" t="s">
-        <v>931</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
+        <v>931</v>
+      </c>
+      <c r="B485" t="s">
         <v>932</v>
-      </c>
-      <c r="B485" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
+        <v>933</v>
+      </c>
+      <c r="B486" t="s">
         <v>934</v>
-      </c>
-      <c r="B486" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
+        <v>935</v>
+      </c>
+      <c r="B487" t="s">
         <v>936</v>
-      </c>
-      <c r="B487" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
+        <v>937</v>
+      </c>
+      <c r="B488" t="s">
         <v>938</v>
-      </c>
-      <c r="B488" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
+        <v>939</v>
+      </c>
+      <c r="B489" t="s">
         <v>940</v>
-      </c>
-      <c r="B489" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B490" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C490" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" t="s">
+        <v>942</v>
+      </c>
+      <c r="B492" t="s">
         <v>943</v>
-      </c>
-      <c r="B492" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="493" spans="1:3">
       <c r="A493" t="s">
+        <v>944</v>
+      </c>
+      <c r="B493" t="s">
         <v>945</v>
-      </c>
-      <c r="B493" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
+        <v>946</v>
+      </c>
+      <c r="B494" t="s">
         <v>947</v>
-      </c>
-      <c r="B494" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
+        <v>948</v>
+      </c>
+      <c r="B495" t="s">
         <v>949</v>
-      </c>
-      <c r="B495" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
+        <v>950</v>
+      </c>
+      <c r="B496" t="s">
         <v>951</v>
-      </c>
-      <c r="B496" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B497" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C497" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499" t="s">
+        <v>953</v>
+      </c>
+      <c r="B499" t="s">
         <v>954</v>
-      </c>
-      <c r="B499" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="500" spans="1:3">
       <c r="A500" t="s">
+        <v>955</v>
+      </c>
+      <c r="B500" t="s">
         <v>956</v>
-      </c>
-      <c r="B500" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
+        <v>957</v>
+      </c>
+      <c r="B501" t="s">
         <v>958</v>
-      </c>
-      <c r="B501" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
+        <v>959</v>
+      </c>
+      <c r="B502" t="s">
         <v>960</v>
-      </c>
-      <c r="B502" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
+        <v>961</v>
+      </c>
+      <c r="B503" t="s">
         <v>962</v>
-      </c>
-      <c r="B503" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B504" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C504" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="506" spans="1:3">
       <c r="A506" t="s">
+        <v>964</v>
+      </c>
+      <c r="B506" t="s">
         <v>965</v>
       </c>
-      <c r="B506" t="s">
-        <v>966</v>
-      </c>
       <c r="C506" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="507" spans="1:3">
       <c r="A507" t="s">
+        <v>966</v>
+      </c>
+      <c r="B507" t="s">
         <v>967</v>
-      </c>
-      <c r="B507" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
+        <v>968</v>
+      </c>
+      <c r="B508" t="s">
         <v>969</v>
-      </c>
-      <c r="B508" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
+        <v>970</v>
+      </c>
+      <c r="B509" t="s">
         <v>971</v>
-      </c>
-      <c r="B509" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B510" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C510" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B512" t="s">
         <v>1012</v>
-      </c>
-      <c r="B512" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B513" t="s">
         <v>1014</v>
-      </c>
-      <c r="B513" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B514" t="s">
         <v>1016</v>
-      </c>
-      <c r="B514" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B515" t="s">
         <v>1018</v>
-      </c>
-      <c r="B515" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B516" t="s">
         <v>1020</v>
-      </c>
-      <c r="B516" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B517" t="s">
         <v>1022</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B518" t="s">
         <v>1024</v>
-      </c>
-      <c r="B518" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B519" t="s">
         <v>1026</v>
-      </c>
-      <c r="B519" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B520" t="s">
         <v>1028</v>
-      </c>
-      <c r="B520" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B521" t="s">
         <v>1030</v>
-      </c>
-      <c r="B521" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B522" t="s">
         <v>1032</v>
-      </c>
-      <c r="B522" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B523" t="s">
         <v>1034</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B524" t="s">
         <v>1036</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B525" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C525" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B501D39-4394-4090-9102-6ACE98159B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B0A448-0804-48DE-ADD4-44ED023E2214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="1205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="1207">
   <si>
     <t>Name</t>
   </si>
@@ -978,9 +978,6 @@
     <t>Name listed on the Self-Employment Certification and Profit/Lost Statement do not match.</t>
   </si>
   <si>
-    <t>Net Income displayed on the Profit/Loss Statement doe not match the calculated Net Income.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amount listed on the Self-Employment Certification and Profit/Loss Statement do not line up as expected. Needs additional review. </t>
   </si>
   <si>
@@ -1533,9 +1530,6 @@
     <t xml:space="preserve">Profit Loss forms does not exist for Self-Employment Verification </t>
   </si>
   <si>
-    <t xml:space="preserve">1040, Schedulec forms does not exist for Self-Employment Verification </t>
-  </si>
-  <si>
     <t>IAQ_AssetsValueMatch</t>
   </si>
   <si>
@@ -1713,21 +1707,6 @@
     <t>SSIB_OverPayment</t>
   </si>
   <si>
-    <t xml:space="preserve">Name listed on the Verification of Reccurring Cash Contribution and ICW do not match. </t>
-  </si>
-  <si>
-    <t>Date listed on the Verification of Reccurring Cash Contribution is over 120 days in the past.</t>
-  </si>
-  <si>
-    <t>Date listed on the Verification of Reccurring Cash Contribution is not with in 120 days of Move-In date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification of Reccurring Cash Contribution has not been signed. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification of Reccurring Cash Contribution has not been dated appropriately. </t>
-  </si>
-  <si>
     <t>LLM_ImageQuality</t>
   </si>
   <si>
@@ -1794,9 +1773,6 @@
     <t>ICW check was removed from this check</t>
   </si>
   <si>
-    <t xml:space="preserve">Contributor and Amount listed on the Verification of Reccurring Cash Contribution and ICW do not match. </t>
-  </si>
-  <si>
     <t>EDC_hourly_and_paycheck</t>
   </si>
   <si>
@@ -2166,9 +2142,6 @@
     <t>CSEI_SupportingDocsExist</t>
   </si>
   <si>
-    <t>Supporting documents do not exist for the Certification of Self-Employmet Income.</t>
-  </si>
-  <si>
     <t>CSEI_MemName</t>
   </si>
   <si>
@@ -3603,9 +3576,6 @@
     <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
   </si>
   <si>
-    <t>Unable to validate Verification of Reccurring Cash Contribution. Manual review is needed.</t>
-  </si>
-  <si>
     <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
   </si>
   <si>
@@ -3658,6 +3628,42 @@
   </si>
   <si>
     <t xml:space="preserve">The Release and Consent Form is missing from the application. </t>
+  </si>
+  <si>
+    <t>SE_003</t>
+  </si>
+  <si>
+    <t>Assign button cannot be found in Yardi.</t>
+  </si>
+  <si>
+    <t>ManagerName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1040, Schedule C forms does not exist for Self-Employment Verification </t>
+  </si>
+  <si>
+    <t>Supporting documents do not exist for the Certification of Self-Employment Income.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name listed on the Verification of Recurring Cash Contribution and ICW do not match. </t>
+  </si>
+  <si>
+    <t>Date listed on the Verification of Recurring Cash Contribution is over 120 days in the past.</t>
+  </si>
+  <si>
+    <t>Date listed on the Verification of Recurring Cash Contribution is not with in 120 days of Move-In date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contributor and Amount listed on the Verification of Recurring Cash Contribution and ICW do not match. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification of Recurring Cash Contribution has not been signed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification of Recurring Cash Contribution has not been dated appropriately. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Recurring Cash Contribution. Manual review is needed.</t>
   </si>
 </sst>
 </file>
@@ -4093,7 +4099,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1130</v>
+        <v>1121</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -4114,7 +4120,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -4126,7 +4132,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1129</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -4156,10 +4162,10 @@
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
       <c r="B12" t="s">
-        <v>1073</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -4167,7 +4173,7 @@
         <v>208</v>
       </c>
       <c r="B13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
@@ -4180,10 +4186,10 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="B15" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
@@ -4191,7 +4197,7 @@
         <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
@@ -4199,7 +4205,7 @@
         <v>211</v>
       </c>
       <c r="B17" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
@@ -4207,7 +4213,7 @@
         <v>212</v>
       </c>
       <c r="B18" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C18" t="s">
         <v>227</v>
@@ -4229,7 +4235,7 @@
         <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C20" t="s">
         <v>229</v>
@@ -4240,7 +4246,7 @@
         <v>215</v>
       </c>
       <c r="B21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C21" t="s">
         <v>230</v>
@@ -4251,7 +4257,7 @@
         <v>216</v>
       </c>
       <c r="B22" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
@@ -4259,7 +4265,7 @@
         <v>217</v>
       </c>
       <c r="B23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
@@ -4267,7 +4273,7 @@
         <v>218</v>
       </c>
       <c r="B24" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
@@ -4275,12 +4281,12 @@
         <v>219</v>
       </c>
       <c r="B25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B26" t="s">
         <v>228</v>
@@ -4291,7 +4297,7 @@
         <v>232</v>
       </c>
       <c r="B27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
@@ -4331,10 +4337,10 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1">
@@ -4347,221 +4353,221 @@
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
+        <v>329</v>
+      </c>
+      <c r="B34" t="s">
         <v>330</v>
-      </c>
-      <c r="B34" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1">
       <c r="A35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B36" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1">
       <c r="A37" t="s">
+        <v>356</v>
+      </c>
+      <c r="B37" t="s">
         <v>357</v>
-      </c>
-      <c r="B37" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1">
       <c r="A38" t="s">
+        <v>404</v>
+      </c>
+      <c r="B38" t="s">
         <v>405</v>
-      </c>
-      <c r="B38" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B39" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
+        <v>354</v>
+      </c>
+      <c r="B40" t="s">
         <v>355</v>
-      </c>
-      <c r="B40" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
       <c r="A41" t="s">
+        <v>407</v>
+      </c>
+      <c r="B41" t="s">
         <v>408</v>
-      </c>
-      <c r="B41" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B43" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="B44" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="B45" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="B46" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="B47" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="B48" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="B49" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="B50" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="B51" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
       <c r="B52" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="B53" t="s">
-        <v>976</v>
+        <v>967</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>977</v>
+        <v>968</v>
       </c>
       <c r="B54" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1">
       <c r="A55" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
       <c r="B55" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="B56" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="C56" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="B57" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1">
       <c r="A58" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="B58" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
       <c r="B59" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="B60" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
@@ -5527,10 +5533,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B1" t="s">
         <v>420</v>
-      </c>
-      <c r="B1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5538,15 +5544,15 @@
         <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5554,15 +5560,15 @@
         <v>226</v>
       </c>
       <c r="B4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5570,15 +5576,15 @@
         <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5586,15 +5592,15 @@
         <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5602,15 +5608,15 @@
         <v>223</v>
       </c>
       <c r="B10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>426</v>
+      </c>
+      <c r="B11" t="s">
         <v>427</v>
-      </c>
-      <c r="B11" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5626,47 +5632,47 @@
         <v>221</v>
       </c>
       <c r="B13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>429</v>
+      </c>
+      <c r="B16" t="s">
         <v>430</v>
-      </c>
-      <c r="B16" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B18" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5674,7 +5680,7 @@
         <v>230</v>
       </c>
       <c r="B19" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5682,23 +5688,23 @@
         <v>227</v>
       </c>
       <c r="B20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
+        <v>434</v>
+      </c>
+      <c r="B22" t="s">
         <v>435</v>
-      </c>
-      <c r="B22" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5706,7 +5712,7 @@
         <v>228</v>
       </c>
       <c r="B23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5714,23 +5720,23 @@
         <v>229</v>
       </c>
       <c r="B24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B26" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -5738,7 +5744,7 @@
         <v>266</v>
       </c>
       <c r="B27" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -5746,7 +5752,7 @@
         <v>278</v>
       </c>
       <c r="B28" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -5754,15 +5760,15 @@
         <v>289</v>
       </c>
       <c r="B29" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5770,95 +5776,95 @@
         <v>1040</v>
       </c>
       <c r="B31" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B34" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B36" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B37" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B38" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B39" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B40" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B41" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="B42" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -6058,10 +6064,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="B20" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
@@ -6069,23 +6075,23 @@
         <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B22" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B23" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
@@ -6154,7 +6160,14 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A34" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1196</v>
+      </c>
+    </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="36" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
@@ -7180,10 +7193,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="B3" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -7260,90 +7273,90 @@
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B13" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B15" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B16" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B17" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B18" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B19" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B20" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="B22" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B23" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
@@ -7404,197 +7417,204 @@
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B31" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B32" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B34" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B35" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B36" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B37" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1">
       <c r="A38" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B38" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="B39" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="B40" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25" customHeight="1">
       <c r="A41" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="B41" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="B42" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B43" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="B44" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="B45" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B46" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.25" customHeight="1">
       <c r="A47" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="B47" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="B48" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="B49" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="B50" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>1128</v>
+        <v>1119</v>
       </c>
       <c r="B51" t="s">
-        <v>1128</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1131</v>
+        <v>1122</v>
       </c>
       <c r="B52" t="s">
-        <v>1131</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1132</v>
+        <v>1123</v>
       </c>
       <c r="B53" t="s">
-        <v>1132</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1133</v>
+        <v>1124</v>
       </c>
       <c r="B54" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A55" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1197</v>
+      </c>
+    </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="57" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8588,87 +8608,87 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1063</v>
+        <v>1054</v>
       </c>
       <c r="B5" t="s">
-        <v>1064</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B7" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C7" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="B8" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C8" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="B9" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="C9" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="B10" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="C10" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="B11" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="C11" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="B12" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="C12" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="B13" t="s">
-        <v>1152</v>
+        <v>1143</v>
       </c>
       <c r="C13" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8676,7 +8696,7 @@
         <v>174</v>
       </c>
       <c r="B15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -8700,7 +8720,7 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>1084</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8711,100 +8731,100 @@
         <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>490</v>
+      </c>
+      <c r="B20" t="s">
         <v>491</v>
-      </c>
-      <c r="B20" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B21" t="s">
-        <v>1137</v>
+        <v>1128</v>
       </c>
       <c r="C21" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B22" t="s">
-        <v>1153</v>
+        <v>1144</v>
       </c>
       <c r="C22" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B23" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C23" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="B24" t="s">
-        <v>1154</v>
+        <v>1145</v>
       </c>
       <c r="C24" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B25" t="s">
-        <v>1155</v>
+        <v>1146</v>
       </c>
       <c r="C25" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="B26" t="s">
-        <v>1138</v>
+        <v>1129</v>
       </c>
       <c r="C26" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="B27" t="s">
-        <v>1156</v>
+        <v>1147</v>
       </c>
       <c r="C27" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B28" t="s">
-        <v>1157</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8825,10 +8845,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B32" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8844,7 +8864,7 @@
         <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>1085</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -8852,7 +8872,7 @@
         <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -8860,7 +8880,7 @@
         <v>190</v>
       </c>
       <c r="B36" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -8897,48 +8917,48 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B41" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B42" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B43" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C43" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="B44" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="C44" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B45" t="s">
-        <v>1158</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -8954,7 +8974,7 @@
         <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>1086</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9005,7 +9025,7 @@
         <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -9018,48 +9038,48 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="B56" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="B57" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="B58" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B59" t="s">
-        <v>1159</v>
+        <v>1150</v>
       </c>
       <c r="C59" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s">
-        <v>1160</v>
+        <v>1151</v>
       </c>
       <c r="C60" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9067,7 +9087,7 @@
         <v>178</v>
       </c>
       <c r="B62" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -9078,7 +9098,7 @@
         <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -9089,7 +9109,7 @@
         <v>112</v>
       </c>
       <c r="C64" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -9100,7 +9120,7 @@
         <v>114</v>
       </c>
       <c r="C65" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -9111,7 +9131,7 @@
         <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -9122,7 +9142,7 @@
         <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -9133,7 +9153,7 @@
         <v>106</v>
       </c>
       <c r="C68" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -9141,7 +9161,7 @@
         <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>1087</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -9149,7 +9169,7 @@
         <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -9157,77 +9177,77 @@
         <v>196</v>
       </c>
       <c r="B71" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C71" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B72" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>488</v>
+      </c>
+      <c r="B73" t="s">
         <v>489</v>
-      </c>
-      <c r="B73" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B74" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B75" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="C75" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>1089</v>
+        <v>1080</v>
       </c>
       <c r="B76" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>1082</v>
+        <v>1073</v>
       </c>
       <c r="B77" t="s">
-        <v>1083</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="B78" t="s">
-        <v>1092</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B79" t="s">
-        <v>1161</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9243,7 +9263,7 @@
         <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -9256,62 +9276,62 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B84" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="B85" t="s">
-        <v>1139</v>
+        <v>1130</v>
       </c>
       <c r="C85" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="B86" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="C86" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="B87" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C87" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="B88" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="C88" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B89" t="s">
-        <v>1162</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -9319,29 +9339,29 @@
         <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="B92" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="C92" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="B93" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="C93" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -9365,7 +9385,7 @@
         <v>132</v>
       </c>
       <c r="B96" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -9373,7 +9393,7 @@
         <v>133</v>
       </c>
       <c r="B97" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -9381,7 +9401,7 @@
         <v>134</v>
       </c>
       <c r="B98" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -9389,7 +9409,7 @@
         <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -9397,10 +9417,10 @@
         <v>136</v>
       </c>
       <c r="B100" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C100" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -9408,10 +9428,10 @@
         <v>137</v>
       </c>
       <c r="B101" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C101" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -9419,124 +9439,124 @@
         <v>138</v>
       </c>
       <c r="B102" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C102" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B104" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C104" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="B105" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="B106" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="C106" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="B107" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="C107" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="B108" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="C108" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="B109" t="s">
-        <v>1140</v>
+        <v>1131</v>
       </c>
       <c r="C109" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="B110" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="B111" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="B112" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B113" t="s">
-        <v>1163</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>1134</v>
+        <v>1125</v>
       </c>
       <c r="B115" t="s">
-        <v>1135</v>
+        <v>1126</v>
       </c>
       <c r="C115" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -9547,7 +9567,7 @@
         <v>144</v>
       </c>
       <c r="C116" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -9558,7 +9578,7 @@
         <v>145</v>
       </c>
       <c r="C117" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -9569,7 +9589,7 @@
         <v>146</v>
       </c>
       <c r="C118" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -9577,21 +9597,21 @@
         <v>139</v>
       </c>
       <c r="B119" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C119" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B120" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C120" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -9602,7 +9622,7 @@
         <v>123</v>
       </c>
       <c r="C121" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -9610,10 +9630,10 @@
         <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C122" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -9624,26 +9644,26 @@
         <v>124</v>
       </c>
       <c r="C123" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="B124" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C124" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B125" t="s">
-        <v>1164</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9680,13 +9700,13 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="B131" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="C131" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -9707,62 +9727,62 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B134" t="s">
-        <v>1165</v>
+        <v>1156</v>
       </c>
       <c r="C134" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B135" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="B136" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="C136" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B137" t="s">
-        <v>1166</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B139" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="C139" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B140" t="s">
-        <v>1167</v>
+        <v>1158</v>
       </c>
       <c r="C140" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -9794,45 +9814,45 @@
         <v>156</v>
       </c>
       <c r="B145" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B146" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="C146" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="B147" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="C147" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B148" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B149" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -9861,29 +9881,29 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="B154" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B155" t="s">
-        <v>1169</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B156" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C156" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -9902,7 +9922,7 @@
         <v>166</v>
       </c>
       <c r="C159" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -9913,7 +9933,7 @@
         <v>167</v>
       </c>
       <c r="C160" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -9924,7 +9944,7 @@
         <v>168</v>
       </c>
       <c r="C161" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -9951,122 +9971,122 @@
         <v>171</v>
       </c>
       <c r="C164" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="B165" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B166" t="s">
-        <v>1170</v>
+        <v>1161</v>
       </c>
       <c r="C166" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>1080</v>
+        <v>1071</v>
       </c>
       <c r="B168" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="C168" t="s">
-        <v>1081</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="B169" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="C169" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="B170" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C170" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="B171" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="C171" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="B172" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="C172" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B173" t="s">
-        <v>1154</v>
+        <v>1145</v>
       </c>
       <c r="C173" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
       <c r="B174" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="C174" t="s">
-        <v>1093</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B176" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
       <c r="B177" t="s">
-        <v>1068</v>
+        <v>1059</v>
       </c>
       <c r="C177" t="s">
-        <v>1069</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -10074,10 +10094,10 @@
         <v>233</v>
       </c>
       <c r="B178" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="C178" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -10085,7 +10105,7 @@
         <v>234</v>
       </c>
       <c r="B179" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -10093,21 +10113,21 @@
         <v>242</v>
       </c>
       <c r="B180" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="C180" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="B181" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="C181" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -10120,10 +10140,10 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B183" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -10131,10 +10151,10 @@
         <v>237</v>
       </c>
       <c r="B184" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="C184" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -10142,7 +10162,7 @@
         <v>238</v>
       </c>
       <c r="B185" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -10150,7 +10170,7 @@
         <v>239</v>
       </c>
       <c r="B186" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -10158,7 +10178,7 @@
         <v>240</v>
       </c>
       <c r="B187" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -10166,7 +10186,7 @@
         <v>241</v>
       </c>
       <c r="B188" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -10174,10 +10194,10 @@
         <v>272</v>
       </c>
       <c r="B189" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="C189" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -10190,92 +10210,92 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B191" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B192" t="s">
-        <v>1142</v>
+        <v>1133</v>
       </c>
       <c r="C192" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="B193" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="C193" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="B194" t="s">
-        <v>1171</v>
+        <v>1162</v>
       </c>
       <c r="C194" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="B195" t="s">
-        <v>1143</v>
+        <v>1134</v>
       </c>
       <c r="C195" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>1096</v>
+        <v>1087</v>
       </c>
       <c r="B196" t="s">
-        <v>1097</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B197" t="s">
-        <v>1172</v>
+        <v>1163</v>
       </c>
       <c r="C197" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="B199" t="s">
-        <v>1173</v>
+        <v>1164</v>
       </c>
       <c r="C199" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B200" t="s">
-        <v>1098</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -10283,10 +10303,10 @@
         <v>243</v>
       </c>
       <c r="B201" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="C201" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.5" customHeight="1">
@@ -10294,10 +10314,10 @@
         <v>245</v>
       </c>
       <c r="B202" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="C202" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -10305,7 +10325,7 @@
         <v>244</v>
       </c>
       <c r="B203" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -10313,10 +10333,10 @@
         <v>246</v>
       </c>
       <c r="B204" t="s">
-        <v>1174</v>
+        <v>1165</v>
       </c>
       <c r="C204" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -10335,15 +10355,15 @@
         <v>249</v>
       </c>
       <c r="C206" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B207" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -10351,7 +10371,7 @@
         <v>251</v>
       </c>
       <c r="B208" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -10367,7 +10387,7 @@
         <v>257</v>
       </c>
       <c r="B210" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -10375,7 +10395,7 @@
         <v>258</v>
       </c>
       <c r="B211" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -10383,10 +10403,10 @@
         <v>259</v>
       </c>
       <c r="B212" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="C212" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -10394,7 +10414,7 @@
         <v>260</v>
       </c>
       <c r="B213" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -10402,10 +10422,10 @@
         <v>261</v>
       </c>
       <c r="B214" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="C214" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -10413,7 +10433,7 @@
         <v>262</v>
       </c>
       <c r="B215" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -10429,10 +10449,10 @@
         <v>271</v>
       </c>
       <c r="B217" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="C217" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -10440,59 +10460,59 @@
         <v>273</v>
       </c>
       <c r="B218" t="s">
-        <v>1175</v>
+        <v>1166</v>
       </c>
       <c r="C218" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B219" t="s">
-        <v>1142</v>
+        <v>1133</v>
       </c>
       <c r="C219" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="B220" t="s">
-        <v>1176</v>
+        <v>1167</v>
       </c>
       <c r="C220" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B221" t="s">
-        <v>1177</v>
+        <v>1168</v>
       </c>
       <c r="C221" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B223" t="s">
-        <v>1099</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B224" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -10500,7 +10520,7 @@
         <v>267</v>
       </c>
       <c r="B225" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -10508,7 +10528,7 @@
         <v>268</v>
       </c>
       <c r="B226" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -10516,7 +10536,7 @@
         <v>275</v>
       </c>
       <c r="B227" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -10524,7 +10544,7 @@
         <v>274</v>
       </c>
       <c r="B228" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -10532,45 +10552,45 @@
         <v>276</v>
       </c>
       <c r="B229" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B230" t="s">
-        <v>1142</v>
+        <v>1133</v>
       </c>
       <c r="C230" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B231" t="s">
-        <v>1178</v>
+        <v>1169</v>
       </c>
       <c r="C231" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B233" t="s">
-        <v>1100</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B234" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -10578,7 +10598,7 @@
         <v>279</v>
       </c>
       <c r="B235" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -10594,7 +10614,7 @@
         <v>281</v>
       </c>
       <c r="B237" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -10602,7 +10622,7 @@
         <v>283</v>
       </c>
       <c r="B238" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -10610,7 +10630,7 @@
         <v>284</v>
       </c>
       <c r="B239" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -10618,7 +10638,7 @@
         <v>285</v>
       </c>
       <c r="B240" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -10626,64 +10646,64 @@
         <v>286</v>
       </c>
       <c r="B241" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="B242" t="s">
-        <v>1142</v>
+        <v>1133</v>
       </c>
       <c r="C242" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>1144</v>
+        <v>1135</v>
       </c>
       <c r="B243" t="s">
-        <v>1145</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B244" t="s">
-        <v>1179</v>
+        <v>1170</v>
       </c>
       <c r="C244" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B246" t="s">
-        <v>1101</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B247" t="s">
         <v>292</v>
       </c>
       <c r="C247" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B248" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -10691,10 +10711,10 @@
         <v>290</v>
       </c>
       <c r="B249" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="C249" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -10702,15 +10722,15 @@
         <v>291</v>
       </c>
       <c r="B250" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B251" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -10718,10 +10738,10 @@
         <v>293</v>
       </c>
       <c r="B252" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="C252" t="s">
-        <v>1102</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -10729,7 +10749,7 @@
         <v>294</v>
       </c>
       <c r="B253" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -10737,7 +10757,7 @@
         <v>295</v>
       </c>
       <c r="B254" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -10745,7 +10765,7 @@
         <v>296</v>
       </c>
       <c r="B255" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -10753,75 +10773,75 @@
         <v>297</v>
       </c>
       <c r="B256" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B257" t="s">
-        <v>1142</v>
+        <v>1133</v>
       </c>
       <c r="C257" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B258" t="s">
-        <v>1180</v>
+        <v>1171</v>
       </c>
       <c r="C258" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="B260" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C260" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B261" t="s">
-        <v>496</v>
+        <v>1198</v>
       </c>
       <c r="C261" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
+        <v>493</v>
+      </c>
+      <c r="B262" t="s">
         <v>494</v>
       </c>
-      <c r="B262" t="s">
-        <v>495</v>
-      </c>
       <c r="C262" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B263" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B264" t="s">
         <v>300</v>
@@ -10829,26 +10849,26 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B265" t="s">
         <v>301</v>
       </c>
       <c r="C265" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B266" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B267" t="s">
         <v>302</v>
@@ -10856,7 +10876,7 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B268" t="s">
         <v>303</v>
@@ -10864,7 +10884,7 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B269" t="s">
         <v>304</v>
@@ -10872,18 +10892,18 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B270" t="s">
         <v>305</v>
       </c>
       <c r="C270" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B271" t="s">
         <v>306</v>
@@ -10891,7 +10911,7 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B272" t="s">
         <v>307</v>
@@ -10899,7 +10919,7 @@
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B273" t="s">
         <v>308</v>
@@ -10907,7 +10927,7 @@
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B274" t="s">
         <v>309</v>
@@ -10915,949 +10935,949 @@
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B275" t="s">
         <v>310</v>
       </c>
       <c r="C275" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B276" t="s">
-        <v>311</v>
+        <v>738</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B277" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B278" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B279" t="s">
-        <v>1181</v>
+        <v>1172</v>
       </c>
       <c r="C279" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B281" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B282" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B283" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B284" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C284" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B285" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B286" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C286" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B287" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B288" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C288" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B289" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B290" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B291" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B292" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B293" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="B294" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="C294" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="B295" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="C295" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="B296" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="C296" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1103</v>
+        <v>1094</v>
       </c>
       <c r="B297" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B298" t="s">
-        <v>1182</v>
+        <v>1173</v>
       </c>
       <c r="C298" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="B300" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="C300" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="B301" t="s">
-        <v>1146</v>
+        <v>1137</v>
       </c>
       <c r="C301" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="B302" t="s">
-        <v>1147</v>
+        <v>1138</v>
       </c>
       <c r="C302" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="B303" t="s">
-        <v>1183</v>
+        <v>1174</v>
       </c>
       <c r="C303" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B305" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="C305" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
+        <v>464</v>
+      </c>
+      <c r="B306" t="s">
         <v>465</v>
-      </c>
-      <c r="B306" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B307" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B308" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C308" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B309" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B310" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C310" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B311" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C311" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B312" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B313" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B314" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B315" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B316" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B317" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B318" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="B319" t="s">
-        <v>1148</v>
+        <v>1139</v>
       </c>
       <c r="C319" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="B320" t="s">
-        <v>1062</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B321" t="s">
-        <v>1184</v>
+        <v>1175</v>
       </c>
       <c r="C321" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="B322" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B323" t="s">
-        <v>1185</v>
+        <v>1176</v>
       </c>
       <c r="C323" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B325" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B326" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B327" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C327" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B328" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B329" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C329" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B330" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C330" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B331" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B332" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B333" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B334" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B335" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B336" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B337" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B338" t="s">
-        <v>1184</v>
+        <v>1175</v>
       </c>
       <c r="C338" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="B339" t="s">
-        <v>1108</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B340" t="s">
-        <v>1185</v>
+        <v>1176</v>
       </c>
       <c r="C340" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B342" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="C342" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B343" t="s">
-        <v>556</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B344" t="s">
-        <v>557</v>
+        <v>1201</v>
       </c>
       <c r="C344" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B345" t="s">
-        <v>558</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B346" t="s">
-        <v>583</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B347" t="s">
-        <v>559</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B348" t="s">
-        <v>560</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
       <c r="B349" t="s">
-        <v>1076</v>
+        <v>1067</v>
       </c>
       <c r="C349" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B350" t="s">
-        <v>1186</v>
+        <v>1206</v>
       </c>
       <c r="C350" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B352" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="C352" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B353" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
       <c r="C353" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="B355" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="B356" t="s">
-        <v>707</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="B357" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="B358" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="B359" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="B360" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="B361" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="B362" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="B363" t="s">
-        <v>1110</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="B364" t="s">
-        <v>1188</v>
+        <v>1178</v>
       </c>
       <c r="C364" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="B365" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="B366" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="B367" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="B368" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="B369" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="B370" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
       <c r="B371" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="B372" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>1111</v>
+        <v>1102</v>
       </c>
       <c r="B373" t="s">
-        <v>1112</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="B374" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
       <c r="C374" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="B376" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="B377" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="B378" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="B379" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="B380" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="B381" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="B382" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="B383" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="B384" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="B385" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="B386" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="B387" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="C387" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="B389" t="s">
         <v>306</v>
@@ -11865,15 +11885,15 @@
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="B390" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="B391" t="s">
         <v>308</v>
@@ -11881,1039 +11901,1039 @@
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="B392" t="s">
-        <v>1113</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="B394" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="B395" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="B396" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="B397" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="B398" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="B399" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="C399" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="B401" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="B402" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="B403" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="B404" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="B405" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="B406" t="s">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="C406" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="B408" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="B409" t="s">
-        <v>1070</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="B410" t="s">
-        <v>1173</v>
+        <v>1164</v>
       </c>
       <c r="C410" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="B411" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="B412" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
       <c r="C412" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="B413" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="B414" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="B415" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="B416" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="B417" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="B418" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="B419" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="B420" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="B421" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B422" t="s">
-        <v>1175</v>
+        <v>1166</v>
       </c>
       <c r="C422" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="B423" t="s">
-        <v>1142</v>
+        <v>1133</v>
       </c>
       <c r="C423" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="B424" t="s">
-        <v>1176</v>
+        <v>1167</v>
       </c>
       <c r="C424" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="B425" t="s">
-        <v>1194</v>
+        <v>1184</v>
       </c>
       <c r="C425" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>1114</v>
+        <v>1105</v>
       </c>
       <c r="B426" t="s">
-        <v>1097</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="B427" t="s">
-        <v>997</v>
+        <v>988</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>998</v>
+        <v>989</v>
       </c>
       <c r="B428" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
       <c r="B429" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="B430" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="B431" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="B432" t="s">
-        <v>1007</v>
+        <v>998</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="B433" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="B434" t="s">
-        <v>1149</v>
+        <v>1140</v>
       </c>
       <c r="C434" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="B435" t="s">
-        <v>1115</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B437" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="B438" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="B439" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="B440" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="B441" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="B442" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="B443" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="B444" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="B445" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="B446" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="B447" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="B448" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="B449" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="B450" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="B451" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="B452" t="s">
-        <v>1150</v>
+        <v>1141</v>
       </c>
       <c r="C452" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="B453" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="B454" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="B455" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="B456" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>1116</v>
+        <v>1107</v>
       </c>
       <c r="B457" t="s">
-        <v>1117</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="B458" t="s">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="C458" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="B460" t="s">
-        <v>1078</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="B461" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="B462" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="B463" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="B464" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="B465" t="s">
-        <v>1118</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="B466" t="s">
-        <v>1119</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="B467" t="s">
-        <v>1120</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="B468" t="s">
-        <v>1121</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="B469" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>1123</v>
+        <v>1114</v>
       </c>
       <c r="B470" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="B471" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
       <c r="C471" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="B473" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
       <c r="C473" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="B474" t="s">
-        <v>1198</v>
+        <v>1188</v>
       </c>
       <c r="C474" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="B476" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="C476" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="B477" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
       <c r="C477" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="B479" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="B480" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
       <c r="B481" t="s">
-        <v>1126</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="B482" t="s">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="C482" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="B484" t="s">
-        <v>1204</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="B485" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="B486" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="B487" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="B488" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="B489" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="B490" t="s">
-        <v>1201</v>
+        <v>1191</v>
       </c>
       <c r="C490" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="B492" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
     </row>
     <row r="493" spans="1:3">
       <c r="A493" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="B493" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="B494" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="B495" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="B496" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="B497" t="s">
-        <v>1151</v>
+        <v>1142</v>
       </c>
       <c r="C497" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="B499" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
     </row>
     <row r="500" spans="1:3">
       <c r="A500" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="B500" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="B501" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="B502" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="B503" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="B504" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="C504" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="506" spans="1:3">
       <c r="A506" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="B506" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="C506" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="507" spans="1:3">
       <c r="A507" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="B507" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="B508" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="B509" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="B510" t="s">
-        <v>1202</v>
+        <v>1192</v>
       </c>
       <c r="C510" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="B512" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="B513" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="B514" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="B515" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="B516" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="B517" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="B518" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="B519" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="B520" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1029</v>
+        <v>1020</v>
       </c>
       <c r="B521" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="B522" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="B523" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
       <c r="B524" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="B525" t="s">
-        <v>1203</v>
+        <v>1193</v>
       </c>
       <c r="C525" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B0A448-0804-48DE-ADD4-44ED023E2214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5753B921-D182-4E7D-86D4-3E8A41725FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="1209">
   <si>
     <t>Name</t>
   </si>
@@ -3664,6 +3664,12 @@
   </si>
   <si>
     <t>Unable to validate Verification of Recurring Cash Contribution. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>DelayAfterTime</t>
+  </si>
+  <si>
+    <t>ElementTimeout</t>
   </si>
 </sst>
 </file>
@@ -7138,7 +7144,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z1014"/>
+  <dimension ref="A1:Z1016"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
@@ -7553,70 +7559,84 @@
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>910</v>
+        <v>1207</v>
       </c>
       <c r="B48" t="s">
-        <v>910</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>1047</v>
+        <v>1208</v>
       </c>
       <c r="B49" t="s">
-        <v>1047</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" t="s">
-        <v>1048</v>
+        <v>910</v>
       </c>
       <c r="B50" t="s">
-        <v>1048</v>
+        <v>910</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
       <c r="A51" t="s">
-        <v>1119</v>
+        <v>1047</v>
       </c>
       <c r="B51" t="s">
-        <v>1119</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1122</v>
+        <v>1048</v>
       </c>
       <c r="B52" t="s">
-        <v>1122</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="B53" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
       <c r="A54" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B54" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1">
       <c r="A55" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A56" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A57" t="s">
         <v>1197</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B57" t="s">
         <v>1197</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="57" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="59" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8574,6 +8594,8 @@
     <row r="1012" ht="14.25" customHeight="1"/>
     <row r="1013" ht="14.25" customHeight="1"/>
     <row r="1014" ht="14.25" customHeight="1"/>
+    <row r="1015" ht="14.25" customHeight="1"/>
+    <row r="1016" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5753B921-D182-4E7D-86D4-3E8A41725FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA54ECE3-234E-4A49-89C5-C04F508E26B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="16740" windowHeight="8250" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="1209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1211">
   <si>
     <t>Name</t>
   </si>
@@ -3670,6 +3670,12 @@
   </si>
   <si>
     <t>ElementTimeout</t>
+  </si>
+  <si>
+    <t>UnsupportedIncomeTypesFilePath</t>
+  </si>
+  <si>
+    <t>TX_VSAVerificationProperties</t>
   </si>
 </sst>
 </file>
@@ -7637,8 +7643,22 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="59" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="58" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A58" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A59" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1210</v>
+      </c>
+    </row>
     <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="61" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="62" spans="1:2" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA54ECE3-234E-4A49-89C5-C04F508E26B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677C3510-5FCA-4B43-93D2-5ACF7A332E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="16740" windowHeight="8250" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1212">
   <si>
     <t>Name</t>
   </si>
@@ -3676,6 +3676,9 @@
   </si>
   <si>
     <t>TX_VSAVerificationProperties</t>
+  </si>
+  <si>
+    <t>TX_NoAssetsCheckProperties</t>
   </si>
 </sst>
 </file>
@@ -7659,7 +7662,14 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="60" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A60" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1211</v>
+      </c>
+    </row>
     <row r="61" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="62" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="63" spans="1:2" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677C3510-5FCA-4B43-93D2-5ACF7A332E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FA8820-BE92-48E5-9025-6CA9B7770066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1394">
   <si>
     <t>Name</t>
   </si>
@@ -3679,6 +3679,552 @@
   </si>
   <si>
     <t>TX_NoAssetsCheckProperties</t>
+  </si>
+  <si>
+    <t>CQExists</t>
+  </si>
+  <si>
+    <t>The Certification Questionnaire is missing for one or more adult household members. </t>
+  </si>
+  <si>
+    <t>CQ_Name</t>
+  </si>
+  <si>
+    <t>Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>CQ_UnitNumber</t>
+  </si>
+  <si>
+    <t>Unit Number has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>CQ_PropertyName</t>
+  </si>
+  <si>
+    <t>Property Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>CQ_Checkboxes</t>
+  </si>
+  <si>
+    <t>One of the Move-In, Recertification, or Addition of Household checkboxes has not been selected. </t>
+  </si>
+  <si>
+    <t>CQ_Q1NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 1 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q1YesNoPHAName</t>
+  </si>
+  <si>
+    <t>Question 1 has been answered Yes, but the PHA Name has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q1Yes</t>
+  </si>
+  <si>
+    <t>Question 1 has been answered Yes. Upload HAP contract with final signed documents. </t>
+  </si>
+  <si>
+    <t>CQ_Q2NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 2 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q2YesNoProgramName</t>
+  </si>
+  <si>
+    <t>Question 2 has been answered Yes, but the Program Name and/or the Organization Providing Rental Assistance has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q3NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 3 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q3Yes</t>
+  </si>
+  <si>
+    <t>Question 3 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q4NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 4 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q4Yes</t>
+  </si>
+  <si>
+    <t>Question 4 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q5NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 5 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q5Yes</t>
+  </si>
+  <si>
+    <t>Question 5 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q6NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 6 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q6Yes</t>
+  </si>
+  <si>
+    <t>Question 6 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q7NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 7 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q7Yes</t>
+  </si>
+  <si>
+    <t>Question 7 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q8NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 8 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q8Yes</t>
+  </si>
+  <si>
+    <t>Question 8 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q9NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 9 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q9Yes</t>
+  </si>
+  <si>
+    <t>Question 9 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q9YesNoICWNamesMatch</t>
+  </si>
+  <si>
+    <t>Question 9 has been answered Yes, but one or more household member names listed in the income section does not match the ICW. </t>
+  </si>
+  <si>
+    <t>CQ_Q10NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 10 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q10Yes</t>
+  </si>
+  <si>
+    <t>Question 10 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q11NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 11 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q11Yes</t>
+  </si>
+  <si>
+    <t>Question 11 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q12NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 12 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q12Yes</t>
+  </si>
+  <si>
+    <t>Question 12 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q13NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 13 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q13Yes</t>
+  </si>
+  <si>
+    <t>Question 13 has not been fully completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q14NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 14 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q14Yes</t>
+  </si>
+  <si>
+    <t>Question 14 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q15NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 15 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q15Yes</t>
+  </si>
+  <si>
+    <t>Question 15 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q16NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 16 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q16Yes</t>
+  </si>
+  <si>
+    <t>Question 16 has been answered Yes, but Monthly Net Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q17NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 17 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q17Yes</t>
+  </si>
+  <si>
+    <t>Question 17 has been answered Yes, but Amount Per Semester has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q18NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 18 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q19NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 19 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_IncomeType</t>
+  </si>
+  <si>
+    <t>One or more income types documented on the Certification Questionnaire do not match the income information listed on the ICW. </t>
+  </si>
+  <si>
+    <t>CQ_Q20NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 20 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q20Yes</t>
+  </si>
+  <si>
+    <t>Question 20 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q21NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 21 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q21Yes</t>
+  </si>
+  <si>
+    <t>Question 21 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q22NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 22 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q22Yes</t>
+  </si>
+  <si>
+    <t>Question 22 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q23NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 23 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q23Yes</t>
+  </si>
+  <si>
+    <t>Question 23 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q24NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 24 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q24Yes</t>
+  </si>
+  <si>
+    <t>Question 24 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q25NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 25 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q25Yes</t>
+  </si>
+  <si>
+    <t>Question 25 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q26NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 26 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q26Yes</t>
+  </si>
+  <si>
+    <t>Question 26 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q27NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 27 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q27Yes</t>
+  </si>
+  <si>
+    <t>Question 27 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q28NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 28 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q28Yes</t>
+  </si>
+  <si>
+    <t>Question 28 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q29NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 29 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q29Yes</t>
+  </si>
+  <si>
+    <t>Question 29 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q30NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 30 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q30Yes</t>
+  </si>
+  <si>
+    <t>Question 30 has been answered Yes, but Cash Value has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q31NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 31 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q31Yes</t>
+  </si>
+  <si>
+    <t>Question 31 has been answered Yes, but Cash Value has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q32NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 32 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q32Yes</t>
+  </si>
+  <si>
+    <t>Question 32 has been answered Yes. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>CQ_Q33NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 33 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q33Yes</t>
+  </si>
+  <si>
+    <t>Question 33 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q34NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 34 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q34Yes</t>
+  </si>
+  <si>
+    <t>Question 34 has been answered Yes, but Current Balance has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q35NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 35 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q35Yes</t>
+  </si>
+  <si>
+    <t>Question 35 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q36NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 36 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q36Yes</t>
+  </si>
+  <si>
+    <t>Question 36 has been answered Yes, but Amount Received has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_AssetType</t>
+  </si>
+  <si>
+    <t>One or more asset type(s), source(s), and/or cash value(s) documented on the Certification Questionnaire do not match the asset information listed on the ICW. </t>
+  </si>
+  <si>
+    <t>CQ_Q37NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 37 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q37No</t>
+  </si>
+  <si>
+    <t>Question 37 has been answered No, but one or more of Questions 38–54 have been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q37Yes</t>
+  </si>
+  <si>
+    <t>Question 37 has been answered Yes, but the required student certification questions have not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q39Yes</t>
+  </si>
+  <si>
+    <t>Question 39 has been answered Yes, but the required questions have not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_HomeSHTF</t>
+  </si>
+  <si>
+    <t>Application is for a HOME/SHTF unit, but Questions 45–50 have not been fully completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q51-54NotCompleted</t>
+  </si>
+  <si>
+    <t>Questions 51–54 have not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_NotSigned</t>
+  </si>
+  <si>
+    <t>Certification Questionnaire has not been signed. </t>
+  </si>
+  <si>
+    <t>CQ_PrintedName</t>
+  </si>
+  <si>
+    <t>Printed Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>CQ_NotDated</t>
+  </si>
+  <si>
+    <t>Certification Questionnaire has not been dated. </t>
+  </si>
+  <si>
+    <t>CQ_CheckMoveInDate</t>
+  </si>
+  <si>
+    <t>Date listed on the Certification Questionnaire is not within 120 days of Move-In date. </t>
+  </si>
+  <si>
+    <t>CQ_FindingError</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Certification Questionnaire. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>CQ</t>
+  </si>
+  <si>
+    <t>Certification Questionnaire</t>
   </si>
 </sst>
 </file>
@@ -4585,7 +5131,14 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="61" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A61" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1393</v>
+      </c>
+    </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="63" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="64" spans="1:3" ht="14.25" customHeight="1"/>
@@ -8634,7 +9187,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C525"/>
+  <dimension ref="A1:C616"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -12988,6 +13541,726 @@
         <v>1127</v>
       </c>
     </row>
+    <row r="527" spans="1:3">
+      <c r="A527" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B591" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B600" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1391</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C525" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
   <conditionalFormatting sqref="A478:A479 A475:A476 A460:A470 A472:A473 A481">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677C3510-5FCA-4B43-93D2-5ACF7A332E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C9A896-13B7-4735-994D-6A24A709304F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Findings" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$525</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$526</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1393">
   <si>
     <t>Name</t>
   </si>
@@ -3186,499 +3186,1042 @@
     <t>LLM_Classification_RetryCount</t>
   </si>
   <si>
+    <t>TX_TSAHCCheck</t>
+  </si>
+  <si>
+    <t>CZI_PartAYes</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>Verification Services Income</t>
+  </si>
+  <si>
+    <t>SSBL_NotMatchingIAQCheckbox</t>
+  </si>
+  <si>
+    <t>Social and/or Supplemental Security Income document on the Benefits Letter does not match the checkbox on the Income &amp; Asset Questionnaire.</t>
+  </si>
+  <si>
+    <t>ApplicationIncomplete</t>
+  </si>
+  <si>
+    <t>This application is not complete as application documents are missing. Please ensure all files are included before resubmitting</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Anticipated income in the next 12 months has been documented as yes for at least one question in Part A of the Certification of Zero Income. Manual review required.</t>
+  </si>
+  <si>
+    <t>PS_Checking&amp;SavingAccount</t>
+  </si>
+  <si>
+    <t>Additional checking and/or accounts have been listed on the Paystub that are not listed on the ICW.</t>
+  </si>
+  <si>
+    <t>Newly Added by removing Saving and checking accounts check separately</t>
+  </si>
+  <si>
+    <t>Day Calculator does not exist for Employment Verification.</t>
+  </si>
+  <si>
+    <t>CSEI_ScheduleCCountCheck</t>
+  </si>
+  <si>
+    <t>There are more Schedule Cs than CSEI</t>
+  </si>
+  <si>
+    <t>Application Incomplete</t>
+  </si>
+  <si>
+    <t>CSEI_FindingError</t>
+  </si>
+  <si>
+    <t>VRCC_EmailReceipt</t>
+  </si>
+  <si>
+    <t>Verification of Recurring Cash Contributions email receipt requires manual review.</t>
+  </si>
+  <si>
+    <t>RCV_EmailReceiptAndClarification</t>
+  </si>
+  <si>
+    <t>Regular Contributions Verification email receipt requires manual review.</t>
+  </si>
+  <si>
+    <t>EV_TX_ApplicantName</t>
+  </si>
+  <si>
+    <t>EDC_HighestCalValue</t>
+  </si>
+  <si>
+    <t>Newly added by Harmandeep</t>
+  </si>
+  <si>
+    <t>IAQ_NoSupportingDocument</t>
+  </si>
+  <si>
+    <t>Income listed on IAQ page 2 does not have supporting documentation</t>
+  </si>
+  <si>
+    <t>Annual Income is above the Income Limit listed on the Income Calculation Worksheet. Manual review required.</t>
+  </si>
+  <si>
+    <t>The special needs question has not been answered.</t>
+  </si>
+  <si>
+    <t>None of the student options were documented.</t>
+  </si>
+  <si>
+    <t>All adults have not initialed the form.</t>
+  </si>
+  <si>
+    <t>Assets Type and/or  value does not match that listed on the Income Calculation Worksheet.</t>
+  </si>
+  <si>
+    <t>IAQ_Page1NotMatchingPage2</t>
+  </si>
+  <si>
+    <t>Income Type Marked Yes on IAQ page 1 but not listed on IAQ page 2</t>
+  </si>
+  <si>
+    <t>IAQ_VeteransLetter</t>
+  </si>
+  <si>
+    <t>Veterans benefits have been indicated, but not all VA Benefits Letters have been provided.</t>
+  </si>
+  <si>
+    <t>Newly added by Bagi</t>
+  </si>
+  <si>
+    <t>Day Calculator does not exist for Paystub</t>
+  </si>
+  <si>
+    <t>Implementing this only in EDC.</t>
+  </si>
+  <si>
+    <t>PS_NameNotMatchingIAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employment income has been indicated, but not all supporting Employment document has been provided (Paystub, Employment Verification, Offer Letter, or Verification Services). </t>
+  </si>
+  <si>
+    <t>Day Calculator does not exist for Verification of employment</t>
+  </si>
+  <si>
+    <t>Day Calculator does not exist for Offer Letter</t>
+  </si>
+  <si>
+    <t>Day Calculator does not exist for Work Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day Calculator does not exist for Verification services </t>
+  </si>
+  <si>
+    <t>Implementing whis only in EDC.</t>
+  </si>
+  <si>
+    <t>CSPH_NameNotMatchingIAQ</t>
+  </si>
+  <si>
+    <t>Child support income has been indicated, but not all Child Support documentation has been provided.</t>
+  </si>
+  <si>
+    <t>SSBL_NameNotMatchingIAQ</t>
+  </si>
+  <si>
+    <t>Social Security benefits have been indicated, but not all Social Security Benefits Letters have been provided. </t>
+  </si>
+  <si>
+    <t>SSIB_NameNotMatchingIAQ</t>
+  </si>
+  <si>
+    <t>Supplemental Security Income has been indicated, but not all Social Security Benefits Letters have been provided. </t>
+  </si>
+  <si>
+    <t>Newly added by Bagi for AZ</t>
+  </si>
+  <si>
+    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has not been completed.</t>
+  </si>
+  <si>
+    <t>CSEI_NameNotMatchingIAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-employment income has been indicated, but not all Self Employment documentation has been provided. </t>
+  </si>
+  <si>
+    <t>The 1040 tax form was not dated.</t>
+  </si>
+  <si>
+    <t>EV_NameNotMatchingIAQ</t>
+  </si>
+  <si>
+    <t>Applicant Name across the Employment Verification, Day Calculator, and Income Calculation Worksheet do not match.</t>
+  </si>
+  <si>
+    <t>CSS_GraduateandFullTimeStudents</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The Certification of Student Status has indicated that someone has graduated in the calendar year and all residents in the household are full time students which does not align.</t>
+  </si>
+  <si>
+    <t>Verification of Regular Contributions Verification has not been signed by recipient.</t>
+  </si>
+  <si>
+    <t>Verification of Regular Contributions Verification has not been dated by recipient.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification of Regular Contributions Verification has not been signed by contributor. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular Contributions Verification has not been dated by contributor. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency of payments checkbox on the Regular Contributions Verification has not been documented. </t>
+  </si>
+  <si>
+    <t>RCV_NameNotMatchingIAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurring Monetary Contributions have been indicated, but not all Regular Monetary Contributions documentation has been provided. </t>
+  </si>
+  <si>
+    <t>VABL_NameNotMatchingIAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veterans benefits have been indicated, but not all VA Benefits Letters have not been provided. </t>
+  </si>
+  <si>
+    <t>Unable to validate the TSAHC. Manual review required. </t>
+  </si>
+  <si>
+    <t>FindAllBusinessNmeMatches_Threshold</t>
+  </si>
+  <si>
+    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
+  </si>
+  <si>
+    <t>ApplicationReviewProcess</t>
+  </si>
+  <si>
+    <t>BackToSiteStates</t>
+  </si>
+  <si>
+    <t>NotBackToSiteStates</t>
+  </si>
+  <si>
+    <t>YardiReviewer</t>
+  </si>
+  <si>
+    <t>ASFAExists</t>
+  </si>
+  <si>
+    <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
+  </si>
+  <si>
+    <t>Updated by Raluca</t>
+  </si>
+  <si>
+    <t>Assets exceed HUD asset limit. Third party verification of all assets is required.</t>
+  </si>
+  <si>
+    <t>Annual income is listed as zero. Confirm this is accurate and ensure the Certification of Zero Income is present in the file.</t>
+  </si>
+  <si>
+    <t>Current employment has been documented on the Self-Certification of Non-Employment. Verification of employment is needed.</t>
+  </si>
+  <si>
+    <t>Applicant has reported they have no assets. If applicant has income, confirm how the income is paid.</t>
+  </si>
+  <si>
+    <t>Raluca removed the check as per business requirement</t>
+  </si>
+  <si>
+    <t>Multiple sources of verification included for same income. Remove verification documents that are not being used in the calculation of income.</t>
+  </si>
+  <si>
+    <t>Paystubs list YTD pay that is not paid on a current paystub so annual income cannot be accurately predicted. Clarify, with the employer, the pay type and how often it is received.</t>
+  </si>
+  <si>
+    <t>WN_TotalMatchSum</t>
+  </si>
+  <si>
+    <t>Total Pay listed on the Work Number does not match the sum of each pay type on the Work Number.</t>
+  </si>
+  <si>
+    <t>Both 120 days of pay history available and 120 days of pay history not available data sections are populated on the Child Support Calculator. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
+  </si>
+  <si>
+    <t>The consistent payments data is populated on Child Support Calcs but additional data tables are populated as well. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
+  </si>
+  <si>
+    <t>Social Security Benefits Letter is missing at least one page. Upload missing page with final signed documents.</t>
+  </si>
+  <si>
+    <t>Season or Sporadic work has been documented on the Employment Verification. Manual review is needed.  </t>
+  </si>
+  <si>
+    <t>Applicant marked that no household members are part of the original qualifying household. Please have the applicant correct.</t>
+  </si>
+  <si>
+    <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant is a Dominium employee. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Income type included that cannot be validated with automation. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>This application is a Section 811 unit. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Application Summary. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Applicant reported a minor will live in the household less than 50% of the time. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Member Information Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Income &amp; Asset Questionnaire. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self Certification of Non Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Self Certification &amp; Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Affidavit of Student Financial Assistance. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Student Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Annual Student Certification since there is Home unit . Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Zero Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate VAWA Acknowledgement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Screening Document. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Regular pay rate has increased across paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate paystubs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Verification of Employment - manual review is needed to ensure document was received via 3rd party.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Commission, bonuses, tips, other amount has been populated. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Anticipated wage increase indicated on employment verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Employment. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Offer Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Work Number. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Self-Employment Certification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Payment History. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Child Support Calcs. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Certification of Self-Employment Income. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Profit/Loss Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Household Asset Breakdown. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Employment Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate the Certification of Student Status. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Regular Contributions Verification. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Bank statements are included in the file. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Bank Statements. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Leave and Earnings Statement. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>Unable to validate Release and Consent Form. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification Services. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Release and Consent Form is missing from the application. </t>
+  </si>
+  <si>
+    <t>SE_003</t>
+  </si>
+  <si>
+    <t>Assign button cannot be found in Yardi.</t>
+  </si>
+  <si>
+    <t>ManagerName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1040, Schedule C forms does not exist for Self-Employment Verification </t>
+  </si>
+  <si>
+    <t>Supporting documents do not exist for the Certification of Self-Employment Income.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name listed on the Verification of Recurring Cash Contribution and ICW do not match. </t>
+  </si>
+  <si>
+    <t>Date listed on the Verification of Recurring Cash Contribution is over 120 days in the past.</t>
+  </si>
+  <si>
+    <t>Date listed on the Verification of Recurring Cash Contribution is not with in 120 days of Move-In date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contributor and Amount listed on the Verification of Recurring Cash Contribution and ICW do not match. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification of Recurring Cash Contribution has not been signed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification of Recurring Cash Contribution has not been dated appropriately. </t>
+  </si>
+  <si>
+    <t>Unable to validate Verification of Recurring Cash Contribution. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>DelayAfterTime</t>
+  </si>
+  <si>
+    <t>ElementTimeout</t>
+  </si>
+  <si>
+    <t>UnsupportedIncomeTypesFilePath</t>
+  </si>
+  <si>
+    <t>TX_VSAVerificationProperties</t>
+  </si>
+  <si>
+    <t>Third party verification of assets is missing from the application and this property requires asset verification. Manual review required.</t>
+  </si>
+  <si>
+    <t>ThirdPartyVerification</t>
+  </si>
+  <si>
     <t>TX_VSACheck</t>
   </si>
   <si>
-    <t>TX_TSAHCCheck</t>
-  </si>
-  <si>
-    <t>CZI_PartAYes</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>Verification Services Income</t>
-  </si>
-  <si>
-    <t>SSBL_NotMatchingIAQCheckbox</t>
-  </si>
-  <si>
-    <t>Social and/or Supplemental Security Income document on the Benefits Letter does not match the checkbox on the Income &amp; Asset Questionnaire.</t>
-  </si>
-  <si>
-    <t>ApplicationIncomplete</t>
-  </si>
-  <si>
-    <t>This application is not complete as application documents are missing. Please ensure all files are included before resubmitting</t>
-  </si>
-  <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>Anticipated income in the next 12 months has been documented as yes for at least one question in Part A of the Certification of Zero Income. Manual review required.</t>
-  </si>
-  <si>
-    <t>PS_Checking&amp;SavingAccount</t>
-  </si>
-  <si>
-    <t>Additional checking and/or accounts have been listed on the Paystub that are not listed on the ICW.</t>
-  </si>
-  <si>
-    <t>Newly Added by removing Saving and checking accounts check separately</t>
-  </si>
-  <si>
-    <t>Day Calculator does not exist for Employment Verification.</t>
-  </si>
-  <si>
-    <t>CSEI_ScheduleCCountCheck</t>
-  </si>
-  <si>
-    <t>There are more Schedule Cs than CSEI</t>
-  </si>
-  <si>
-    <t>Application Incomplete</t>
-  </si>
-  <si>
-    <t>CSEI_FindingError</t>
-  </si>
-  <si>
-    <t>VRCC_EmailReceipt</t>
-  </si>
-  <si>
-    <t>Verification of Recurring Cash Contributions email receipt requires manual review.</t>
-  </si>
-  <si>
-    <t>RCV_EmailReceiptAndClarification</t>
-  </si>
-  <si>
-    <t>Regular Contributions Verification email receipt requires manual review.</t>
-  </si>
-  <si>
-    <t>EV_TX_ApplicantName</t>
-  </si>
-  <si>
-    <t>EDC_HighestCalValue</t>
-  </si>
-  <si>
-    <t>Newly added by Harmandeep</t>
-  </si>
-  <si>
-    <t>IAQ_NoSupportingDocument</t>
-  </si>
-  <si>
-    <t>Income listed on IAQ page 2 does not have supporting documentation</t>
-  </si>
-  <si>
-    <t>Annual Income is above the Income Limit listed on the Income Calculation Worksheet. Manual review required.</t>
-  </si>
-  <si>
-    <t>The special needs question has not been answered.</t>
-  </si>
-  <si>
-    <t>None of the student options were documented.</t>
-  </si>
-  <si>
-    <t>All adults have not initialed the form.</t>
-  </si>
-  <si>
-    <t>Assets Type and/or  value does not match that listed on the Income Calculation Worksheet.</t>
-  </si>
-  <si>
-    <t>IAQ_Page1NotMatchingPage2</t>
-  </si>
-  <si>
-    <t>Income Type Marked Yes on IAQ page 1 but not listed on IAQ page 2</t>
-  </si>
-  <si>
-    <t>IAQ_VeteransLetter</t>
-  </si>
-  <si>
-    <t>Veterans benefits have been indicated, but not all VA Benefits Letters have been provided.</t>
-  </si>
-  <si>
-    <t>Newly added by Bagi</t>
-  </si>
-  <si>
-    <t>Day Calculator does not exist for Paystub</t>
-  </si>
-  <si>
-    <t>Implementing this only in EDC.</t>
-  </si>
-  <si>
-    <t>PS_NameNotMatchingIAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employment income has been indicated, but not all supporting Employment document has been provided (Paystub, Employment Verification, Offer Letter, or Verification Services). </t>
-  </si>
-  <si>
-    <t>Day Calculator does not exist for Verification of employment</t>
-  </si>
-  <si>
-    <t>Day Calculator does not exist for Offer Letter</t>
-  </si>
-  <si>
-    <t>Day Calculator does not exist for Work Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day Calculator does not exist for Verification services </t>
-  </si>
-  <si>
-    <t>Implementing whis only in EDC.</t>
-  </si>
-  <si>
-    <t>CSPH_NameNotMatchingIAQ</t>
-  </si>
-  <si>
-    <t>Child support income has been indicated, but not all Child Support documentation has been provided.</t>
-  </si>
-  <si>
-    <t>SSBL_NameNotMatchingIAQ</t>
-  </si>
-  <si>
-    <t>Social Security benefits have been indicated, but not all Social Security Benefits Letters have been provided. </t>
-  </si>
-  <si>
-    <t>SSIB_NameNotMatchingIAQ</t>
-  </si>
-  <si>
-    <t>Supplemental Security Income has been indicated, but not all Social Security Benefits Letters have been provided. </t>
-  </si>
-  <si>
-    <t>Newly added by Bagi for AZ</t>
-  </si>
-  <si>
-    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has not been completed.</t>
-  </si>
-  <si>
-    <t>CSEI_NameNotMatchingIAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self-employment income has been indicated, but not all Self Employment documentation has been provided. </t>
-  </si>
-  <si>
-    <t>The 1040 tax form was not dated.</t>
-  </si>
-  <si>
-    <t>EV_NameNotMatchingIAQ</t>
-  </si>
-  <si>
-    <t>Applicant Name across the Employment Verification, Day Calculator, and Income Calculation Worksheet do not match.</t>
-  </si>
-  <si>
-    <t>CSS_GraduateandFullTimeStudents</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The Certification of Student Status has indicated that someone has graduated in the calendar year and all residents in the household are full time students which does not align.</t>
-  </si>
-  <si>
-    <t>Verification of Regular Contributions Verification has not been signed by recipient.</t>
-  </si>
-  <si>
-    <t>Verification of Regular Contributions Verification has not been dated by recipient.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification of Regular Contributions Verification has not been signed by contributor. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular Contributions Verification has not been dated by contributor. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency of payments checkbox on the Regular Contributions Verification has not been documented. </t>
-  </si>
-  <si>
-    <t>RCV_NameNotMatchingIAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recurring Monetary Contributions have been indicated, but not all Regular Monetary Contributions documentation has been provided. </t>
-  </si>
-  <si>
-    <t>VABL_NameNotMatchingIAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veterans benefits have been indicated, but not all VA Benefits Letters have not been provided. </t>
-  </si>
-  <si>
-    <t>Unable to validate the TSAHC. Manual review required. </t>
-  </si>
-  <si>
-    <t>FindAllBusinessNmeMatches_Threshold</t>
-  </si>
-  <si>
-    <t>C:\Users\raluca.ilinca.azureai-jump2\Documents\AZApplicationReview\Prompts\</t>
-  </si>
-  <si>
-    <t>ApplicationReviewProcess</t>
-  </si>
-  <si>
-    <t>BackToSiteStates</t>
-  </si>
-  <si>
-    <t>NotBackToSiteStates</t>
-  </si>
-  <si>
-    <t>YardiReviewer</t>
-  </si>
-  <si>
-    <t>ASFAExists</t>
-  </si>
-  <si>
-    <t>Affidavit of Student Financial Assistance is present in the application, manual review required.</t>
-  </si>
-  <si>
-    <t>Updated by Raluca</t>
-  </si>
-  <si>
-    <t>Assets exceed HUD asset limit. Third party verification of all assets is required.</t>
-  </si>
-  <si>
-    <t>Annual income is listed as zero. Confirm this is accurate and ensure the Certification of Zero Income is present in the file.</t>
-  </si>
-  <si>
-    <t>Current employment has been documented on the Self-Certification of Non-Employment. Verification of employment is needed.</t>
-  </si>
-  <si>
-    <t>Applicant has reported they have no assets. If applicant has income, confirm how the income is paid.</t>
-  </si>
-  <si>
-    <t>Raluca removed the check as per business requirement</t>
-  </si>
-  <si>
-    <t>Multiple sources of verification included for same income. Remove verification documents that are not being used in the calculation of income.</t>
-  </si>
-  <si>
-    <t>Paystubs list YTD pay that is not paid on a current paystub so annual income cannot be accurately predicted. Clarify, with the employer, the pay type and how often it is received.</t>
-  </si>
-  <si>
-    <t>WN_TotalMatchSum</t>
-  </si>
-  <si>
-    <t>Total Pay listed on the Work Number does not match the sum of each pay type on the Work Number.</t>
-  </si>
-  <si>
-    <t>Both 120 days of pay history available and 120 days of pay history not available data sections are populated on the Child Support Calculator. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
-  </si>
-  <si>
-    <t>The consistent payments data is populated on Child Support Calcs but additional data tables are populated as well. Archie cannot determine which data to use. Remove the unnecessary information from the calculator. </t>
-  </si>
-  <si>
-    <t>Social Security Benefits Letter is missing at least one page. Upload missing page with final signed documents.</t>
-  </si>
-  <si>
-    <t>Season or Sporadic work has been documented on the Employment Verification. Manual review is needed.  </t>
-  </si>
-  <si>
-    <t>Applicant marked that no household members are part of the original qualifying household. Please have the applicant correct.</t>
-  </si>
-  <si>
-    <t>Unable to validate Tenant Rights and Resource Guide (TRRG). Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Housing History Disclosure. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Live-In Attendant documented on the Income Calculation Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Applicant is a Dominium employee. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Income type included that cannot be validated with automation. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>This application is a Section 811 unit. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Income Calculation Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Application Summary. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Applicant reported a minor will live in the household less than 50% of the time. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Member Information Document. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Income &amp; Asset Questionnaire. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self Certification of Non Employment. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Self Certification &amp; Worksheet. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Affidavit of Student Financial Assistance. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>The applicant has indicated household contains all students by selecting 2 or 3 in Part A on the Student Certification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Student Certification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Annual Student Certification since there is Home unit . Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Zero Income. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate VAWA Acknowledgement. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Screening Document. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Regular pay rate has increased across paystubs. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate paystubs. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Verification of Employment - manual review is needed to ensure document was received via 3rd party.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Commission, bonuses, tips, other amount has been populated. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Anticipated wage increase indicated on employment verification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Employment. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Offer Letter. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Work Number. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Self-Employment Certification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Payment History. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Child Support Calcs. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Overpayment listed on SS/SSI benefit letter. Documentation of months left on repayment is required. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Supplemental Security Income Letter. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Housing Demographic Reporting Form. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Question 3 – Does any other member of your household receive a salary or other payments from this business has been documented as yes. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Certification of Self-Employment Income. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Profit/Loss Statement. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate findings for Applicant/Tenant Release and Consent. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Household Asset Breakdown. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Presently Employed has been listed as No on the Verification of Employment. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Employment Verification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate the Certification of Student Status. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Regular Contributions Verification. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Bank statements are included in the file. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Bank Statements. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Leave and Earnings Statement. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Veterans Affairs Benefits Letter. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>Unable to validate Release and Consent Form. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Verification Services. Manual review is needed. </t>
-  </si>
-  <si>
-    <t>Unable to validate Asset Certification of Net Family Assets. Manual review is needed. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Release and Consent Form is missing from the application. </t>
-  </si>
-  <si>
-    <t>SE_003</t>
-  </si>
-  <si>
-    <t>Assign button cannot be found in Yardi.</t>
-  </si>
-  <si>
-    <t>ManagerName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1040, Schedule C forms does not exist for Self-Employment Verification </t>
-  </si>
-  <si>
-    <t>Supporting documents do not exist for the Certification of Self-Employment Income.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name listed on the Verification of Recurring Cash Contribution and ICW do not match. </t>
-  </si>
-  <si>
-    <t>Date listed on the Verification of Recurring Cash Contribution is over 120 days in the past.</t>
-  </si>
-  <si>
-    <t>Date listed on the Verification of Recurring Cash Contribution is not with in 120 days of Move-In date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contributor and Amount listed on the Verification of Recurring Cash Contribution and ICW do not match. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification of Recurring Cash Contribution has not been signed. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification of Recurring Cash Contribution has not been dated appropriately. </t>
-  </si>
-  <si>
-    <t>Unable to validate Verification of Recurring Cash Contribution. Manual review is needed.</t>
-  </si>
-  <si>
-    <t>DelayAfterTime</t>
-  </si>
-  <si>
-    <t>ElementTimeout</t>
-  </si>
-  <si>
-    <t>UnsupportedIncomeTypesFilePath</t>
-  </si>
-  <si>
-    <t>TX_VSAVerificationProperties</t>
-  </si>
-  <si>
-    <t>TX_NoAssetsCheckProperties</t>
+    <t>CQExists</t>
+  </si>
+  <si>
+    <t>The Certification Questionnaire is missing for one or more adult household members. </t>
+  </si>
+  <si>
+    <t>CQ_Name</t>
+  </si>
+  <si>
+    <t>Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>CQ_UnitNumber</t>
+  </si>
+  <si>
+    <t>Unit Number has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>CQ_PropertyName</t>
+  </si>
+  <si>
+    <t>Property Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>CQ_Checkboxes</t>
+  </si>
+  <si>
+    <t>One of the Move-In, Recertification, or Addition of Household checkboxes has not been selected. </t>
+  </si>
+  <si>
+    <t>CQ_Q1NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 1 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q1YesNoPHAName</t>
+  </si>
+  <si>
+    <t>Question 1 has been answered Yes, but the PHA Name has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q1Yes</t>
+  </si>
+  <si>
+    <t>Question 1 has been answered Yes. Upload HAP contract with final signed documents. </t>
+  </si>
+  <si>
+    <t>CQ_Q2NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 2 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q2YesNoProgramName</t>
+  </si>
+  <si>
+    <t>Question 2 has been answered Yes, but the Program Name and/or the Organization Providing Rental Assistance has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q3NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 3 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q3Yes</t>
+  </si>
+  <si>
+    <t>Question 3 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q4NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 4 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q4Yes</t>
+  </si>
+  <si>
+    <t>Question 4 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q5NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 5 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q5Yes</t>
+  </si>
+  <si>
+    <t>Question 5 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q6NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 6 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q6Yes</t>
+  </si>
+  <si>
+    <t>Question 6 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q7NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 7 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q7Yes</t>
+  </si>
+  <si>
+    <t>Question 7 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q8NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 8 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q8Yes</t>
+  </si>
+  <si>
+    <t>Question 8 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q9NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 9 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q9Yes</t>
+  </si>
+  <si>
+    <t>Question 9 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q9YesNoICWNamesMatch</t>
+  </si>
+  <si>
+    <t>Question 9 has been answered Yes, but one or more household member names listed in the income section does not match the ICW. </t>
+  </si>
+  <si>
+    <t>CQ_Q10NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 10 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q10Yes</t>
+  </si>
+  <si>
+    <t>Question 10 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q11NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 11 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q11Yes</t>
+  </si>
+  <si>
+    <t>Question 11 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q12NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 12 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q12Yes</t>
+  </si>
+  <si>
+    <t>Question 12 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q13NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 13 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q13Yes</t>
+  </si>
+  <si>
+    <t>Question 13 has not been fully completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q14NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 14 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q14Yes</t>
+  </si>
+  <si>
+    <t>Question 14 has been answered Yes, but Monthly Gross Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q15NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 15 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q15Yes</t>
+  </si>
+  <si>
+    <t>Question 15 has been answered Yes, but the required income information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q16NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 16 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q16Yes</t>
+  </si>
+  <si>
+    <t>Question 16 has been answered Yes, but Monthly Net Income has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q17NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 17 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q17Yes</t>
+  </si>
+  <si>
+    <t>Question 17 has been answered Yes, but Amount Per Semester has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q18NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 18 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q19NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 19 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_IncomeType</t>
+  </si>
+  <si>
+    <t>One or more income types documented on the Certification Questionnaire do not match the income information listed on the ICW. </t>
+  </si>
+  <si>
+    <t>CQ_Q20NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 20 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q20Yes</t>
+  </si>
+  <si>
+    <t>Question 20 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q21NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 21 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q21Yes</t>
+  </si>
+  <si>
+    <t>Question 21 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q22NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 22 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q22Yes</t>
+  </si>
+  <si>
+    <t>Question 22 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q23NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 23 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q23Yes</t>
+  </si>
+  <si>
+    <t>Question 23 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q24NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 24 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q24Yes</t>
+  </si>
+  <si>
+    <t>Question 24 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q25NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 25 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q25Yes</t>
+  </si>
+  <si>
+    <t>Question 25 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q26NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 26 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q26Yes</t>
+  </si>
+  <si>
+    <t>Question 26 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q27NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 27 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q27Yes</t>
+  </si>
+  <si>
+    <t>Question 27 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q28NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 28 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q28Yes</t>
+  </si>
+  <si>
+    <t>Question 28 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q29NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 29 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q29Yes</t>
+  </si>
+  <si>
+    <t>Question 29 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q30NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 30 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q30Yes</t>
+  </si>
+  <si>
+    <t>Question 30 has been answered Yes, but Cash Value has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q31NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 31 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q31Yes</t>
+  </si>
+  <si>
+    <t>Question 31 has been answered Yes, but Cash Value has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q32NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 32 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q32Yes</t>
+  </si>
+  <si>
+    <t>Question 32 has been answered Yes. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>CQ_Q33NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 33 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q33Yes</t>
+  </si>
+  <si>
+    <t>Question 33 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q34NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 34 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q34Yes</t>
+  </si>
+  <si>
+    <t>Question 34 has been answered Yes, but Current Balance has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_Q35NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 35 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q35Yes</t>
+  </si>
+  <si>
+    <t>Question 35 has been answered Yes, but the required asset information has not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q36NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 36 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q36Yes</t>
+  </si>
+  <si>
+    <t>Question 36 has been answered Yes, but Amount Received has not been provided. </t>
+  </si>
+  <si>
+    <t>CQ_AssetType</t>
+  </si>
+  <si>
+    <t>One or more asset type(s), source(s), and/or cash value(s) documented on the Certification Questionnaire do not match the asset information listed on the ICW. </t>
+  </si>
+  <si>
+    <t>CQ_Q37NotYesNo</t>
+  </si>
+  <si>
+    <t>Question 37 has not been answered Yes or No. </t>
+  </si>
+  <si>
+    <t>CQ_Q37No</t>
+  </si>
+  <si>
+    <t>Question 37 has been answered No, but one or more of Questions 38–54 have been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q37Yes</t>
+  </si>
+  <si>
+    <t>Question 37 has been answered Yes, but the required student certification questions have not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q39Yes</t>
+  </si>
+  <si>
+    <t>Question 39 has been answered Yes, but the required questions have not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_HomeSHTF</t>
+  </si>
+  <si>
+    <t>Application is for a HOME/SHTF unit, but Questions 45–50 have not been fully completed. </t>
+  </si>
+  <si>
+    <t>CQ_Q51-54NotCompleted</t>
+  </si>
+  <si>
+    <t>Questions 51–54 have not been completed. </t>
+  </si>
+  <si>
+    <t>CQ_NotSigned</t>
+  </si>
+  <si>
+    <t>Certification Questionnaire has not been signed. </t>
+  </si>
+  <si>
+    <t>CQ_PrintedName</t>
+  </si>
+  <si>
+    <t>Printed Name has not been completed on the Certification Questionnaire. </t>
+  </si>
+  <si>
+    <t>CQ_NotDated</t>
+  </si>
+  <si>
+    <t>Certification Questionnaire has not been dated. </t>
+  </si>
+  <si>
+    <t>CQ_CheckMoveInDate</t>
+  </si>
+  <si>
+    <t>Date listed on the Certification Questionnaire is not within 120 days of Move-In date. </t>
+  </si>
+  <si>
+    <t>CQ_FindingError</t>
+  </si>
+  <si>
+    <t>Unable to validate findings for Certification Questionnaire. Manual review is needed. </t>
   </si>
 </sst>
 </file>
@@ -4114,7 +4657,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -4147,7 +4690,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -4177,10 +4720,10 @@
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B12" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -4571,10 +5114,10 @@
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B59" t="s">
         <v>1050</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
@@ -6177,10 +6720,10 @@
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B34" t="s">
         <v>1195</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
@@ -7153,7 +7696,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z1016"/>
+  <dimension ref="A1:Z1014"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
@@ -7568,18 +8111,18 @@
     </row>
     <row r="48" spans="1:2" ht="14.25" customHeight="1">
       <c r="A48" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B48" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B49" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
@@ -7600,18 +8143,18 @@
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
       <c r="A52" t="s">
-        <v>1048</v>
+        <v>1118</v>
       </c>
       <c r="B52" t="s">
-        <v>1048</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B53" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25" customHeight="1">
@@ -7632,18 +8175,18 @@
     </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1">
       <c r="A56" t="s">
-        <v>1124</v>
+        <v>1196</v>
       </c>
       <c r="B56" t="s">
-        <v>1124</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.25" customHeight="1">
       <c r="A57" t="s">
-        <v>1197</v>
+        <v>1208</v>
       </c>
       <c r="B57" t="s">
-        <v>1197</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.25" customHeight="1">
@@ -7656,20 +8199,13 @@
     </row>
     <row r="59" spans="1:2" ht="14.25" customHeight="1">
       <c r="A59" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B59" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A60" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1211</v>
-      </c>
-    </row>
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="61" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="62" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="63" spans="1:2" ht="14.25" customHeight="1"/>
@@ -8624,8 +9160,6 @@
     <row r="1012" ht="14.25" customHeight="1"/>
     <row r="1013" ht="14.25" customHeight="1"/>
     <row r="1014" ht="14.25" customHeight="1"/>
-    <row r="1015" ht="14.25" customHeight="1"/>
-    <row r="1016" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8634,7 +9168,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C525"/>
+  <dimension ref="A1:C617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -8660,29 +9194,26 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B5" t="s">
         <v>1054</v>
       </c>
-      <c r="B5" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>612</v>
-      </c>
-      <c r="B7" t="s">
-        <v>647</v>
-      </c>
-      <c r="C7" t="s">
-        <v>586</v>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1210</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>642</v>
+        <v>612</v>
       </c>
       <c r="B8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C8" t="s">
         <v>586</v>
@@ -8690,10 +9221,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C9" t="s">
         <v>586</v>
@@ -8701,10 +9232,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C10" t="s">
         <v>586</v>
@@ -8712,10 +9243,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="B11" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C11" t="s">
         <v>586</v>
@@ -8723,10 +9254,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>676</v>
+        <v>652</v>
       </c>
       <c r="B12" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="C12" t="s">
         <v>586</v>
@@ -8734,272 +9265,272 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>676</v>
+      </c>
+      <c r="B13" t="s">
+        <v>677</v>
+      </c>
+      <c r="C13" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>645</v>
       </c>
-      <c r="B13" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15" t="s">
-        <v>443</v>
+      <c r="B14" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s">
-        <v>1075</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C19" t="s">
-        <v>579</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>490</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s">
-        <v>491</v>
+        <v>198</v>
+      </c>
+      <c r="C20" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>582</v>
+        <v>490</v>
       </c>
       <c r="B21" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1127</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B22" t="s">
-        <v>1144</v>
+        <v>1127</v>
       </c>
       <c r="C22" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="B23" t="s">
-        <v>603</v>
+        <v>1143</v>
       </c>
       <c r="C23" t="s">
-        <v>586</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="B24" t="s">
-        <v>1145</v>
+        <v>603</v>
       </c>
       <c r="C24" t="s">
-        <v>1127</v>
+        <v>586</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B25" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C25" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>684</v>
+        <v>617</v>
       </c>
       <c r="B26" t="s">
-        <v>1129</v>
+        <v>1145</v>
       </c>
       <c r="C26" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>817</v>
+        <v>684</v>
       </c>
       <c r="B27" t="s">
-        <v>1147</v>
+        <v>1128</v>
       </c>
       <c r="C27" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>817</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>472</v>
       </c>
-      <c r="B28" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>175</v>
-      </c>
-      <c r="B30" t="s">
-        <v>176</v>
+      <c r="B29" t="s">
+        <v>1147</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>498</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>499</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>498</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>1076</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>673</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>674</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>556</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>557</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="B42" t="s">
-        <v>681</v>
+        <v>557</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="B43" t="s">
-        <v>605</v>
-      </c>
-      <c r="C43" t="s">
-        <v>586</v>
+        <v>681</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>678</v>
+        <v>604</v>
       </c>
       <c r="B44" t="s">
-        <v>679</v>
+        <v>605</v>
       </c>
       <c r="C44" t="s">
         <v>586</v>
@@ -9007,158 +9538,158 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>678</v>
+      </c>
+      <c r="B45" t="s">
+        <v>679</v>
+      </c>
+      <c r="C45" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>487</v>
       </c>
-      <c r="B45" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>177</v>
-      </c>
-      <c r="B47" t="s">
-        <v>179</v>
+      <c r="B46" t="s">
+        <v>1148</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>1077</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" t="s">
-        <v>523</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="C55" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>558</v>
+        <v>101</v>
       </c>
       <c r="B56" t="s">
-        <v>559</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>668</v>
+        <v>558</v>
       </c>
       <c r="B57" t="s">
-        <v>669</v>
+        <v>559</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>1029</v>
+        <v>668</v>
       </c>
       <c r="B58" t="s">
-        <v>1030</v>
+        <v>669</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>587</v>
+        <v>1029</v>
       </c>
       <c r="B59" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1127</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>587</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
         <v>486</v>
       </c>
-      <c r="B60" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>178</v>
-      </c>
-      <c r="B62" t="s">
-        <v>526</v>
+      <c r="B61" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
         <v>523</v>
@@ -9166,10 +9697,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C65" t="s">
         <v>523</v>
@@ -9177,10 +9708,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C66" t="s">
         <v>523</v>
@@ -9188,10 +9719,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
         <v>523</v>
@@ -9199,10 +9730,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C68" t="s">
         <v>523</v>
@@ -9210,158 +9741,158 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B69" t="s">
-        <v>1078</v>
+        <v>106</v>
+      </c>
+      <c r="C69" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>670</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B71" t="s">
-        <v>671</v>
-      </c>
-      <c r="C71" t="s">
-        <v>523</v>
+        <v>670</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>514</v>
+        <v>196</v>
       </c>
       <c r="B72" t="s">
-        <v>672</v>
+        <v>671</v>
+      </c>
+      <c r="C72" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="B73" t="s">
-        <v>489</v>
+        <v>672</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B74" t="s">
-        <v>1079</v>
+        <v>489</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>631</v>
+        <v>495</v>
       </c>
       <c r="B75" t="s">
-        <v>630</v>
-      </c>
-      <c r="C75" t="s">
-        <v>586</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>1080</v>
+        <v>631</v>
       </c>
       <c r="B76" t="s">
-        <v>1081</v>
+        <v>630</v>
+      </c>
+      <c r="C76" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B78" t="s">
         <v>1073</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B79" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>152</v>
-      </c>
-      <c r="B81" t="s">
-        <v>115</v>
+      <c r="B80" t="s">
+        <v>1151</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B82" t="s">
-        <v>527</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B83" t="s">
-        <v>117</v>
+        <v>527</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>560</v>
+        <v>118</v>
       </c>
       <c r="B84" t="s">
-        <v>561</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>641</v>
+        <v>560</v>
       </c>
       <c r="B85" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1127</v>
+        <v>561</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="B86" t="s">
-        <v>660</v>
+        <v>1129</v>
       </c>
       <c r="C86" t="s">
-        <v>586</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B87" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C87" t="s">
         <v>586</v>
@@ -9369,10 +9900,10 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B88" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C88" t="s">
         <v>586</v>
@@ -9380,37 +9911,37 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
+        <v>657</v>
+      </c>
+      <c r="B89" t="s">
+        <v>662</v>
+      </c>
+      <c r="C89" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
         <v>484</v>
       </c>
-      <c r="B89" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" t="s">
-        <v>180</v>
-      </c>
-      <c r="B91" t="s">
-        <v>976</v>
+      <c r="B90" t="s">
+        <v>1152</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>640</v>
+        <v>180</v>
       </c>
       <c r="B92" t="s">
-        <v>653</v>
-      </c>
-      <c r="C92" t="s">
-        <v>586</v>
+        <v>976</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B93" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="C93" t="s">
         <v>586</v>
@@ -9418,80 +9949,80 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>119</v>
+        <v>638</v>
       </c>
       <c r="B94" t="s">
-        <v>121</v>
+        <v>639</v>
+      </c>
+      <c r="C94" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B95" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B96" t="s">
-        <v>528</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>442</v>
-      </c>
-      <c r="C100" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B101" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C101" t="s">
-        <v>496</v>
+        <v>581</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B102" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C102" t="s">
         <v>496</v>
@@ -9499,48 +10030,48 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>562</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>563</v>
+        <v>445</v>
+      </c>
+      <c r="C103" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>606</v>
+        <v>562</v>
       </c>
       <c r="B104" t="s">
-        <v>607</v>
-      </c>
-      <c r="C104" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>843</v>
+        <v>606</v>
       </c>
       <c r="B105" t="s">
-        <v>844</v>
+        <v>607</v>
+      </c>
+      <c r="C105" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>632</v>
+        <v>843</v>
       </c>
       <c r="B106" t="s">
-        <v>633</v>
-      </c>
-      <c r="C106" t="s">
-        <v>586</v>
+        <v>844</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B107" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C107" t="s">
         <v>586</v>
@@ -9548,10 +10079,10 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B108" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C108" t="s">
         <v>586</v>
@@ -9559,75 +10090,75 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>840</v>
+        <v>637</v>
       </c>
       <c r="B109" t="s">
-        <v>1131</v>
+        <v>636</v>
       </c>
       <c r="C109" t="s">
-        <v>1127</v>
+        <v>586</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B110" t="s">
-        <v>842</v>
+        <v>1130</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B111" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B112" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
+        <v>848</v>
+      </c>
+      <c r="B113" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
         <v>483</v>
       </c>
-      <c r="B113" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C115" t="s">
-        <v>586</v>
+      <c r="B114" t="s">
+        <v>1153</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>141</v>
+        <v>1124</v>
       </c>
       <c r="B116" t="s">
-        <v>144</v>
+        <v>1125</v>
       </c>
       <c r="C116" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B117" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
         <v>579</v>
@@ -9635,10 +10166,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C118" t="s">
         <v>579</v>
@@ -9646,32 +10177,32 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B119" t="s">
-        <v>515</v>
+        <v>146</v>
       </c>
       <c r="C119" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>584</v>
+        <v>139</v>
       </c>
       <c r="B120" t="s">
         <v>515</v>
       </c>
       <c r="C120" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>140</v>
+        <v>584</v>
       </c>
       <c r="B121" t="s">
-        <v>123</v>
+        <v>515</v>
       </c>
       <c r="C121" t="s">
         <v>579</v>
@@ -9679,10 +10210,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B122" t="s">
-        <v>532</v>
+        <v>123</v>
       </c>
       <c r="C122" t="s">
         <v>579</v>
@@ -9690,10 +10221,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B123" t="s">
-        <v>124</v>
+        <v>532</v>
       </c>
       <c r="C123" t="s">
         <v>579</v>
@@ -9701,10 +10232,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>564</v>
+        <v>126</v>
       </c>
       <c r="B124" t="s">
-        <v>565</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
         <v>579</v>
@@ -9712,277 +10243,277 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
+        <v>564</v>
+      </c>
+      <c r="B125" t="s">
+        <v>565</v>
+      </c>
+      <c r="C125" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
         <v>482</v>
       </c>
-      <c r="B125" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" t="s">
-        <v>181</v>
-      </c>
-      <c r="B127" t="s">
-        <v>182</v>
+      <c r="B126" t="s">
+        <v>1154</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="B128" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>683</v>
+        <v>128</v>
       </c>
       <c r="B131" t="s">
-        <v>682</v>
-      </c>
-      <c r="C131" t="s">
-        <v>586</v>
+        <v>149</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>683</v>
       </c>
       <c r="B132" t="s">
-        <v>150</v>
+        <v>682</v>
+      </c>
+      <c r="C132" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B133" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>555</v>
+        <v>131</v>
       </c>
       <c r="B134" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C134" t="s">
-        <v>1127</v>
+        <v>151</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="B135" t="s">
-        <v>567</v>
+        <v>1155</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>608</v>
+        <v>566</v>
       </c>
       <c r="B136" t="s">
-        <v>609</v>
-      </c>
-      <c r="C136" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
+        <v>608</v>
+      </c>
+      <c r="B137" t="s">
+        <v>609</v>
+      </c>
+      <c r="C137" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
         <v>481</v>
       </c>
-      <c r="B137" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" t="s">
-        <v>598</v>
-      </c>
-      <c r="B139" t="s">
-        <v>599</v>
-      </c>
-      <c r="C139" t="s">
-        <v>600</v>
+      <c r="B138" t="s">
+        <v>1156</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B140" t="s">
-        <v>1158</v>
+        <v>599</v>
       </c>
       <c r="C140" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
-      <c r="A142" t="s">
-        <v>153</v>
-      </c>
-      <c r="B142" t="s">
-        <v>157</v>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>601</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C141" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B144" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B145" t="s">
-        <v>533</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>497</v>
+        <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>621</v>
-      </c>
-      <c r="C146" t="s">
-        <v>622</v>
+        <v>533</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>1049</v>
+        <v>497</v>
       </c>
       <c r="B147" t="s">
-        <v>1057</v>
+        <v>621</v>
       </c>
       <c r="C147" t="s">
-        <v>586</v>
+        <v>622</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>572</v>
+        <v>1048</v>
       </c>
       <c r="B148" t="s">
-        <v>573</v>
+        <v>1056</v>
+      </c>
+      <c r="C148" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
+        <v>572</v>
+      </c>
+      <c r="B149" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
         <v>480</v>
       </c>
-      <c r="B149" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
-        <v>185</v>
-      </c>
-      <c r="B151" t="s">
-        <v>186</v>
+      <c r="B150" t="s">
+        <v>1158</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B152" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>568</v>
+        <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>569</v>
+        <v>163</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>479</v>
+        <v>568</v>
       </c>
       <c r="B155" t="s">
-        <v>1160</v>
+        <v>569</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
+        <v>479</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
         <v>610</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>611</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C157" t="s">
         <v>586</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" t="s">
-        <v>183</v>
-      </c>
-      <c r="B158" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>166</v>
-      </c>
-      <c r="C159" t="s">
-        <v>523</v>
+        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C160" t="s">
         <v>523</v>
@@ -9990,10 +10521,10 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B161" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C161" t="s">
         <v>523</v>
@@ -10001,1166 +10532,1166 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="B162" t="s">
-        <v>193</v>
+        <v>168</v>
+      </c>
+      <c r="C162" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B163" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>171</v>
-      </c>
-      <c r="C164" t="s">
-        <v>523</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>570</v>
+        <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>571</v>
+        <v>171</v>
+      </c>
+      <c r="C165" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
+        <v>570</v>
+      </c>
+      <c r="B166" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
         <v>468</v>
       </c>
-      <c r="B166" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C166" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B168" t="s">
-        <v>759</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1072</v>
+      <c r="B167" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>576</v>
+        <v>1070</v>
       </c>
       <c r="B169" t="s">
-        <v>820</v>
+        <v>759</v>
       </c>
       <c r="C169" t="s">
-        <v>1132</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>613</v>
+        <v>576</v>
       </c>
       <c r="B170" t="s">
-        <v>614</v>
+        <v>820</v>
       </c>
       <c r="C170" t="s">
-        <v>586</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
       <c r="B171" t="s">
-        <v>821</v>
+        <v>614</v>
       </c>
       <c r="C171" t="s">
-        <v>1132</v>
+        <v>586</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B172" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C172" t="s">
-        <v>586</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B173" t="s">
-        <v>1145</v>
+        <v>822</v>
       </c>
       <c r="C173" t="s">
-        <v>1127</v>
+        <v>586</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
+        <v>693</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
         <v>1044</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B175" t="s">
         <v>827</v>
       </c>
-      <c r="C174" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" t="s">
-        <v>459</v>
-      </c>
-      <c r="B176" t="s">
-        <v>1085</v>
+      <c r="C175" t="s">
+        <v>1083</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>1058</v>
+        <v>459</v>
       </c>
       <c r="B177" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C177" t="s">
-        <v>1060</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>233</v>
+        <v>1057</v>
       </c>
       <c r="B178" t="s">
-        <v>823</v>
+        <v>1058</v>
       </c>
       <c r="C178" t="s">
-        <v>523</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B179" t="s">
-        <v>824</v>
+        <v>823</v>
+      </c>
+      <c r="C179" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B180" t="s">
-        <v>825</v>
-      </c>
-      <c r="C180" t="s">
-        <v>575</v>
+        <v>824</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>667</v>
+        <v>242</v>
       </c>
       <c r="B181" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C181" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>236</v>
+        <v>667</v>
       </c>
       <c r="B182" t="s">
-        <v>235</v>
+        <v>826</v>
+      </c>
+      <c r="C182" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>449</v>
+        <v>236</v>
       </c>
       <c r="B183" t="s">
-        <v>458</v>
+        <v>235</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>237</v>
+        <v>449</v>
       </c>
       <c r="B184" t="s">
-        <v>827</v>
-      </c>
-      <c r="C184" t="s">
-        <v>1086</v>
+        <v>458</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B185" t="s">
-        <v>828</v>
+        <v>827</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B186" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B187" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B188" t="s">
-        <v>759</v>
+        <v>830</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="B189" t="s">
-        <v>827</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1086</v>
+        <v>759</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="B190" t="s">
-        <v>299</v>
+        <v>827</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>578</v>
+        <v>298</v>
       </c>
       <c r="B191" t="s">
-        <v>1043</v>
+        <v>299</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="B192" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C192" t="s">
-        <v>1127</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>654</v>
+        <v>591</v>
       </c>
       <c r="B193" t="s">
-        <v>655</v>
+        <v>1132</v>
       </c>
       <c r="C193" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="B194" t="s">
-        <v>1162</v>
+        <v>655</v>
       </c>
       <c r="C194" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>839</v>
+        <v>666</v>
       </c>
       <c r="B195" t="s">
-        <v>1134</v>
+        <v>1161</v>
       </c>
       <c r="C195" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>1087</v>
+        <v>839</v>
       </c>
       <c r="B196" t="s">
-        <v>1088</v>
+        <v>1133</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" t="s">
         <v>467</v>
       </c>
-      <c r="B197" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C197" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" t="s">
-        <v>665</v>
-      </c>
-      <c r="B199" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C199" t="s">
-        <v>1127</v>
+      <c r="B198" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>460</v>
+        <v>665</v>
       </c>
       <c r="B200" t="s">
-        <v>1089</v>
+        <v>1163</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
+        <v>460</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
         <v>243</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B202" t="s">
         <v>831</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C202" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="13.5" customHeight="1">
-      <c r="A202" t="s">
+    <row r="203" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A203" t="s">
         <v>245</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B203" t="s">
         <v>832</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C203" t="s">
         <v>588</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" t="s">
-        <v>244</v>
-      </c>
-      <c r="B203" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B204" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1127</v>
+        <v>794</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B205" t="s">
-        <v>248</v>
+        <v>1164</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B206" t="s">
-        <v>249</v>
-      </c>
-      <c r="C206" t="s">
-        <v>580</v>
+        <v>248</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="B207" t="s">
-        <v>505</v>
+        <v>249</v>
+      </c>
+      <c r="C207" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>251</v>
+        <v>450</v>
       </c>
       <c r="B208" t="s">
-        <v>796</v>
+        <v>505</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B209" t="s">
-        <v>253</v>
+        <v>796</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B210" t="s">
-        <v>797</v>
+        <v>253</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B211" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B212" t="s">
-        <v>833</v>
-      </c>
-      <c r="C212" t="s">
-        <v>580</v>
+        <v>798</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B213" t="s">
-        <v>799</v>
+        <v>833</v>
+      </c>
+      <c r="C213" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B214" t="s">
-        <v>834</v>
-      </c>
-      <c r="C214" t="s">
-        <v>580</v>
+        <v>799</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B215" t="s">
-        <v>800</v>
+        <v>834</v>
+      </c>
+      <c r="C215" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B216" t="s">
-        <v>270</v>
+        <v>800</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B217" t="s">
-        <v>827</v>
-      </c>
-      <c r="C217" t="s">
-        <v>1086</v>
+        <v>270</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B218" t="s">
-        <v>1166</v>
+        <v>827</v>
       </c>
       <c r="C218" t="s">
-        <v>1127</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>592</v>
+        <v>273</v>
       </c>
       <c r="B219" t="s">
-        <v>1133</v>
+        <v>1165</v>
       </c>
       <c r="C219" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B220" t="s">
-        <v>1167</v>
+        <v>1132</v>
       </c>
       <c r="C220" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
+        <v>589</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" t="s">
         <v>478</v>
       </c>
-      <c r="B221" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C221" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223" t="s">
-        <v>461</v>
-      </c>
-      <c r="B223" t="s">
-        <v>1090</v>
+      <c r="B222" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B224" t="s">
-        <v>506</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>267</v>
+        <v>451</v>
       </c>
       <c r="B225" t="s">
-        <v>760</v>
+        <v>506</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B226" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B227" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B228" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B229" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>593</v>
+        <v>276</v>
       </c>
       <c r="B230" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C230" t="s">
-        <v>1127</v>
+        <v>763</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
+        <v>593</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C231" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" t="s">
         <v>477</v>
       </c>
-      <c r="B231" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C231" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233" t="s">
-        <v>462</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1091</v>
+      <c r="B232" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C232" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B234" t="s">
-        <v>507</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>279</v>
+        <v>452</v>
       </c>
       <c r="B235" t="s">
-        <v>754</v>
+        <v>507</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B236" t="s">
-        <v>282</v>
+        <v>754</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B237" t="s">
-        <v>755</v>
+        <v>282</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B238" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B239" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B240" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B241" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>594</v>
+        <v>286</v>
       </c>
       <c r="B242" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C242" t="s">
-        <v>1127</v>
+        <v>759</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>1135</v>
+        <v>594</v>
       </c>
       <c r="B243" t="s">
-        <v>1136</v>
+        <v>1132</v>
+      </c>
+      <c r="C243" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" t="s">
         <v>476</v>
       </c>
-      <c r="B244" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C244" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" t="s">
-        <v>463</v>
-      </c>
-      <c r="B246" t="s">
-        <v>1092</v>
+      <c r="B245" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="B247" t="s">
-        <v>292</v>
-      </c>
-      <c r="C247" t="s">
-        <v>523</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B248" t="s">
-        <v>508</v>
+        <v>292</v>
+      </c>
+      <c r="C248" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>290</v>
+        <v>453</v>
       </c>
       <c r="B249" t="s">
-        <v>835</v>
-      </c>
-      <c r="C249" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B250" t="s">
-        <v>818</v>
+        <v>835</v>
+      </c>
+      <c r="C250" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>446</v>
+        <v>291</v>
       </c>
       <c r="B251" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>293</v>
+        <v>446</v>
       </c>
       <c r="B252" t="s">
-        <v>827</v>
-      </c>
-      <c r="C252" t="s">
-        <v>1093</v>
+        <v>819</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B253" t="s">
-        <v>836</v>
+        <v>827</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1092</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B254" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B255" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B256" t="s">
-        <v>759</v>
+        <v>838</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>595</v>
+        <v>297</v>
       </c>
       <c r="B257" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C257" t="s">
-        <v>1127</v>
+        <v>759</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
+        <v>595</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C258" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" t="s">
         <v>475</v>
       </c>
-      <c r="B258" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C258" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3">
-      <c r="A260" t="s">
-        <v>627</v>
-      </c>
-      <c r="B260" t="s">
-        <v>628</v>
-      </c>
-      <c r="C260" t="s">
-        <v>586</v>
+      <c r="B259" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C259" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>492</v>
+        <v>627</v>
       </c>
       <c r="B261" t="s">
-        <v>1198</v>
+        <v>628</v>
       </c>
       <c r="C261" t="s">
-        <v>521</v>
+        <v>586</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B262" t="s">
-        <v>494</v>
+        <v>1197</v>
       </c>
       <c r="C262" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="B263" t="s">
-        <v>534</v>
+        <v>494</v>
+      </c>
+      <c r="C263" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>313</v>
+        <v>520</v>
       </c>
       <c r="B264" t="s">
-        <v>300</v>
+        <v>534</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B265" t="s">
-        <v>301</v>
-      </c>
-      <c r="C265" t="s">
-        <v>523</v>
+        <v>300</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>454</v>
+        <v>314</v>
       </c>
       <c r="B266" t="s">
-        <v>509</v>
+        <v>301</v>
+      </c>
+      <c r="C266" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>315</v>
+        <v>454</v>
       </c>
       <c r="B267" t="s">
-        <v>302</v>
+        <v>509</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B268" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B269" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B270" t="s">
-        <v>305</v>
-      </c>
-      <c r="C270" t="s">
-        <v>523</v>
+        <v>304</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B271" t="s">
-        <v>306</v>
+        <v>305</v>
+      </c>
+      <c r="C271" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B272" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B273" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B274" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B275" t="s">
-        <v>310</v>
-      </c>
-      <c r="C275" t="s">
-        <v>523</v>
+        <v>309</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B276" t="s">
-        <v>738</v>
+        <v>310</v>
+      </c>
+      <c r="C276" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B277" t="s">
-        <v>311</v>
+        <v>738</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B278" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
+        <v>326</v>
+      </c>
+      <c r="B279" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" t="s">
         <v>474</v>
       </c>
-      <c r="B279" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C279" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" t="s">
-        <v>538</v>
-      </c>
-      <c r="B281" t="s">
-        <v>539</v>
+      <c r="B280" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C280" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>333</v>
+        <v>538</v>
       </c>
       <c r="B282" t="s">
-        <v>351</v>
+        <v>539</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B283" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B284" t="s">
-        <v>349</v>
-      </c>
-      <c r="C284" t="s">
-        <v>523</v>
+        <v>348</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>455</v>
+        <v>335</v>
       </c>
       <c r="B285" t="s">
-        <v>510</v>
+        <v>349</v>
+      </c>
+      <c r="C285" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>352</v>
+        <v>455</v>
       </c>
       <c r="B286" t="s">
-        <v>350</v>
-      </c>
-      <c r="C286" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B287" t="s">
-        <v>342</v>
+        <v>350</v>
+      </c>
+      <c r="C287" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="B288" t="s">
-        <v>343</v>
-      </c>
-      <c r="C288" t="s">
-        <v>500</v>
+        <v>342</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="B289" t="s">
-        <v>344</v>
+        <v>343</v>
+      </c>
+      <c r="C289" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B290" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B291" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B292" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B293" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>1031</v>
+        <v>341</v>
       </c>
       <c r="B294" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C294" t="s">
-        <v>1033</v>
+        <v>344</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B295" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="C295" t="s">
         <v>1033</v>
@@ -11168,10 +11699,10 @@
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B296" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C296" t="s">
         <v>1033</v>
@@ -11179,130 +11710,130 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1094</v>
+        <v>1036</v>
       </c>
       <c r="B297" t="s">
-        <v>1095</v>
+        <v>1037</v>
+      </c>
+      <c r="C297" t="s">
+        <v>1033</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" t="s">
         <v>473</v>
       </c>
-      <c r="B298" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C298" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300" t="s">
-        <v>629</v>
-      </c>
-      <c r="B300" t="s">
-        <v>646</v>
-      </c>
-      <c r="C300" t="s">
-        <v>586</v>
+      <c r="B299" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C299" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>1038</v>
+        <v>629</v>
       </c>
       <c r="B301" t="s">
-        <v>1137</v>
+        <v>646</v>
       </c>
       <c r="C301" t="s">
-        <v>1127</v>
+        <v>586</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B302" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C302" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C303" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" t="s">
         <v>1040</v>
       </c>
-      <c r="B303" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C303" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3">
-      <c r="A305" t="s">
-        <v>625</v>
-      </c>
-      <c r="B305" t="s">
-        <v>626</v>
-      </c>
-      <c r="C305" t="s">
-        <v>586</v>
+      <c r="B304" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>464</v>
+        <v>625</v>
       </c>
       <c r="B306" t="s">
-        <v>465</v>
+        <v>626</v>
+      </c>
+      <c r="C306" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>359</v>
+        <v>464</v>
       </c>
       <c r="B307" t="s">
-        <v>370</v>
+        <v>465</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B308" t="s">
-        <v>371</v>
-      </c>
-      <c r="C308" t="s">
-        <v>523</v>
+        <v>370</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>511</v>
+        <v>360</v>
       </c>
       <c r="B309" t="s">
-        <v>512</v>
+        <v>371</v>
+      </c>
+      <c r="C309" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>361</v>
+        <v>511</v>
       </c>
       <c r="B310" t="s">
-        <v>372</v>
-      </c>
-      <c r="C310" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B311" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C311" t="s">
         <v>523</v>
@@ -11310,161 +11841,161 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B312" t="s">
-        <v>524</v>
+        <v>373</v>
+      </c>
+      <c r="C312" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B313" t="s">
-        <v>374</v>
+        <v>524</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B314" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B315" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B316" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B317" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B318" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>680</v>
+        <v>369</v>
       </c>
       <c r="B319" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C319" t="s">
-        <v>1127</v>
+        <v>379</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>1052</v>
+        <v>680</v>
       </c>
       <c r="B320" t="s">
-        <v>1053</v>
+        <v>1138</v>
+      </c>
+      <c r="C320" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>547</v>
+        <v>1051</v>
       </c>
       <c r="B321" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C321" t="s">
-        <v>1127</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>1096</v>
+        <v>547</v>
       </c>
       <c r="B322" t="s">
-        <v>1097</v>
+        <v>1174</v>
+      </c>
+      <c r="C322" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B323" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" t="s">
         <v>471</v>
       </c>
-      <c r="B323" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C323" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3">
-      <c r="A325" t="s">
-        <v>466</v>
-      </c>
-      <c r="B325" t="s">
-        <v>465</v>
+      <c r="B324" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C324" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>386</v>
+        <v>466</v>
       </c>
       <c r="B326" t="s">
-        <v>397</v>
+        <v>465</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B327" t="s">
-        <v>398</v>
-      </c>
-      <c r="C327" t="s">
-        <v>523</v>
+        <v>397</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>456</v>
+        <v>387</v>
       </c>
       <c r="B328" t="s">
-        <v>513</v>
+        <v>398</v>
+      </c>
+      <c r="C328" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="B329" t="s">
-        <v>399</v>
-      </c>
-      <c r="C329" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B330" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C330" t="s">
         <v>523</v>
@@ -11472,1525 +12003,2256 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B331" t="s">
-        <v>525</v>
+        <v>400</v>
+      </c>
+      <c r="C331" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B332" t="s">
-        <v>374</v>
+        <v>525</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B333" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B334" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B335" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B336" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B337" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>553</v>
+        <v>396</v>
       </c>
       <c r="B338" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C338" t="s">
-        <v>1127</v>
+        <v>379</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>1098</v>
+        <v>553</v>
       </c>
       <c r="B339" t="s">
-        <v>1099</v>
+        <v>1174</v>
+      </c>
+      <c r="C339" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" t="s">
         <v>470</v>
       </c>
-      <c r="B340" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C340" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3">
-      <c r="A342" t="s">
-        <v>623</v>
-      </c>
-      <c r="B342" t="s">
-        <v>624</v>
-      </c>
-      <c r="C342" t="s">
-        <v>586</v>
+      <c r="B341" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C341" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>380</v>
+        <v>623</v>
       </c>
       <c r="B343" t="s">
-        <v>1200</v>
+        <v>624</v>
+      </c>
+      <c r="C343" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B344" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C344" t="s">
-        <v>523</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>457</v>
+        <v>381</v>
       </c>
       <c r="B345" t="s">
-        <v>1202</v>
+        <v>1200</v>
+      </c>
+      <c r="C345" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>382</v>
+        <v>457</v>
       </c>
       <c r="B346" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B347" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B348" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>1066</v>
+        <v>384</v>
       </c>
       <c r="B349" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C349" t="s">
-        <v>1100</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C350" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" t="s">
         <v>469</v>
       </c>
-      <c r="B350" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3">
-      <c r="A352" t="s">
-        <v>688</v>
-      </c>
-      <c r="B352" t="s">
-        <v>689</v>
-      </c>
-      <c r="C352" t="s">
-        <v>586</v>
+      <c r="B351" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C351" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
+        <v>688</v>
+      </c>
+      <c r="B353" t="s">
+        <v>689</v>
+      </c>
+      <c r="C353" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" t="s">
         <v>690</v>
       </c>
-      <c r="B353" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C353" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3">
-      <c r="A355" t="s">
-        <v>696</v>
-      </c>
-      <c r="B355" t="s">
-        <v>697</v>
+      <c r="B354" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C354" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B356" t="s">
-        <v>1199</v>
+        <v>697</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B357" t="s">
-        <v>700</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B358" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B359" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B360" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B361" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B362" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B363" t="s">
-        <v>1101</v>
+        <v>710</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B364" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C364" t="s">
-        <v>1127</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B365" t="s">
-        <v>714</v>
+        <v>1177</v>
+      </c>
+      <c r="C365" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B366" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B367" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B368" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B369" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B370" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>1062</v>
+        <v>723</v>
       </c>
       <c r="B371" t="s">
-        <v>1063</v>
+        <v>724</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>725</v>
+        <v>1061</v>
       </c>
       <c r="B372" t="s">
-        <v>726</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>1102</v>
+        <v>725</v>
       </c>
       <c r="B373" t="s">
-        <v>1103</v>
+        <v>726</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>1065</v>
+        <v>1101</v>
       </c>
       <c r="B374" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C374" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3">
-      <c r="A376" t="s">
-        <v>727</v>
-      </c>
-      <c r="B376" t="s">
-        <v>728</v>
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B377" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B378" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B379" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B380" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B381" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B382" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B383" t="s">
-        <v>312</v>
+        <v>740</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B384" t="s">
-        <v>743</v>
+        <v>312</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B385" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B386" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
+        <v>746</v>
+      </c>
+      <c r="B387" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" t="s">
         <v>748</v>
       </c>
-      <c r="B387" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C387" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3">
-      <c r="A389" t="s">
-        <v>749</v>
-      </c>
-      <c r="B389" t="s">
-        <v>306</v>
+      <c r="B388" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C388" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B390" t="s">
-        <v>751</v>
+        <v>306</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B391" t="s">
-        <v>308</v>
+        <v>751</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
+        <v>752</v>
+      </c>
+      <c r="B392" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393" t="s">
         <v>753</v>
       </c>
-      <c r="B392" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3">
-      <c r="A394" t="s">
-        <v>774</v>
-      </c>
-      <c r="B394" t="s">
-        <v>775</v>
+      <c r="B393" t="s">
+        <v>1103</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B395" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B396" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B397" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B398" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
+        <v>766</v>
+      </c>
+      <c r="B399" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400" t="s">
         <v>771</v>
       </c>
-      <c r="B399" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C399" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3">
-      <c r="A401" t="s">
-        <v>778</v>
-      </c>
-      <c r="B401" t="s">
-        <v>783</v>
+      <c r="B400" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C400" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="B402" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B403" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B404" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B405" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
+        <v>781</v>
+      </c>
+      <c r="B406" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407" t="s">
         <v>782</v>
       </c>
-      <c r="B406" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C406" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3">
-      <c r="A408" t="s">
-        <v>790</v>
-      </c>
-      <c r="B408" t="s">
-        <v>791</v>
+      <c r="B407" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C407" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B409" t="s">
-        <v>1061</v>
+        <v>791</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B410" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C410" t="s">
-        <v>1127</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B411" t="s">
-        <v>978</v>
+        <v>1163</v>
+      </c>
+      <c r="C411" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="B412" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C412" t="s">
-        <v>1127</v>
+        <v>978</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B413" t="s">
-        <v>979</v>
+        <v>1182</v>
+      </c>
+      <c r="C413" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B414" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B415" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B416" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B417" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B418" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B419" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B420" t="s">
-        <v>800</v>
+        <v>985</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B421" t="s">
-        <v>986</v>
+        <v>800</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B422" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C422" t="s">
-        <v>1127</v>
+        <v>986</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B423" t="s">
-        <v>1133</v>
+        <v>1165</v>
       </c>
       <c r="C423" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="B424" t="s">
-        <v>1167</v>
+        <v>1132</v>
       </c>
       <c r="C424" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B425" t="s">
-        <v>1184</v>
+        <v>1166</v>
       </c>
       <c r="C425" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>1105</v>
+        <v>804</v>
       </c>
       <c r="B426" t="s">
-        <v>1088</v>
+        <v>1183</v>
+      </c>
+      <c r="C426" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>987</v>
+        <v>1104</v>
       </c>
       <c r="B427" t="s">
-        <v>988</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B428" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B429" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B430" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B431" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B432" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B433" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B434" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C434" t="s">
-        <v>1127</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>1070</v>
+        <v>1001</v>
       </c>
       <c r="B435" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3">
-      <c r="A437" t="s">
-        <v>851</v>
-      </c>
-      <c r="B437" t="s">
-        <v>852</v>
+        <v>1139</v>
+      </c>
+      <c r="C435" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3">
+      <c r="A436" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B438" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B439" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B440" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B441" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B442" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B443" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B444" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B445" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B446" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B447" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B448" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B449" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B450" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B451" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B452" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C452" t="s">
-        <v>1127</v>
+        <v>880</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B453" t="s">
-        <v>883</v>
+        <v>1140</v>
+      </c>
+      <c r="C453" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B454" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B455" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B456" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>1107</v>
+        <v>888</v>
       </c>
       <c r="B457" t="s">
-        <v>1108</v>
+        <v>889</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3">
+      <c r="A459" t="s">
         <v>890</v>
       </c>
-      <c r="B458" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C458" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3">
-      <c r="A460" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B460" t="s">
-        <v>1069</v>
+      <c r="B459" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C459" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>891</v>
+        <v>1067</v>
       </c>
       <c r="B461" t="s">
-        <v>892</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B462" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B463" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B464" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B465" t="s">
-        <v>1109</v>
+        <v>898</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B466" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B467" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B468" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B469" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>1114</v>
+        <v>903</v>
       </c>
       <c r="B470" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3">
+      <c r="A472" t="s">
         <v>904</v>
       </c>
-      <c r="B471" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C471" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3">
-      <c r="A473" t="s">
-        <v>911</v>
-      </c>
-      <c r="B473" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C473" t="s">
-        <v>1127</v>
+      <c r="B472" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
+        <v>911</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3">
+      <c r="A475" t="s">
         <v>912</v>
       </c>
-      <c r="B474" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C474" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3">
-      <c r="A476" t="s">
-        <v>913</v>
-      </c>
-      <c r="B476" t="s">
-        <v>914</v>
-      </c>
-      <c r="C476" t="s">
-        <v>1132</v>
+      <c r="B475" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
+        <v>913</v>
+      </c>
+      <c r="B477" t="s">
+        <v>914</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3">
+      <c r="A478" t="s">
         <v>915</v>
       </c>
-      <c r="B477" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C477" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3">
-      <c r="A479" t="s">
-        <v>916</v>
-      </c>
-      <c r="B479" t="s">
-        <v>917</v>
+      <c r="B478" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B480" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>1116</v>
+        <v>918</v>
       </c>
       <c r="B481" t="s">
-        <v>1117</v>
+        <v>919</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3">
+      <c r="A483" t="s">
         <v>920</v>
       </c>
-      <c r="B482" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C482" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3">
-      <c r="A484" t="s">
-        <v>921</v>
-      </c>
-      <c r="B484" t="s">
-        <v>1194</v>
+      <c r="B483" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C483" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B485" t="s">
-        <v>923</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B486" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B487" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B488" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B489" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
+        <v>930</v>
+      </c>
+      <c r="B490" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3">
+      <c r="A491" t="s">
         <v>932</v>
       </c>
-      <c r="B490" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C490" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3">
-      <c r="A492" t="s">
-        <v>933</v>
-      </c>
-      <c r="B492" t="s">
-        <v>934</v>
+      <c r="B491" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C491" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="493" spans="1:3">
       <c r="A493" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B493" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B494" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B495" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B496" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
+        <v>941</v>
+      </c>
+      <c r="B497" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3">
+      <c r="A498" t="s">
         <v>943</v>
       </c>
-      <c r="B497" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C497" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3">
-      <c r="A499" t="s">
-        <v>944</v>
-      </c>
-      <c r="B499" t="s">
-        <v>945</v>
+      <c r="B498" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="500" spans="1:3">
       <c r="A500" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B500" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B501" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B502" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B503" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
+        <v>952</v>
+      </c>
+      <c r="B504" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3">
+      <c r="A505" t="s">
         <v>954</v>
       </c>
-      <c r="B504" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C504" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3">
-      <c r="A506" t="s">
-        <v>955</v>
-      </c>
-      <c r="B506" t="s">
-        <v>956</v>
-      </c>
-      <c r="C506" t="s">
-        <v>1132</v>
+      <c r="B505" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="507" spans="1:3">
       <c r="A507" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B507" t="s">
-        <v>958</v>
+        <v>956</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B508" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B509" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
+        <v>961</v>
+      </c>
+      <c r="B510" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3">
+      <c r="A511" t="s">
         <v>963</v>
       </c>
-      <c r="B510" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3">
-      <c r="A512" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B512" t="s">
-        <v>1003</v>
+      <c r="B511" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B513" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B514" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B515" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B516" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B517" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B518" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B519" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B520" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B521" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B522" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B523" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B524" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3">
+      <c r="A526" t="s">
         <v>1028</v>
       </c>
-      <c r="B525" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C525" t="s">
-        <v>1127</v>
+      <c r="B526" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B591" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B600" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1392</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C525" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
-  <conditionalFormatting sqref="A478:A479 A475:A476 A460:A470 A472:A473 A481">
+  <autoFilter ref="A1:C526" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
+  <conditionalFormatting sqref="A479:A480 A476:A477 A461:A471 A473:A474 A482">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1021\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C9A896-13B7-4735-994D-6A24A709304F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C95A81-3FFE-4B5E-99F4-FA412CBFA5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Findings" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$526</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$527</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="1396">
   <si>
     <t>Name</t>
   </si>
@@ -4222,6 +4222,15 @@
   </si>
   <si>
     <t>Unable to validate findings for Certification Questionnaire. Manual review is needed. </t>
+  </si>
+  <si>
+    <t>ICW_IncomeNearLimit</t>
+  </si>
+  <si>
+    <t>Annual Income is within $2000 of the Income Limit listed on the Income Calculation Worksheet. Manual review needed.</t>
+  </si>
+  <si>
+    <t>Newly added by Harman</t>
   </si>
 </sst>
 </file>
@@ -9168,7 +9177,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C617"/>
+  <dimension ref="A1:C618"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -9421,127 +9430,127 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>175</v>
-      </c>
-      <c r="B31" t="s">
-        <v>176</v>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1395</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>498</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>499</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>498</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>499</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>1075</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>673</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>674</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>556</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s">
-        <v>557</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="B43" t="s">
-        <v>681</v>
+        <v>557</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="B44" t="s">
-        <v>605</v>
-      </c>
-      <c r="C44" t="s">
-        <v>586</v>
+        <v>681</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>678</v>
+        <v>604</v>
       </c>
       <c r="B45" t="s">
-        <v>679</v>
+        <v>605</v>
       </c>
       <c r="C45" t="s">
         <v>586</v>
@@ -9549,158 +9558,158 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>678</v>
+      </c>
+      <c r="B46" t="s">
+        <v>679</v>
+      </c>
+      <c r="C46" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>487</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>1148</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>177</v>
-      </c>
-      <c r="B48" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s">
-        <v>1076</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" t="s">
-        <v>523</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="C56" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>558</v>
+        <v>101</v>
       </c>
       <c r="B57" t="s">
-        <v>559</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>668</v>
+        <v>558</v>
       </c>
       <c r="B58" t="s">
-        <v>669</v>
+        <v>559</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>1029</v>
+        <v>668</v>
       </c>
       <c r="B59" t="s">
-        <v>1030</v>
+        <v>669</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>587</v>
+        <v>1029</v>
       </c>
       <c r="B60" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1126</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>486</v>
+        <v>587</v>
       </c>
       <c r="B61" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C61" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>178</v>
-      </c>
-      <c r="B63" t="s">
-        <v>526</v>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>486</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C65" t="s">
         <v>523</v>
@@ -9708,10 +9717,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
         <v>523</v>
@@ -9719,10 +9728,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C67" t="s">
         <v>523</v>
@@ -9730,10 +9739,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
         <v>523</v>
@@ -9741,10 +9750,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C69" t="s">
         <v>523</v>
@@ -9752,158 +9761,158 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B70" t="s">
-        <v>1077</v>
+        <v>106</v>
+      </c>
+      <c r="C70" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>670</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B72" t="s">
-        <v>671</v>
-      </c>
-      <c r="C72" t="s">
-        <v>523</v>
+        <v>670</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>514</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s">
-        <v>672</v>
+        <v>671</v>
+      </c>
+      <c r="C73" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="B74" t="s">
-        <v>489</v>
+        <v>672</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s">
-        <v>1078</v>
+        <v>489</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>631</v>
+        <v>495</v>
       </c>
       <c r="B76" t="s">
-        <v>630</v>
-      </c>
-      <c r="C76" t="s">
-        <v>586</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>1079</v>
+        <v>631</v>
       </c>
       <c r="B77" t="s">
-        <v>1080</v>
+        <v>630</v>
+      </c>
+      <c r="C77" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
         <v>1072</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>1073</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>1151</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" t="s">
-        <v>152</v>
-      </c>
-      <c r="B82" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B83" t="s">
-        <v>527</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B84" t="s">
-        <v>117</v>
+        <v>527</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>560</v>
+        <v>118</v>
       </c>
       <c r="B85" t="s">
-        <v>561</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>641</v>
+        <v>560</v>
       </c>
       <c r="B86" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1126</v>
+        <v>561</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="B87" t="s">
-        <v>660</v>
+        <v>1129</v>
       </c>
       <c r="C87" t="s">
-        <v>586</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B88" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C88" t="s">
         <v>586</v>
@@ -9911,10 +9920,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B89" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C89" t="s">
         <v>586</v>
@@ -9922,37 +9931,37 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
+        <v>657</v>
+      </c>
+      <c r="B90" t="s">
+        <v>662</v>
+      </c>
+      <c r="C90" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
         <v>484</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>1152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
-        <v>180</v>
-      </c>
-      <c r="B92" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>640</v>
+        <v>180</v>
       </c>
       <c r="B93" t="s">
-        <v>653</v>
-      </c>
-      <c r="C93" t="s">
-        <v>586</v>
+        <v>976</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B94" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="C94" t="s">
         <v>586</v>
@@ -9960,80 +9969,80 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>638</v>
       </c>
       <c r="B95" t="s">
-        <v>121</v>
+        <v>639</v>
+      </c>
+      <c r="C95" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B96" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B97" t="s">
-        <v>528</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B98" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B99" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B100" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B101" t="s">
-        <v>442</v>
-      </c>
-      <c r="C101" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B102" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C102" t="s">
-        <v>496</v>
+        <v>581</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B103" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C103" t="s">
         <v>496</v>
@@ -10041,48 +10050,48 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>562</v>
+        <v>138</v>
       </c>
       <c r="B104" t="s">
-        <v>563</v>
+        <v>445</v>
+      </c>
+      <c r="C104" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>606</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s">
-        <v>607</v>
-      </c>
-      <c r="C105" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>843</v>
+        <v>606</v>
       </c>
       <c r="B106" t="s">
-        <v>844</v>
+        <v>607</v>
+      </c>
+      <c r="C106" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>632</v>
+        <v>843</v>
       </c>
       <c r="B107" t="s">
-        <v>633</v>
-      </c>
-      <c r="C107" t="s">
-        <v>586</v>
+        <v>844</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B108" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C108" t="s">
         <v>586</v>
@@ -10090,10 +10099,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B109" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C109" t="s">
         <v>586</v>
@@ -10101,75 +10110,75 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>840</v>
+        <v>637</v>
       </c>
       <c r="B110" t="s">
-        <v>1130</v>
+        <v>636</v>
       </c>
       <c r="C110" t="s">
-        <v>1126</v>
+        <v>586</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B111" t="s">
-        <v>842</v>
+        <v>1130</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B112" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B113" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
+        <v>848</v>
+      </c>
+      <c r="B114" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
         <v>483</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B115" t="s">
         <v>1153</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C116" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>141</v>
+        <v>1124</v>
       </c>
       <c r="B117" t="s">
-        <v>144</v>
+        <v>1125</v>
       </c>
       <c r="C117" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C118" t="s">
         <v>579</v>
@@ -10177,10 +10186,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C119" t="s">
         <v>579</v>
@@ -10188,32 +10197,32 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B120" t="s">
-        <v>515</v>
+        <v>146</v>
       </c>
       <c r="C120" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>584</v>
+        <v>139</v>
       </c>
       <c r="B121" t="s">
         <v>515</v>
       </c>
       <c r="C121" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>584</v>
       </c>
       <c r="B122" t="s">
-        <v>123</v>
+        <v>515</v>
       </c>
       <c r="C122" t="s">
         <v>579</v>
@@ -10221,10 +10230,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>532</v>
+        <v>123</v>
       </c>
       <c r="C123" t="s">
         <v>579</v>
@@ -10232,10 +10241,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>532</v>
       </c>
       <c r="C124" t="s">
         <v>579</v>
@@ -10243,10 +10252,10 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>564</v>
+        <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>565</v>
+        <v>124</v>
       </c>
       <c r="C125" t="s">
         <v>579</v>
@@ -10254,277 +10263,277 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
+        <v>564</v>
+      </c>
+      <c r="B126" t="s">
+        <v>565</v>
+      </c>
+      <c r="C126" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
         <v>482</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B127" t="s">
         <v>1154</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" t="s">
-        <v>181</v>
-      </c>
-      <c r="B128" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="B129" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B130" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>683</v>
+        <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>682</v>
-      </c>
-      <c r="C132" t="s">
-        <v>586</v>
+        <v>149</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>683</v>
       </c>
       <c r="B133" t="s">
-        <v>150</v>
+        <v>682</v>
+      </c>
+      <c r="C133" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>555</v>
+        <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C135" t="s">
-        <v>1126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="B136" t="s">
-        <v>567</v>
+        <v>1155</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>608</v>
+        <v>566</v>
       </c>
       <c r="B137" t="s">
-        <v>609</v>
-      </c>
-      <c r="C137" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
+        <v>608</v>
+      </c>
+      <c r="B138" t="s">
+        <v>609</v>
+      </c>
+      <c r="C138" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
         <v>481</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B139" t="s">
         <v>1156</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" t="s">
-        <v>598</v>
-      </c>
-      <c r="B140" t="s">
-        <v>599</v>
-      </c>
-      <c r="C140" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B141" t="s">
-        <v>1157</v>
+        <v>599</v>
       </c>
       <c r="C141" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
-      <c r="A143" t="s">
-        <v>153</v>
-      </c>
-      <c r="B143" t="s">
-        <v>157</v>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>601</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C142" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B145" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B146" t="s">
-        <v>533</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>497</v>
+        <v>156</v>
       </c>
       <c r="B147" t="s">
-        <v>621</v>
-      </c>
-      <c r="C147" t="s">
-        <v>622</v>
+        <v>533</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>1048</v>
+        <v>497</v>
       </c>
       <c r="B148" t="s">
-        <v>1056</v>
+        <v>621</v>
       </c>
       <c r="C148" t="s">
-        <v>586</v>
+        <v>622</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>572</v>
+        <v>1048</v>
       </c>
       <c r="B149" t="s">
-        <v>573</v>
+        <v>1056</v>
+      </c>
+      <c r="C149" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
+        <v>572</v>
+      </c>
+      <c r="B150" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
         <v>480</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B151" t="s">
         <v>1158</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" t="s">
-        <v>185</v>
-      </c>
-      <c r="B152" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B153" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B154" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>568</v>
+        <v>161</v>
       </c>
       <c r="B155" t="s">
-        <v>569</v>
+        <v>163</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>479</v>
+        <v>568</v>
       </c>
       <c r="B156" t="s">
-        <v>1159</v>
+        <v>569</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
+        <v>479</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
         <v>610</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>611</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C158" t="s">
         <v>586</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" t="s">
-        <v>183</v>
-      </c>
-      <c r="B159" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B160" t="s">
-        <v>166</v>
-      </c>
-      <c r="C160" t="s">
-        <v>523</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B161" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C161" t="s">
         <v>523</v>
@@ -10532,10 +10541,10 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B162" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C162" t="s">
         <v>523</v>
@@ -10543,312 +10552,312 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="B163" t="s">
-        <v>193</v>
+        <v>168</v>
+      </c>
+      <c r="C163" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B164" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B165" t="s">
-        <v>171</v>
-      </c>
-      <c r="C165" t="s">
-        <v>523</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>570</v>
+        <v>170</v>
       </c>
       <c r="B166" t="s">
-        <v>571</v>
+        <v>171</v>
+      </c>
+      <c r="C166" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
+        <v>570</v>
+      </c>
+      <c r="B167" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
         <v>468</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B168" t="s">
         <v>1160</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C168" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B169" t="s">
-        <v>759</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>576</v>
+        <v>1070</v>
       </c>
       <c r="B170" t="s">
-        <v>820</v>
+        <v>759</v>
       </c>
       <c r="C170" t="s">
-        <v>1131</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>613</v>
+        <v>576</v>
       </c>
       <c r="B171" t="s">
-        <v>614</v>
+        <v>820</v>
       </c>
       <c r="C171" t="s">
-        <v>586</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
       <c r="B172" t="s">
-        <v>821</v>
+        <v>614</v>
       </c>
       <c r="C172" t="s">
-        <v>1131</v>
+        <v>586</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B173" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C173" t="s">
-        <v>586</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B174" t="s">
-        <v>1144</v>
+        <v>822</v>
       </c>
       <c r="C174" t="s">
-        <v>1126</v>
+        <v>586</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
+        <v>693</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
         <v>1044</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B176" t="s">
         <v>827</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C176" t="s">
         <v>1083</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" t="s">
-        <v>459</v>
-      </c>
-      <c r="B177" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>1057</v>
+        <v>459</v>
       </c>
       <c r="B178" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C178" t="s">
-        <v>1059</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>233</v>
+        <v>1057</v>
       </c>
       <c r="B179" t="s">
-        <v>823</v>
+        <v>1058</v>
       </c>
       <c r="C179" t="s">
-        <v>523</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B180" t="s">
-        <v>824</v>
+        <v>823</v>
+      </c>
+      <c r="C180" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B181" t="s">
-        <v>825</v>
-      </c>
-      <c r="C181" t="s">
-        <v>575</v>
+        <v>824</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>667</v>
+        <v>242</v>
       </c>
       <c r="B182" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C182" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>236</v>
+        <v>667</v>
       </c>
       <c r="B183" t="s">
-        <v>235</v>
+        <v>826</v>
+      </c>
+      <c r="C183" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>449</v>
+        <v>236</v>
       </c>
       <c r="B184" t="s">
-        <v>458</v>
+        <v>235</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>237</v>
+        <v>449</v>
       </c>
       <c r="B185" t="s">
-        <v>827</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1085</v>
+        <v>458</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B186" t="s">
-        <v>828</v>
+        <v>827</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B187" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B188" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B189" t="s">
-        <v>759</v>
+        <v>830</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="B190" t="s">
-        <v>827</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1085</v>
+        <v>759</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="B191" t="s">
-        <v>299</v>
+        <v>827</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>578</v>
+        <v>298</v>
       </c>
       <c r="B192" t="s">
-        <v>1043</v>
+        <v>299</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="B193" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C193" t="s">
-        <v>1126</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>654</v>
+        <v>591</v>
       </c>
       <c r="B194" t="s">
-        <v>655</v>
+        <v>1132</v>
       </c>
       <c r="C194" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="B195" t="s">
-        <v>1161</v>
+        <v>655</v>
       </c>
       <c r="C195" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>839</v>
+        <v>666</v>
       </c>
       <c r="B196" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="C196" t="s">
         <v>1126</v>
@@ -10856,216 +10865,216 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>1086</v>
+        <v>839</v>
       </c>
       <c r="B197" t="s">
-        <v>1087</v>
+        <v>1133</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
         <v>467</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B199" t="s">
         <v>1162</v>
       </c>
-      <c r="C198" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" t="s">
-        <v>665</v>
-      </c>
-      <c r="B200" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="C199" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>460</v>
+        <v>665</v>
       </c>
       <c r="B201" t="s">
-        <v>1088</v>
+        <v>1163</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
+        <v>460</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" t="s">
         <v>243</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B203" t="s">
         <v>831</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C203" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="13.5" customHeight="1">
-      <c r="A203" t="s">
+    <row r="204" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A204" t="s">
         <v>245</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B204" t="s">
         <v>832</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C204" t="s">
         <v>588</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" t="s">
-        <v>244</v>
-      </c>
-      <c r="B204" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B205" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C205" t="s">
-        <v>1126</v>
+        <v>794</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B206" t="s">
-        <v>248</v>
+        <v>1164</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B207" t="s">
-        <v>249</v>
-      </c>
-      <c r="C207" t="s">
-        <v>580</v>
+        <v>248</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="B208" t="s">
-        <v>505</v>
+        <v>249</v>
+      </c>
+      <c r="C208" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>251</v>
+        <v>450</v>
       </c>
       <c r="B209" t="s">
-        <v>796</v>
+        <v>505</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B210" t="s">
-        <v>253</v>
+        <v>796</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B211" t="s">
-        <v>797</v>
+        <v>253</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B212" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B213" t="s">
-        <v>833</v>
-      </c>
-      <c r="C213" t="s">
-        <v>580</v>
+        <v>798</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B214" t="s">
-        <v>799</v>
+        <v>833</v>
+      </c>
+      <c r="C214" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B215" t="s">
-        <v>834</v>
-      </c>
-      <c r="C215" t="s">
-        <v>580</v>
+        <v>799</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B216" t="s">
-        <v>800</v>
+        <v>834</v>
+      </c>
+      <c r="C216" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B217" t="s">
-        <v>270</v>
+        <v>800</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B218" t="s">
-        <v>827</v>
-      </c>
-      <c r="C218" t="s">
-        <v>1085</v>
+        <v>270</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B219" t="s">
-        <v>1165</v>
+        <v>827</v>
       </c>
       <c r="C219" t="s">
-        <v>1126</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>592</v>
+        <v>273</v>
       </c>
       <c r="B220" t="s">
-        <v>1132</v>
+        <v>1165</v>
       </c>
       <c r="C220" t="s">
         <v>1126</v>
@@ -11073,10 +11082,10 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B221" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C221" t="s">
         <v>1126</v>
@@ -11084,625 +11093,625 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>478</v>
+        <v>589</v>
       </c>
       <c r="B222" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C222" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
-      <c r="A224" t="s">
-        <v>461</v>
-      </c>
-      <c r="B224" t="s">
-        <v>1089</v>
+    <row r="223" spans="1:3">
+      <c r="A223" t="s">
+        <v>478</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B225" t="s">
-        <v>506</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>267</v>
+        <v>451</v>
       </c>
       <c r="B226" t="s">
-        <v>760</v>
+        <v>506</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B227" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B228" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B229" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B230" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>593</v>
+        <v>276</v>
       </c>
       <c r="B231" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C231" t="s">
-        <v>1126</v>
+        <v>763</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>477</v>
+        <v>593</v>
       </c>
       <c r="B232" t="s">
-        <v>1168</v>
+        <v>1132</v>
       </c>
       <c r="C232" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
-      <c r="A234" t="s">
-        <v>462</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1090</v>
+    <row r="233" spans="1:3">
+      <c r="A233" t="s">
+        <v>477</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C233" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B235" t="s">
-        <v>507</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>279</v>
+        <v>452</v>
       </c>
       <c r="B236" t="s">
-        <v>754</v>
+        <v>507</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B237" t="s">
-        <v>282</v>
+        <v>754</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B238" t="s">
-        <v>755</v>
+        <v>282</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B239" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B240" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B241" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B242" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>594</v>
+        <v>286</v>
       </c>
       <c r="B243" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C243" t="s">
-        <v>1126</v>
+        <v>759</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>1134</v>
+        <v>594</v>
       </c>
       <c r="B244" t="s">
-        <v>1135</v>
+        <v>1132</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" t="s">
         <v>476</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B246" t="s">
         <v>1169</v>
       </c>
-      <c r="C245" t="s">
+      <c r="C246" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" t="s">
-        <v>463</v>
-      </c>
-      <c r="B247" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="B248" t="s">
-        <v>292</v>
-      </c>
-      <c r="C248" t="s">
-        <v>523</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B249" t="s">
-        <v>508</v>
+        <v>292</v>
+      </c>
+      <c r="C249" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>290</v>
+        <v>453</v>
       </c>
       <c r="B250" t="s">
-        <v>835</v>
-      </c>
-      <c r="C250" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B251" t="s">
-        <v>818</v>
+        <v>835</v>
+      </c>
+      <c r="C251" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>446</v>
+        <v>291</v>
       </c>
       <c r="B252" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>293</v>
+        <v>446</v>
       </c>
       <c r="B253" t="s">
-        <v>827</v>
-      </c>
-      <c r="C253" t="s">
-        <v>1092</v>
+        <v>819</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B254" t="s">
-        <v>836</v>
+        <v>827</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1092</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B255" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B256" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B257" t="s">
-        <v>759</v>
+        <v>838</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>595</v>
+        <v>297</v>
       </c>
       <c r="B258" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C258" t="s">
-        <v>1126</v>
+        <v>759</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>475</v>
+        <v>595</v>
       </c>
       <c r="B259" t="s">
-        <v>1170</v>
+        <v>1132</v>
       </c>
       <c r="C259" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
-      <c r="A261" t="s">
-        <v>627</v>
-      </c>
-      <c r="B261" t="s">
-        <v>628</v>
-      </c>
-      <c r="C261" t="s">
-        <v>586</v>
+    <row r="260" spans="1:3">
+      <c r="A260" t="s">
+        <v>475</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>492</v>
+        <v>627</v>
       </c>
       <c r="B262" t="s">
-        <v>1197</v>
+        <v>628</v>
       </c>
       <c r="C262" t="s">
-        <v>521</v>
+        <v>586</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B263" t="s">
-        <v>494</v>
+        <v>1197</v>
       </c>
       <c r="C263" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="B264" t="s">
-        <v>534</v>
+        <v>494</v>
+      </c>
+      <c r="C264" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>313</v>
+        <v>520</v>
       </c>
       <c r="B265" t="s">
-        <v>300</v>
+        <v>534</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B266" t="s">
-        <v>301</v>
-      </c>
-      <c r="C266" t="s">
-        <v>523</v>
+        <v>300</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>454</v>
+        <v>314</v>
       </c>
       <c r="B267" t="s">
-        <v>509</v>
+        <v>301</v>
+      </c>
+      <c r="C267" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>315</v>
+        <v>454</v>
       </c>
       <c r="B268" t="s">
-        <v>302</v>
+        <v>509</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B269" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B270" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B271" t="s">
-        <v>305</v>
-      </c>
-      <c r="C271" t="s">
-        <v>523</v>
+        <v>304</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B272" t="s">
-        <v>306</v>
+        <v>305</v>
+      </c>
+      <c r="C272" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B273" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B274" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B275" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B276" t="s">
-        <v>310</v>
-      </c>
-      <c r="C276" t="s">
-        <v>523</v>
+        <v>309</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B277" t="s">
-        <v>738</v>
+        <v>310</v>
+      </c>
+      <c r="C277" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B278" t="s">
-        <v>311</v>
+        <v>738</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B279" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
+        <v>326</v>
+      </c>
+      <c r="B280" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
         <v>474</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B281" t="s">
         <v>1171</v>
       </c>
-      <c r="C280" t="s">
+      <c r="C281" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3">
-      <c r="A282" t="s">
-        <v>538</v>
-      </c>
-      <c r="B282" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>333</v>
+        <v>538</v>
       </c>
       <c r="B283" t="s">
-        <v>351</v>
+        <v>539</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B284" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B285" t="s">
-        <v>349</v>
-      </c>
-      <c r="C285" t="s">
-        <v>523</v>
+        <v>348</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>455</v>
+        <v>335</v>
       </c>
       <c r="B286" t="s">
-        <v>510</v>
+        <v>349</v>
+      </c>
+      <c r="C286" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>352</v>
+        <v>455</v>
       </c>
       <c r="B287" t="s">
-        <v>350</v>
-      </c>
-      <c r="C287" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B288" t="s">
-        <v>342</v>
+        <v>350</v>
+      </c>
+      <c r="C288" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="B289" t="s">
-        <v>343</v>
-      </c>
-      <c r="C289" t="s">
-        <v>500</v>
+        <v>342</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="B290" t="s">
-        <v>344</v>
+        <v>343</v>
+      </c>
+      <c r="C290" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B291" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B292" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B293" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B294" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>1031</v>
+        <v>341</v>
       </c>
       <c r="B295" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C295" t="s">
-        <v>1033</v>
+        <v>344</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B296" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="C296" t="s">
         <v>1033</v>
@@ -11710,10 +11719,10 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B297" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C297" t="s">
         <v>1033</v>
@@ -11721,51 +11730,51 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>1093</v>
+        <v>1036</v>
       </c>
       <c r="B298" t="s">
-        <v>1094</v>
+        <v>1037</v>
+      </c>
+      <c r="C298" t="s">
+        <v>1033</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" t="s">
         <v>473</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B300" t="s">
         <v>1172</v>
       </c>
-      <c r="C299" t="s">
+      <c r="C300" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3">
-      <c r="A301" t="s">
-        <v>629</v>
-      </c>
-      <c r="B301" t="s">
-        <v>646</v>
-      </c>
-      <c r="C301" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>1038</v>
+        <v>629</v>
       </c>
       <c r="B302" t="s">
-        <v>1136</v>
+        <v>646</v>
       </c>
       <c r="C302" t="s">
-        <v>1126</v>
+        <v>586</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B303" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C303" t="s">
         <v>1126</v>
@@ -11773,78 +11782,78 @@
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B304" t="s">
-        <v>1173</v>
+        <v>1137</v>
       </c>
       <c r="C304" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
-      <c r="A306" t="s">
-        <v>625</v>
-      </c>
-      <c r="B306" t="s">
-        <v>626</v>
-      </c>
-      <c r="C306" t="s">
-        <v>586</v>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C305" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>464</v>
+        <v>625</v>
       </c>
       <c r="B307" t="s">
-        <v>465</v>
+        <v>626</v>
+      </c>
+      <c r="C307" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>359</v>
+        <v>464</v>
       </c>
       <c r="B308" t="s">
-        <v>370</v>
+        <v>465</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B309" t="s">
-        <v>371</v>
-      </c>
-      <c r="C309" t="s">
-        <v>523</v>
+        <v>370</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>511</v>
+        <v>360</v>
       </c>
       <c r="B310" t="s">
-        <v>512</v>
+        <v>371</v>
+      </c>
+      <c r="C310" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>361</v>
+        <v>511</v>
       </c>
       <c r="B311" t="s">
-        <v>372</v>
-      </c>
-      <c r="C311" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B312" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C312" t="s">
         <v>523</v>
@@ -11852,161 +11861,161 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B313" t="s">
-        <v>524</v>
+        <v>373</v>
+      </c>
+      <c r="C313" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B314" t="s">
-        <v>374</v>
+        <v>524</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B315" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B316" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B317" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B318" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B319" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>680</v>
+        <v>369</v>
       </c>
       <c r="B320" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C320" t="s">
-        <v>1126</v>
+        <v>379</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>1051</v>
+        <v>680</v>
       </c>
       <c r="B321" t="s">
-        <v>1052</v>
+        <v>1138</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>547</v>
+        <v>1051</v>
       </c>
       <c r="B322" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C322" t="s">
-        <v>1126</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>1095</v>
+        <v>547</v>
       </c>
       <c r="B323" t="s">
-        <v>1096</v>
+        <v>1174</v>
+      </c>
+      <c r="C323" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B324" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
         <v>471</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B325" t="s">
         <v>1175</v>
       </c>
-      <c r="C324" t="s">
+      <c r="C325" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3">
-      <c r="A326" t="s">
-        <v>466</v>
-      </c>
-      <c r="B326" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>386</v>
+        <v>466</v>
       </c>
       <c r="B327" t="s">
-        <v>397</v>
+        <v>465</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B328" t="s">
-        <v>398</v>
-      </c>
-      <c r="C328" t="s">
-        <v>523</v>
+        <v>397</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>456</v>
+        <v>387</v>
       </c>
       <c r="B329" t="s">
-        <v>513</v>
+        <v>398</v>
+      </c>
+      <c r="C329" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="B330" t="s">
-        <v>399</v>
-      </c>
-      <c r="C330" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B331" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C331" t="s">
         <v>523</v>
@@ -12014,730 +12023,730 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B332" t="s">
-        <v>525</v>
+        <v>400</v>
+      </c>
+      <c r="C332" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B333" t="s">
-        <v>374</v>
+        <v>525</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B334" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B335" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B336" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B337" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B338" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>553</v>
+        <v>396</v>
       </c>
       <c r="B339" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C339" t="s">
-        <v>1126</v>
+        <v>379</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>1097</v>
+        <v>553</v>
       </c>
       <c r="B340" t="s">
-        <v>1098</v>
+        <v>1174</v>
+      </c>
+      <c r="C340" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" t="s">
         <v>470</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B342" t="s">
         <v>1175</v>
       </c>
-      <c r="C341" t="s">
+      <c r="C342" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3">
-      <c r="A343" t="s">
-        <v>623</v>
-      </c>
-      <c r="B343" t="s">
-        <v>624</v>
-      </c>
-      <c r="C343" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>380</v>
+        <v>623</v>
       </c>
       <c r="B344" t="s">
-        <v>1199</v>
+        <v>624</v>
+      </c>
+      <c r="C344" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B345" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C345" t="s">
-        <v>523</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>457</v>
+        <v>381</v>
       </c>
       <c r="B346" t="s">
-        <v>1201</v>
+        <v>1200</v>
+      </c>
+      <c r="C346" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>382</v>
+        <v>457</v>
       </c>
       <c r="B347" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B348" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B349" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>1065</v>
+        <v>384</v>
       </c>
       <c r="B350" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1099</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C351" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" t="s">
         <v>469</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B352" t="s">
         <v>1205</v>
       </c>
-      <c r="C351" t="s">
+      <c r="C352" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3">
-      <c r="A353" t="s">
-        <v>688</v>
-      </c>
-      <c r="B353" t="s">
-        <v>689</v>
-      </c>
-      <c r="C353" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
+        <v>688</v>
+      </c>
+      <c r="B354" t="s">
+        <v>689</v>
+      </c>
+      <c r="C354" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" t="s">
         <v>690</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B355" t="s">
         <v>1176</v>
       </c>
-      <c r="C354" t="s">
+      <c r="C355" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3">
-      <c r="A356" t="s">
-        <v>696</v>
-      </c>
-      <c r="B356" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B357" t="s">
-        <v>1198</v>
+        <v>697</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B358" t="s">
-        <v>700</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B359" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B360" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B361" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B362" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B363" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B364" t="s">
-        <v>1100</v>
+        <v>710</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B365" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C365" t="s">
-        <v>1126</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B366" t="s">
-        <v>714</v>
+        <v>1177</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B367" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B368" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B369" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B370" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B371" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>1061</v>
+        <v>723</v>
       </c>
       <c r="B372" t="s">
-        <v>1062</v>
+        <v>724</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>725</v>
+        <v>1061</v>
       </c>
       <c r="B373" t="s">
-        <v>726</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>1101</v>
+        <v>725</v>
       </c>
       <c r="B374" t="s">
-        <v>1102</v>
+        <v>726</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" t="s">
         <v>1064</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B376" t="s">
         <v>1178</v>
       </c>
-      <c r="C375" t="s">
+      <c r="C376" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3">
-      <c r="A377" t="s">
-        <v>727</v>
-      </c>
-      <c r="B377" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B378" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B379" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B380" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B381" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B382" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B383" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B384" t="s">
-        <v>312</v>
+        <v>740</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B385" t="s">
-        <v>743</v>
+        <v>312</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B386" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B387" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
+        <v>746</v>
+      </c>
+      <c r="B388" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" t="s">
         <v>748</v>
       </c>
-      <c r="B388" t="s">
+      <c r="B389" t="s">
         <v>1179</v>
       </c>
-      <c r="C388" t="s">
+      <c r="C389" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3">
-      <c r="A390" t="s">
-        <v>749</v>
-      </c>
-      <c r="B390" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B391" t="s">
-        <v>751</v>
+        <v>306</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B392" t="s">
-        <v>308</v>
+        <v>751</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
+        <v>752</v>
+      </c>
+      <c r="B393" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" t="s">
         <v>753</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B394" t="s">
         <v>1103</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3">
-      <c r="A395" t="s">
-        <v>774</v>
-      </c>
-      <c r="B395" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B396" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B397" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B398" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B399" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
+        <v>766</v>
+      </c>
+      <c r="B400" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" t="s">
         <v>771</v>
       </c>
-      <c r="B400" t="s">
+      <c r="B401" t="s">
         <v>1180</v>
       </c>
-      <c r="C400" t="s">
+      <c r="C401" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3">
-      <c r="A402" t="s">
-        <v>778</v>
-      </c>
-      <c r="B402" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="B403" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B404" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B405" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B406" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
+        <v>781</v>
+      </c>
+      <c r="B407" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" t="s">
         <v>782</v>
       </c>
-      <c r="B407" t="s">
+      <c r="B408" t="s">
         <v>1181</v>
       </c>
-      <c r="C407" t="s">
+      <c r="C408" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3">
-      <c r="A409" t="s">
-        <v>790</v>
-      </c>
-      <c r="B409" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B410" t="s">
-        <v>1060</v>
+        <v>791</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B411" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C411" t="s">
-        <v>1126</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B412" t="s">
-        <v>978</v>
+        <v>1163</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="B413" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C413" t="s">
-        <v>1126</v>
+        <v>978</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B414" t="s">
-        <v>979</v>
+        <v>1182</v>
+      </c>
+      <c r="C414" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B415" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B416" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B417" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B418" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B419" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B420" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B421" t="s">
-        <v>800</v>
+        <v>985</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B422" t="s">
-        <v>986</v>
+        <v>800</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B423" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C423" t="s">
-        <v>1126</v>
+        <v>986</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B424" t="s">
-        <v>1132</v>
+        <v>1165</v>
       </c>
       <c r="C424" t="s">
         <v>1126</v>
@@ -12745,10 +12754,10 @@
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="B425" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C425" t="s">
         <v>1126</v>
@@ -12756,10 +12765,10 @@
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B426" t="s">
-        <v>1183</v>
+        <v>1166</v>
       </c>
       <c r="C426" t="s">
         <v>1126</v>
@@ -12767,1492 +12776,1503 @@
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>1104</v>
+        <v>804</v>
       </c>
       <c r="B427" t="s">
-        <v>1087</v>
+        <v>1183</v>
+      </c>
+      <c r="C427" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>987</v>
+        <v>1104</v>
       </c>
       <c r="B428" t="s">
-        <v>988</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B429" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B430" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B431" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B432" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B433" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B434" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B435" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C435" t="s">
-        <v>1126</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C436" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437" t="s">
         <v>1069</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B437" t="s">
         <v>1105</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3">
-      <c r="A438" t="s">
-        <v>851</v>
-      </c>
-      <c r="B438" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B439" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B440" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B441" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B442" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B443" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B444" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B445" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B446" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B447" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B448" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B449" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B450" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B451" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B452" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B453" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C453" t="s">
-        <v>1126</v>
+        <v>880</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B454" t="s">
-        <v>883</v>
+        <v>1140</v>
+      </c>
+      <c r="C454" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B455" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B456" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B457" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>1106</v>
+        <v>888</v>
       </c>
       <c r="B458" t="s">
-        <v>1107</v>
+        <v>889</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3">
+      <c r="A460" t="s">
         <v>890</v>
       </c>
-      <c r="B459" t="s">
+      <c r="B460" t="s">
         <v>1184</v>
       </c>
-      <c r="C459" t="s">
+      <c r="C460" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3">
-      <c r="A461" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B461" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>891</v>
+        <v>1067</v>
       </c>
       <c r="B462" t="s">
-        <v>892</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B463" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B464" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B465" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B466" t="s">
-        <v>1108</v>
+        <v>898</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B467" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B468" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B469" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B470" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>1113</v>
+        <v>903</v>
       </c>
       <c r="B471" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3">
+      <c r="A473" t="s">
         <v>904</v>
       </c>
-      <c r="B472" t="s">
+      <c r="B473" t="s">
         <v>1185</v>
       </c>
-      <c r="C472" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3">
-      <c r="A474" t="s">
-        <v>911</v>
-      </c>
-      <c r="B474" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C474" t="s">
+      <c r="C473" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
+        <v>911</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3">
+      <c r="A476" t="s">
         <v>912</v>
       </c>
-      <c r="B475" t="s">
+      <c r="B476" t="s">
         <v>1187</v>
       </c>
-      <c r="C475" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3">
-      <c r="A477" t="s">
-        <v>913</v>
-      </c>
-      <c r="B477" t="s">
-        <v>914</v>
-      </c>
-      <c r="C477" t="s">
+      <c r="C476" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
+        <v>913</v>
+      </c>
+      <c r="B478" t="s">
+        <v>914</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3">
+      <c r="A479" t="s">
         <v>915</v>
       </c>
-      <c r="B478" t="s">
+      <c r="B479" t="s">
         <v>1188</v>
       </c>
-      <c r="C478" t="s">
+      <c r="C479" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3">
-      <c r="A480" t="s">
-        <v>916</v>
-      </c>
-      <c r="B480" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B481" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
-        <v>1115</v>
+        <v>918</v>
       </c>
       <c r="B482" t="s">
-        <v>1116</v>
+        <v>919</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484" t="s">
         <v>920</v>
       </c>
-      <c r="B483" t="s">
+      <c r="B484" t="s">
         <v>1189</v>
       </c>
-      <c r="C483" t="s">
+      <c r="C484" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3">
-      <c r="A485" t="s">
-        <v>921</v>
-      </c>
-      <c r="B485" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B486" t="s">
-        <v>923</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B487" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B488" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B489" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B490" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="491" spans="1:3">
       <c r="A491" t="s">
+        <v>930</v>
+      </c>
+      <c r="B491" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492" t="s">
         <v>932</v>
       </c>
-      <c r="B491" t="s">
+      <c r="B492" t="s">
         <v>1190</v>
       </c>
-      <c r="C491" t="s">
+      <c r="C492" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3">
-      <c r="A493" t="s">
-        <v>933</v>
-      </c>
-      <c r="B493" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B494" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B495" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B496" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B497" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="498" spans="1:3">
       <c r="A498" t="s">
+        <v>941</v>
+      </c>
+      <c r="B498" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3">
+      <c r="A499" t="s">
         <v>943</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B499" t="s">
         <v>1141</v>
       </c>
-      <c r="C498" t="s">
+      <c r="C499" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3">
-      <c r="A500" t="s">
-        <v>944</v>
-      </c>
-      <c r="B500" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B501" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B502" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B503" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B504" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="505" spans="1:3">
       <c r="A505" t="s">
+        <v>952</v>
+      </c>
+      <c r="B505" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3">
+      <c r="A506" t="s">
         <v>954</v>
       </c>
-      <c r="B505" t="s">
+      <c r="B506" t="s">
         <v>1117</v>
       </c>
-      <c r="C505" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3">
-      <c r="A507" t="s">
-        <v>955</v>
-      </c>
-      <c r="B507" t="s">
-        <v>956</v>
-      </c>
-      <c r="C507" t="s">
+      <c r="C506" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B508" t="s">
-        <v>958</v>
+        <v>956</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B509" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B510" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="511" spans="1:3">
       <c r="A511" t="s">
+        <v>961</v>
+      </c>
+      <c r="B511" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3">
+      <c r="A512" t="s">
         <v>963</v>
       </c>
-      <c r="B511" t="s">
+      <c r="B512" t="s">
         <v>1191</v>
       </c>
-      <c r="C511" t="s">
+      <c r="C512" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3">
-      <c r="A513" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B513" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B514" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B515" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B516" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B517" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B518" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B519" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B520" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B521" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B522" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B523" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B524" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B525" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3">
+      <c r="A527" t="s">
         <v>1028</v>
       </c>
-      <c r="B526" t="s">
+      <c r="B527" t="s">
         <v>1192</v>
       </c>
-      <c r="C526" t="s">
+      <c r="C527" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3">
-      <c r="A528" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B529" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B530" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B531" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B532" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B533" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B534" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B535" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B536" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B537" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B538" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B539" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B540" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B541" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B542" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B543" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B544" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B545" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B546" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B547" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B548" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B549" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="B550" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B551" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B552" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="B553" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="B554" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B555" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B556" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B557" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B558" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B559" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B560" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B561" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B562" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B563" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B564" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B565" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B566" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B567" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B568" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B569" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B570" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B571" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B572" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B573" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B574" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B575" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B576" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B577" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B578" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B579" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B580" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B581" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B582" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B583" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B584" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B585" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B586" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B587" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B588" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B589" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B590" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B591" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B592" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B593" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B594" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B595" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B596" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B597" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B598" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B599" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B600" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B601" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B602" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B603" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B604" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B605" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B606" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B607" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B608" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B609" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B610" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B611" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B612" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B613" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B614" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B615" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B616" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" t="s">
         <v>1391</v>
       </c>
-      <c r="B617" t="s">
+      <c r="B618" t="s">
         <v>1392</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C526" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
-  <conditionalFormatting sqref="A479:A480 A476:A477 A461:A471 A473:A474 A482">
+  <autoFilter ref="A1:C527" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
+  <conditionalFormatting sqref="A480:A481 A477:A478 A462:A472 A474:A475 A483">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harmandeep.singh\Documents\Git\1021\Application-Review-Process_Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C95A81-3FFE-4B5E-99F4-FA412CBFA5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41020FCD-77B0-4E88-9C2F-0F5E21B45AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="13860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1398">
   <si>
     <t>Name</t>
   </si>
@@ -4231,6 +4231,12 @@
   </si>
   <si>
     <t>Newly added by Harman</t>
+  </si>
+  <si>
+    <t>CQ</t>
+  </si>
+  <si>
+    <t>Certification Questionnaire</t>
   </si>
 </sst>
 </file>
@@ -5137,7 +5143,14 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="61" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A61" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1397</v>
+      </c>
+    </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="63" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="64" spans="1:3" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41020FCD-77B0-4E88-9C2F-0F5E21B45AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F4B661-C6EA-4597-A366-9AD29E0AD47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37920" windowHeight="18870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Findings" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$527</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Findings!$A$1:$C$528</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="1400">
   <si>
     <t>Name</t>
   </si>
@@ -4237,6 +4237,12 @@
   </si>
   <si>
     <t>Certification Questionnaire</t>
+  </si>
+  <si>
+    <t>ICW_StudentFinding</t>
+  </si>
+  <si>
+    <t>The applicant has indicated all household contains all students on the Income Calculation Worksheet. Manual review is needed.</t>
   </si>
 </sst>
 </file>
@@ -9190,7 +9196,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}">
-  <dimension ref="A1:C618"/>
+  <dimension ref="A1:C619"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -9437,10 +9443,13 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>472</v>
+        <v>1398</v>
       </c>
       <c r="B29" t="s">
-        <v>1147</v>
+        <v>1399</v>
+      </c>
+      <c r="C29" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9454,127 +9463,124 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>175</v>
-      </c>
-      <c r="B32" t="s">
-        <v>176</v>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>472</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1147</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>498</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>499</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>498</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>1075</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>673</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>674</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>556</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>557</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="B44" t="s">
-        <v>681</v>
+        <v>557</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="B45" t="s">
-        <v>605</v>
-      </c>
-      <c r="C45" t="s">
-        <v>586</v>
+        <v>681</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>678</v>
+        <v>604</v>
       </c>
       <c r="B46" t="s">
-        <v>679</v>
+        <v>605</v>
       </c>
       <c r="C46" t="s">
         <v>586</v>
@@ -9582,158 +9588,158 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>678</v>
+      </c>
+      <c r="B47" t="s">
+        <v>679</v>
+      </c>
+      <c r="C47" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>487</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>1148</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>177</v>
-      </c>
-      <c r="B49" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s">
-        <v>1076</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
-      </c>
-      <c r="C56" t="s">
-        <v>523</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="C57" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>558</v>
+        <v>101</v>
       </c>
       <c r="B58" t="s">
-        <v>559</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>668</v>
+        <v>558</v>
       </c>
       <c r="B59" t="s">
-        <v>669</v>
+        <v>559</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>1029</v>
+        <v>668</v>
       </c>
       <c r="B60" t="s">
-        <v>1030</v>
+        <v>669</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>587</v>
+        <v>1029</v>
       </c>
       <c r="B61" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1126</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>486</v>
+        <v>587</v>
       </c>
       <c r="B62" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C62" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>178</v>
-      </c>
-      <c r="B64" t="s">
-        <v>526</v>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>486</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="B65" t="s">
-        <v>103</v>
-      </c>
-      <c r="C65" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C66" t="s">
         <v>523</v>
@@ -9741,10 +9747,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C67" t="s">
         <v>523</v>
@@ -9752,10 +9758,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
         <v>523</v>
@@ -9763,10 +9769,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C69" t="s">
         <v>523</v>
@@ -9774,10 +9780,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C70" t="s">
         <v>523</v>
@@ -9785,158 +9791,158 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B71" t="s">
-        <v>1077</v>
+        <v>106</v>
+      </c>
+      <c r="C71" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="B72" t="s">
-        <v>670</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B73" t="s">
-        <v>671</v>
-      </c>
-      <c r="C73" t="s">
-        <v>523</v>
+        <v>670</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>514</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>672</v>
+        <v>671</v>
+      </c>
+      <c r="C74" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="B75" t="s">
-        <v>489</v>
+        <v>672</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s">
-        <v>1078</v>
+        <v>489</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>631</v>
+        <v>495</v>
       </c>
       <c r="B77" t="s">
-        <v>630</v>
-      </c>
-      <c r="C77" t="s">
-        <v>586</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>1079</v>
+        <v>631</v>
       </c>
       <c r="B78" t="s">
-        <v>1080</v>
+        <v>630</v>
+      </c>
+      <c r="C78" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
         <v>1072</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>1073</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>1151</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" t="s">
-        <v>152</v>
-      </c>
-      <c r="B83" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B84" t="s">
-        <v>527</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B85" t="s">
-        <v>117</v>
+        <v>527</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>560</v>
+        <v>118</v>
       </c>
       <c r="B86" t="s">
-        <v>561</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>641</v>
+        <v>560</v>
       </c>
       <c r="B87" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1126</v>
+        <v>561</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="B88" t="s">
-        <v>660</v>
+        <v>1129</v>
       </c>
       <c r="C88" t="s">
-        <v>586</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B89" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C89" t="s">
         <v>586</v>
@@ -9944,10 +9950,10 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B90" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C90" t="s">
         <v>586</v>
@@ -9955,37 +9961,37 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
+        <v>657</v>
+      </c>
+      <c r="B91" t="s">
+        <v>662</v>
+      </c>
+      <c r="C91" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
         <v>484</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B92" t="s">
         <v>1152</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" t="s">
-        <v>180</v>
-      </c>
-      <c r="B93" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>640</v>
+        <v>180</v>
       </c>
       <c r="B94" t="s">
-        <v>653</v>
-      </c>
-      <c r="C94" t="s">
-        <v>586</v>
+        <v>976</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B95" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="C95" t="s">
         <v>586</v>
@@ -9993,80 +9999,80 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>119</v>
+        <v>638</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>639</v>
+      </c>
+      <c r="C96" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B98" t="s">
-        <v>528</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B99" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B100" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B101" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B102" t="s">
-        <v>442</v>
-      </c>
-      <c r="C102" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B103" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C103" t="s">
-        <v>496</v>
+        <v>581</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B104" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C104" t="s">
         <v>496</v>
@@ -10074,48 +10080,48 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>562</v>
+        <v>138</v>
       </c>
       <c r="B105" t="s">
-        <v>563</v>
+        <v>445</v>
+      </c>
+      <c r="C105" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>606</v>
+        <v>562</v>
       </c>
       <c r="B106" t="s">
-        <v>607</v>
-      </c>
-      <c r="C106" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>843</v>
+        <v>606</v>
       </c>
       <c r="B107" t="s">
-        <v>844</v>
+        <v>607</v>
+      </c>
+      <c r="C107" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>632</v>
+        <v>843</v>
       </c>
       <c r="B108" t="s">
-        <v>633</v>
-      </c>
-      <c r="C108" t="s">
-        <v>586</v>
+        <v>844</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B109" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C109" t="s">
         <v>586</v>
@@ -10123,10 +10129,10 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B110" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C110" t="s">
         <v>586</v>
@@ -10134,75 +10140,75 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>840</v>
+        <v>637</v>
       </c>
       <c r="B111" t="s">
-        <v>1130</v>
+        <v>636</v>
       </c>
       <c r="C111" t="s">
-        <v>1126</v>
+        <v>586</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B112" t="s">
-        <v>842</v>
+        <v>1130</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B113" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B114" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
+        <v>848</v>
+      </c>
+      <c r="B115" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
         <v>483</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B116" t="s">
         <v>1153</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B117" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C117" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>141</v>
+        <v>1124</v>
       </c>
       <c r="B118" t="s">
-        <v>144</v>
+        <v>1125</v>
       </c>
       <c r="C118" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C119" t="s">
         <v>579</v>
@@ -10210,10 +10216,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C120" t="s">
         <v>579</v>
@@ -10221,32 +10227,32 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B121" t="s">
-        <v>515</v>
+        <v>146</v>
       </c>
       <c r="C121" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>584</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
         <v>515</v>
       </c>
       <c r="C122" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>140</v>
+        <v>584</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>515</v>
       </c>
       <c r="C123" t="s">
         <v>579</v>
@@ -10254,10 +10260,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B124" t="s">
-        <v>532</v>
+        <v>123</v>
       </c>
       <c r="C124" t="s">
         <v>579</v>
@@ -10265,10 +10271,10 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>532</v>
       </c>
       <c r="C125" t="s">
         <v>579</v>
@@ -10276,10 +10282,10 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>564</v>
+        <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>565</v>
+        <v>124</v>
       </c>
       <c r="C126" t="s">
         <v>579</v>
@@ -10287,277 +10293,277 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
+        <v>564</v>
+      </c>
+      <c r="B127" t="s">
+        <v>565</v>
+      </c>
+      <c r="C127" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
         <v>482</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B128" t="s">
         <v>1154</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" t="s">
-        <v>181</v>
-      </c>
-      <c r="B129" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="B130" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B132" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>683</v>
+        <v>128</v>
       </c>
       <c r="B133" t="s">
-        <v>682</v>
-      </c>
-      <c r="C133" t="s">
-        <v>586</v>
+        <v>149</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>130</v>
+        <v>683</v>
       </c>
       <c r="B134" t="s">
-        <v>150</v>
+        <v>682</v>
+      </c>
+      <c r="C134" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B135" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>555</v>
+        <v>131</v>
       </c>
       <c r="B136" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="B137" t="s">
-        <v>567</v>
+        <v>1155</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>608</v>
+        <v>566</v>
       </c>
       <c r="B138" t="s">
-        <v>609</v>
-      </c>
-      <c r="C138" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
+        <v>608</v>
+      </c>
+      <c r="B139" t="s">
+        <v>609</v>
+      </c>
+      <c r="C139" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
         <v>481</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B140" t="s">
         <v>1156</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" t="s">
-        <v>598</v>
-      </c>
-      <c r="B141" t="s">
-        <v>599</v>
-      </c>
-      <c r="C141" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B142" t="s">
-        <v>1157</v>
+        <v>599</v>
       </c>
       <c r="C142" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
-      <c r="A144" t="s">
-        <v>153</v>
-      </c>
-      <c r="B144" t="s">
-        <v>157</v>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>601</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C143" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B145" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B147" t="s">
-        <v>533</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>497</v>
+        <v>156</v>
       </c>
       <c r="B148" t="s">
-        <v>621</v>
-      </c>
-      <c r="C148" t="s">
-        <v>622</v>
+        <v>533</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>1048</v>
+        <v>497</v>
       </c>
       <c r="B149" t="s">
-        <v>1056</v>
+        <v>621</v>
       </c>
       <c r="C149" t="s">
-        <v>586</v>
+        <v>622</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>572</v>
+        <v>1048</v>
       </c>
       <c r="B150" t="s">
-        <v>573</v>
+        <v>1056</v>
+      </c>
+      <c r="C150" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
+        <v>572</v>
+      </c>
+      <c r="B151" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
         <v>480</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B152" t="s">
         <v>1158</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" t="s">
-        <v>185</v>
-      </c>
-      <c r="B153" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B154" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>568</v>
+        <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>569</v>
+        <v>163</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>479</v>
+        <v>568</v>
       </c>
       <c r="B157" t="s">
-        <v>1159</v>
+        <v>569</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
+        <v>479</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
         <v>610</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B159" t="s">
         <v>611</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C159" t="s">
         <v>586</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" t="s">
-        <v>183</v>
-      </c>
-      <c r="B160" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B161" t="s">
-        <v>166</v>
-      </c>
-      <c r="C161" t="s">
-        <v>523</v>
+        <v>184</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C162" t="s">
         <v>523</v>
@@ -10565,10 +10571,10 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B163" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C163" t="s">
         <v>523</v>
@@ -10576,312 +10582,312 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="B164" t="s">
-        <v>193</v>
+        <v>168</v>
+      </c>
+      <c r="C164" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B165" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B166" t="s">
-        <v>171</v>
-      </c>
-      <c r="C166" t="s">
-        <v>523</v>
+        <v>192</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>570</v>
+        <v>170</v>
       </c>
       <c r="B167" t="s">
-        <v>571</v>
+        <v>171</v>
+      </c>
+      <c r="C167" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
+        <v>570</v>
+      </c>
+      <c r="B168" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
         <v>468</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B169" t="s">
         <v>1160</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C169" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B170" t="s">
-        <v>759</v>
-      </c>
-      <c r="C170" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>576</v>
+        <v>1070</v>
       </c>
       <c r="B171" t="s">
-        <v>820</v>
+        <v>759</v>
       </c>
       <c r="C171" t="s">
-        <v>1131</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>613</v>
+        <v>576</v>
       </c>
       <c r="B172" t="s">
-        <v>614</v>
+        <v>820</v>
       </c>
       <c r="C172" t="s">
-        <v>586</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
       <c r="B173" t="s">
-        <v>821</v>
+        <v>614</v>
       </c>
       <c r="C173" t="s">
-        <v>1131</v>
+        <v>586</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B174" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C174" t="s">
-        <v>586</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B175" t="s">
-        <v>1144</v>
+        <v>822</v>
       </c>
       <c r="C175" t="s">
-        <v>1126</v>
+        <v>586</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
+        <v>693</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" t="s">
         <v>1044</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B177" t="s">
         <v>827</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C177" t="s">
         <v>1083</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178" t="s">
-        <v>459</v>
-      </c>
-      <c r="B178" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>1057</v>
+        <v>459</v>
       </c>
       <c r="B179" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C179" t="s">
-        <v>1059</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>233</v>
+        <v>1057</v>
       </c>
       <c r="B180" t="s">
-        <v>823</v>
+        <v>1058</v>
       </c>
       <c r="C180" t="s">
-        <v>523</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B181" t="s">
-        <v>824</v>
+        <v>823</v>
+      </c>
+      <c r="C181" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B182" t="s">
-        <v>825</v>
-      </c>
-      <c r="C182" t="s">
-        <v>575</v>
+        <v>824</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>667</v>
+        <v>242</v>
       </c>
       <c r="B183" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C183" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>236</v>
+        <v>667</v>
       </c>
       <c r="B184" t="s">
-        <v>235</v>
+        <v>826</v>
+      </c>
+      <c r="C184" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>449</v>
+        <v>236</v>
       </c>
       <c r="B185" t="s">
-        <v>458</v>
+        <v>235</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>237</v>
+        <v>449</v>
       </c>
       <c r="B186" t="s">
-        <v>827</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1085</v>
+        <v>458</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B187" t="s">
-        <v>828</v>
+        <v>827</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B188" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B189" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B190" t="s">
-        <v>759</v>
+        <v>830</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="B191" t="s">
-        <v>827</v>
-      </c>
-      <c r="C191" t="s">
-        <v>1085</v>
+        <v>759</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="B192" t="s">
-        <v>299</v>
+        <v>827</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>578</v>
+        <v>298</v>
       </c>
       <c r="B193" t="s">
-        <v>1043</v>
+        <v>299</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="B194" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C194" t="s">
-        <v>1126</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>654</v>
+        <v>591</v>
       </c>
       <c r="B195" t="s">
-        <v>655</v>
+        <v>1132</v>
       </c>
       <c r="C195" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="B196" t="s">
-        <v>1161</v>
+        <v>655</v>
       </c>
       <c r="C196" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>839</v>
+        <v>666</v>
       </c>
       <c r="B197" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="C197" t="s">
         <v>1126</v>
@@ -10889,216 +10895,216 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>1086</v>
+        <v>839</v>
       </c>
       <c r="B198" t="s">
-        <v>1087</v>
+        <v>1133</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" t="s">
         <v>467</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B200" t="s">
         <v>1162</v>
       </c>
-      <c r="C199" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" t="s">
-        <v>665</v>
-      </c>
-      <c r="B201" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="C200" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>460</v>
+        <v>665</v>
       </c>
       <c r="B202" t="s">
-        <v>1088</v>
+        <v>1163</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
+        <v>460</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" t="s">
         <v>243</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B204" t="s">
         <v>831</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C204" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="13.5" customHeight="1">
-      <c r="A204" t="s">
+    <row r="205" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A205" t="s">
         <v>245</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B205" t="s">
         <v>832</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C205" t="s">
         <v>588</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" t="s">
-        <v>244</v>
-      </c>
-      <c r="B205" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B206" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C206" t="s">
-        <v>1126</v>
+        <v>794</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B207" t="s">
-        <v>248</v>
+        <v>1164</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B208" t="s">
-        <v>249</v>
-      </c>
-      <c r="C208" t="s">
-        <v>580</v>
+        <v>248</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="B209" t="s">
-        <v>505</v>
+        <v>249</v>
+      </c>
+      <c r="C209" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>251</v>
+        <v>450</v>
       </c>
       <c r="B210" t="s">
-        <v>796</v>
+        <v>505</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B211" t="s">
-        <v>253</v>
+        <v>796</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B212" t="s">
-        <v>797</v>
+        <v>253</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B213" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B214" t="s">
-        <v>833</v>
-      </c>
-      <c r="C214" t="s">
-        <v>580</v>
+        <v>798</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B215" t="s">
-        <v>799</v>
+        <v>833</v>
+      </c>
+      <c r="C215" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B216" t="s">
-        <v>834</v>
-      </c>
-      <c r="C216" t="s">
-        <v>580</v>
+        <v>799</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B217" t="s">
-        <v>800</v>
+        <v>834</v>
+      </c>
+      <c r="C217" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B218" t="s">
-        <v>270</v>
+        <v>800</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B219" t="s">
-        <v>827</v>
-      </c>
-      <c r="C219" t="s">
-        <v>1085</v>
+        <v>270</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B220" t="s">
-        <v>1165</v>
+        <v>827</v>
       </c>
       <c r="C220" t="s">
-        <v>1126</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>592</v>
+        <v>273</v>
       </c>
       <c r="B221" t="s">
-        <v>1132</v>
+        <v>1165</v>
       </c>
       <c r="C221" t="s">
         <v>1126</v>
@@ -11106,10 +11112,10 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B222" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C222" t="s">
         <v>1126</v>
@@ -11117,625 +11123,625 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>478</v>
+        <v>589</v>
       </c>
       <c r="B223" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C223" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
-      <c r="A225" t="s">
-        <v>461</v>
-      </c>
-      <c r="B225" t="s">
-        <v>1089</v>
+    <row r="224" spans="1:3">
+      <c r="A224" t="s">
+        <v>478</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B226" t="s">
-        <v>506</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>267</v>
+        <v>451</v>
       </c>
       <c r="B227" t="s">
-        <v>760</v>
+        <v>506</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B228" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B229" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B230" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B231" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>593</v>
+        <v>276</v>
       </c>
       <c r="B232" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C232" t="s">
-        <v>1126</v>
+        <v>763</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>477</v>
+        <v>593</v>
       </c>
       <c r="B233" t="s">
-        <v>1168</v>
+        <v>1132</v>
       </c>
       <c r="C233" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
-      <c r="A235" t="s">
-        <v>462</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1090</v>
+    <row r="234" spans="1:3">
+      <c r="A234" t="s">
+        <v>477</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C234" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B236" t="s">
-        <v>507</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>279</v>
+        <v>452</v>
       </c>
       <c r="B237" t="s">
-        <v>754</v>
+        <v>507</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B238" t="s">
-        <v>282</v>
+        <v>754</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B239" t="s">
-        <v>755</v>
+        <v>282</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B240" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B241" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B242" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B243" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>594</v>
+        <v>286</v>
       </c>
       <c r="B244" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C244" t="s">
-        <v>1126</v>
+        <v>759</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>1134</v>
+        <v>594</v>
       </c>
       <c r="B245" t="s">
-        <v>1135</v>
+        <v>1132</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" t="s">
         <v>476</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B247" t="s">
         <v>1169</v>
       </c>
-      <c r="C246" t="s">
+      <c r="C247" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248" t="s">
-        <v>463</v>
-      </c>
-      <c r="B248" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="B249" t="s">
-        <v>292</v>
-      </c>
-      <c r="C249" t="s">
-        <v>523</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B250" t="s">
-        <v>508</v>
+        <v>292</v>
+      </c>
+      <c r="C250" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>290</v>
+        <v>453</v>
       </c>
       <c r="B251" t="s">
-        <v>835</v>
-      </c>
-      <c r="C251" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B252" t="s">
-        <v>818</v>
+        <v>835</v>
+      </c>
+      <c r="C252" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>446</v>
+        <v>291</v>
       </c>
       <c r="B253" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>293</v>
+        <v>446</v>
       </c>
       <c r="B254" t="s">
-        <v>827</v>
-      </c>
-      <c r="C254" t="s">
-        <v>1092</v>
+        <v>819</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B255" t="s">
-        <v>836</v>
+        <v>827</v>
+      </c>
+      <c r="C255" t="s">
+        <v>1092</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B256" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B257" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B258" t="s">
-        <v>759</v>
+        <v>838</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>595</v>
+        <v>297</v>
       </c>
       <c r="B259" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C259" t="s">
-        <v>1126</v>
+        <v>759</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>475</v>
+        <v>595</v>
       </c>
       <c r="B260" t="s">
-        <v>1170</v>
+        <v>1132</v>
       </c>
       <c r="C260" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
-      <c r="A262" t="s">
-        <v>627</v>
-      </c>
-      <c r="B262" t="s">
-        <v>628</v>
-      </c>
-      <c r="C262" t="s">
-        <v>586</v>
+    <row r="261" spans="1:3">
+      <c r="A261" t="s">
+        <v>475</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>492</v>
+        <v>627</v>
       </c>
       <c r="B263" t="s">
-        <v>1197</v>
+        <v>628</v>
       </c>
       <c r="C263" t="s">
-        <v>521</v>
+        <v>586</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B264" t="s">
-        <v>494</v>
+        <v>1197</v>
       </c>
       <c r="C264" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="B265" t="s">
-        <v>534</v>
+        <v>494</v>
+      </c>
+      <c r="C265" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>313</v>
+        <v>520</v>
       </c>
       <c r="B266" t="s">
-        <v>300</v>
+        <v>534</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B267" t="s">
-        <v>301</v>
-      </c>
-      <c r="C267" t="s">
-        <v>523</v>
+        <v>300</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>454</v>
+        <v>314</v>
       </c>
       <c r="B268" t="s">
-        <v>509</v>
+        <v>301</v>
+      </c>
+      <c r="C268" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>315</v>
+        <v>454</v>
       </c>
       <c r="B269" t="s">
-        <v>302</v>
+        <v>509</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B270" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B271" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B272" t="s">
-        <v>305</v>
-      </c>
-      <c r="C272" t="s">
-        <v>523</v>
+        <v>304</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B273" t="s">
-        <v>306</v>
+        <v>305</v>
+      </c>
+      <c r="C273" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B274" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B276" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B277" t="s">
-        <v>310</v>
-      </c>
-      <c r="C277" t="s">
-        <v>523</v>
+        <v>309</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B278" t="s">
-        <v>738</v>
+        <v>310</v>
+      </c>
+      <c r="C278" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B279" t="s">
-        <v>311</v>
+        <v>738</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B280" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
+        <v>326</v>
+      </c>
+      <c r="B281" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" t="s">
         <v>474</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B282" t="s">
         <v>1171</v>
       </c>
-      <c r="C281" t="s">
+      <c r="C282" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3">
-      <c r="A283" t="s">
-        <v>538</v>
-      </c>
-      <c r="B283" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>333</v>
+        <v>538</v>
       </c>
       <c r="B284" t="s">
-        <v>351</v>
+        <v>539</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B285" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B286" t="s">
-        <v>349</v>
-      </c>
-      <c r="C286" t="s">
-        <v>523</v>
+        <v>348</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>455</v>
+        <v>335</v>
       </c>
       <c r="B287" t="s">
-        <v>510</v>
+        <v>349</v>
+      </c>
+      <c r="C287" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>352</v>
+        <v>455</v>
       </c>
       <c r="B288" t="s">
-        <v>350</v>
-      </c>
-      <c r="C288" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B289" t="s">
-        <v>342</v>
+        <v>350</v>
+      </c>
+      <c r="C289" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="B290" t="s">
-        <v>343</v>
-      </c>
-      <c r="C290" t="s">
-        <v>500</v>
+        <v>342</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="B291" t="s">
-        <v>344</v>
+        <v>343</v>
+      </c>
+      <c r="C291" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B292" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B293" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B294" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B295" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>1031</v>
+        <v>341</v>
       </c>
       <c r="B296" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C296" t="s">
-        <v>1033</v>
+        <v>344</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B297" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="C297" t="s">
         <v>1033</v>
@@ -11743,10 +11749,10 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B298" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C298" t="s">
         <v>1033</v>
@@ -11754,51 +11760,51 @@
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>1093</v>
+        <v>1036</v>
       </c>
       <c r="B299" t="s">
-        <v>1094</v>
+        <v>1037</v>
+      </c>
+      <c r="C299" t="s">
+        <v>1033</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B300" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" t="s">
         <v>473</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B301" t="s">
         <v>1172</v>
       </c>
-      <c r="C300" t="s">
+      <c r="C301" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3">
-      <c r="A302" t="s">
-        <v>629</v>
-      </c>
-      <c r="B302" t="s">
-        <v>646</v>
-      </c>
-      <c r="C302" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>1038</v>
+        <v>629</v>
       </c>
       <c r="B303" t="s">
-        <v>1136</v>
+        <v>646</v>
       </c>
       <c r="C303" t="s">
-        <v>1126</v>
+        <v>586</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B304" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C304" t="s">
         <v>1126</v>
@@ -11806,78 +11812,78 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B305" t="s">
-        <v>1173</v>
+        <v>1137</v>
       </c>
       <c r="C305" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
-      <c r="A307" t="s">
-        <v>625</v>
-      </c>
-      <c r="B307" t="s">
-        <v>626</v>
-      </c>
-      <c r="C307" t="s">
-        <v>586</v>
+    <row r="306" spans="1:3">
+      <c r="A306" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B306" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C306" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>464</v>
+        <v>625</v>
       </c>
       <c r="B308" t="s">
-        <v>465</v>
+        <v>626</v>
+      </c>
+      <c r="C308" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>359</v>
+        <v>464</v>
       </c>
       <c r="B309" t="s">
-        <v>370</v>
+        <v>465</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B310" t="s">
-        <v>371</v>
-      </c>
-      <c r="C310" t="s">
-        <v>523</v>
+        <v>370</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>511</v>
+        <v>360</v>
       </c>
       <c r="B311" t="s">
-        <v>512</v>
+        <v>371</v>
+      </c>
+      <c r="C311" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>361</v>
+        <v>511</v>
       </c>
       <c r="B312" t="s">
-        <v>372</v>
-      </c>
-      <c r="C312" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B313" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C313" t="s">
         <v>523</v>
@@ -11885,161 +11891,161 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B314" t="s">
-        <v>524</v>
+        <v>373</v>
+      </c>
+      <c r="C314" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B315" t="s">
-        <v>374</v>
+        <v>524</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B316" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B317" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B318" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B319" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B320" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>680</v>
+        <v>369</v>
       </c>
       <c r="B321" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C321" t="s">
-        <v>1126</v>
+        <v>379</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>1051</v>
+        <v>680</v>
       </c>
       <c r="B322" t="s">
-        <v>1052</v>
+        <v>1138</v>
+      </c>
+      <c r="C322" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>547</v>
+        <v>1051</v>
       </c>
       <c r="B323" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C323" t="s">
-        <v>1126</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>1095</v>
+        <v>547</v>
       </c>
       <c r="B324" t="s">
-        <v>1096</v>
+        <v>1174</v>
+      </c>
+      <c r="C324" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B325" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" t="s">
         <v>471</v>
       </c>
-      <c r="B325" t="s">
+      <c r="B326" t="s">
         <v>1175</v>
       </c>
-      <c r="C325" t="s">
+      <c r="C326" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3">
-      <c r="A327" t="s">
-        <v>466</v>
-      </c>
-      <c r="B327" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>386</v>
+        <v>466</v>
       </c>
       <c r="B328" t="s">
-        <v>397</v>
+        <v>465</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B329" t="s">
-        <v>398</v>
-      </c>
-      <c r="C329" t="s">
-        <v>523</v>
+        <v>397</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>456</v>
+        <v>387</v>
       </c>
       <c r="B330" t="s">
-        <v>513</v>
+        <v>398</v>
+      </c>
+      <c r="C330" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="B331" t="s">
-        <v>399</v>
-      </c>
-      <c r="C331" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B332" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C332" t="s">
         <v>523</v>
@@ -12047,730 +12053,730 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B333" t="s">
-        <v>525</v>
+        <v>400</v>
+      </c>
+      <c r="C333" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B334" t="s">
-        <v>374</v>
+        <v>525</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B335" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B336" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B337" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B338" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B339" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>553</v>
+        <v>396</v>
       </c>
       <c r="B340" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C340" t="s">
-        <v>1126</v>
+        <v>379</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>1097</v>
+        <v>553</v>
       </c>
       <c r="B341" t="s">
-        <v>1098</v>
+        <v>1174</v>
+      </c>
+      <c r="C341" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B342" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" t="s">
         <v>470</v>
       </c>
-      <c r="B342" t="s">
+      <c r="B343" t="s">
         <v>1175</v>
       </c>
-      <c r="C342" t="s">
+      <c r="C343" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3">
-      <c r="A344" t="s">
-        <v>623</v>
-      </c>
-      <c r="B344" t="s">
-        <v>624</v>
-      </c>
-      <c r="C344" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>380</v>
+        <v>623</v>
       </c>
       <c r="B345" t="s">
-        <v>1199</v>
+        <v>624</v>
+      </c>
+      <c r="C345" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B346" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C346" t="s">
-        <v>523</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>457</v>
+        <v>381</v>
       </c>
       <c r="B347" t="s">
-        <v>1201</v>
+        <v>1200</v>
+      </c>
+      <c r="C347" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>382</v>
+        <v>457</v>
       </c>
       <c r="B348" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B349" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B350" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>1065</v>
+        <v>384</v>
       </c>
       <c r="B351" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C351" t="s">
-        <v>1099</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C352" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" t="s">
         <v>469</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B353" t="s">
         <v>1205</v>
       </c>
-      <c r="C352" t="s">
+      <c r="C353" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3">
-      <c r="A354" t="s">
-        <v>688</v>
-      </c>
-      <c r="B354" t="s">
-        <v>689</v>
-      </c>
-      <c r="C354" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
+        <v>688</v>
+      </c>
+      <c r="B355" t="s">
+        <v>689</v>
+      </c>
+      <c r="C355" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" t="s">
         <v>690</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B356" t="s">
         <v>1176</v>
       </c>
-      <c r="C355" t="s">
+      <c r="C356" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3">
-      <c r="A357" t="s">
-        <v>696</v>
-      </c>
-      <c r="B357" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B358" t="s">
-        <v>1198</v>
+        <v>697</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B359" t="s">
-        <v>700</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B360" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B361" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B362" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B363" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B364" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B365" t="s">
-        <v>1100</v>
+        <v>710</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B366" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C366" t="s">
-        <v>1126</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B367" t="s">
-        <v>714</v>
+        <v>1177</v>
+      </c>
+      <c r="C367" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B368" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B369" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B370" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B371" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B372" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>1061</v>
+        <v>723</v>
       </c>
       <c r="B373" t="s">
-        <v>1062</v>
+        <v>724</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>725</v>
+        <v>1061</v>
       </c>
       <c r="B374" t="s">
-        <v>726</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>1101</v>
+        <v>725</v>
       </c>
       <c r="B375" t="s">
-        <v>1102</v>
+        <v>726</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" t="s">
         <v>1064</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B377" t="s">
         <v>1178</v>
       </c>
-      <c r="C376" t="s">
+      <c r="C377" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3">
-      <c r="A378" t="s">
-        <v>727</v>
-      </c>
-      <c r="B378" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B379" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B380" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B381" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B382" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B383" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B384" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B385" t="s">
-        <v>312</v>
+        <v>740</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B386" t="s">
-        <v>743</v>
+        <v>312</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B387" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B388" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
+        <v>746</v>
+      </c>
+      <c r="B389" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" t="s">
         <v>748</v>
       </c>
-      <c r="B389" t="s">
+      <c r="B390" t="s">
         <v>1179</v>
       </c>
-      <c r="C389" t="s">
+      <c r="C390" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3">
-      <c r="A391" t="s">
-        <v>749</v>
-      </c>
-      <c r="B391" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B392" t="s">
-        <v>751</v>
+        <v>306</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B393" t="s">
-        <v>308</v>
+        <v>751</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
+        <v>752</v>
+      </c>
+      <c r="B394" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" t="s">
         <v>753</v>
       </c>
-      <c r="B394" t="s">
+      <c r="B395" t="s">
         <v>1103</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3">
-      <c r="A396" t="s">
-        <v>774</v>
-      </c>
-      <c r="B396" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B397" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B398" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B399" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B400" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
+        <v>766</v>
+      </c>
+      <c r="B401" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" t="s">
         <v>771</v>
       </c>
-      <c r="B401" t="s">
+      <c r="B402" t="s">
         <v>1180</v>
       </c>
-      <c r="C401" t="s">
+      <c r="C402" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3">
-      <c r="A403" t="s">
-        <v>778</v>
-      </c>
-      <c r="B403" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="B404" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B405" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B406" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B407" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
+        <v>781</v>
+      </c>
+      <c r="B408" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409" t="s">
         <v>782</v>
       </c>
-      <c r="B408" t="s">
+      <c r="B409" t="s">
         <v>1181</v>
       </c>
-      <c r="C408" t="s">
+      <c r="C409" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3">
-      <c r="A410" t="s">
-        <v>790</v>
-      </c>
-      <c r="B410" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B411" t="s">
-        <v>1060</v>
+        <v>791</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B412" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C412" t="s">
-        <v>1126</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B413" t="s">
-        <v>978</v>
+        <v>1163</v>
+      </c>
+      <c r="C413" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="B414" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C414" t="s">
-        <v>1126</v>
+        <v>978</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B415" t="s">
-        <v>979</v>
+        <v>1182</v>
+      </c>
+      <c r="C415" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B416" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B417" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B418" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B419" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B420" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B421" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B422" t="s">
-        <v>800</v>
+        <v>985</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B423" t="s">
-        <v>986</v>
+        <v>800</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B424" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C424" t="s">
-        <v>1126</v>
+        <v>986</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B425" t="s">
-        <v>1132</v>
+        <v>1165</v>
       </c>
       <c r="C425" t="s">
         <v>1126</v>
@@ -12778,10 +12784,10 @@
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="B426" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C426" t="s">
         <v>1126</v>
@@ -12789,10 +12795,10 @@
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B427" t="s">
-        <v>1183</v>
+        <v>1166</v>
       </c>
       <c r="C427" t="s">
         <v>1126</v>
@@ -12800,1492 +12806,1503 @@
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>1104</v>
+        <v>804</v>
       </c>
       <c r="B428" t="s">
-        <v>1087</v>
+        <v>1183</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>987</v>
+        <v>1104</v>
       </c>
       <c r="B429" t="s">
-        <v>988</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B430" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B431" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B432" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B433" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B434" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B435" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B436" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C436" t="s">
-        <v>1126</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C437" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438" t="s">
         <v>1069</v>
       </c>
-      <c r="B437" t="s">
+      <c r="B438" t="s">
         <v>1105</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3">
-      <c r="A439" t="s">
-        <v>851</v>
-      </c>
-      <c r="B439" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B440" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B441" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B442" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B443" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B444" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B445" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B446" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B447" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B448" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B449" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B450" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B451" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B452" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B453" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B454" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C454" t="s">
-        <v>1126</v>
+        <v>880</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B455" t="s">
-        <v>883</v>
+        <v>1140</v>
+      </c>
+      <c r="C455" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B456" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B457" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B458" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>1106</v>
+        <v>888</v>
       </c>
       <c r="B459" t="s">
-        <v>1107</v>
+        <v>889</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3">
+      <c r="A461" t="s">
         <v>890</v>
       </c>
-      <c r="B460" t="s">
+      <c r="B461" t="s">
         <v>1184</v>
       </c>
-      <c r="C460" t="s">
+      <c r="C461" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3">
-      <c r="A462" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B462" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>891</v>
+        <v>1067</v>
       </c>
       <c r="B463" t="s">
-        <v>892</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B464" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B465" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B466" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B467" t="s">
-        <v>1108</v>
+        <v>898</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B468" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B469" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B470" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B471" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>1113</v>
+        <v>903</v>
       </c>
       <c r="B472" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3">
+      <c r="A474" t="s">
         <v>904</v>
       </c>
-      <c r="B473" t="s">
+      <c r="B474" t="s">
         <v>1185</v>
       </c>
-      <c r="C473" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3">
-      <c r="A475" t="s">
-        <v>911</v>
-      </c>
-      <c r="B475" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C475" t="s">
+      <c r="C474" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
+        <v>911</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3">
+      <c r="A477" t="s">
         <v>912</v>
       </c>
-      <c r="B476" t="s">
+      <c r="B477" t="s">
         <v>1187</v>
       </c>
-      <c r="C476" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3">
-      <c r="A478" t="s">
-        <v>913</v>
-      </c>
-      <c r="B478" t="s">
-        <v>914</v>
-      </c>
-      <c r="C478" t="s">
+      <c r="C477" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
+        <v>913</v>
+      </c>
+      <c r="B479" t="s">
+        <v>914</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3">
+      <c r="A480" t="s">
         <v>915</v>
       </c>
-      <c r="B479" t="s">
+      <c r="B480" t="s">
         <v>1188</v>
       </c>
-      <c r="C479" t="s">
+      <c r="C480" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3">
-      <c r="A481" t="s">
-        <v>916</v>
-      </c>
-      <c r="B481" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B482" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" t="s">
-        <v>1115</v>
+        <v>918</v>
       </c>
       <c r="B483" t="s">
-        <v>1116</v>
+        <v>919</v>
       </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485" t="s">
         <v>920</v>
       </c>
-      <c r="B484" t="s">
+      <c r="B485" t="s">
         <v>1189</v>
       </c>
-      <c r="C484" t="s">
+      <c r="C485" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3">
-      <c r="A486" t="s">
-        <v>921</v>
-      </c>
-      <c r="B486" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B487" t="s">
-        <v>923</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B488" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B489" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B490" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="491" spans="1:3">
       <c r="A491" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B491" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" t="s">
+        <v>930</v>
+      </c>
+      <c r="B492" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3">
+      <c r="A493" t="s">
         <v>932</v>
       </c>
-      <c r="B492" t="s">
+      <c r="B493" t="s">
         <v>1190</v>
       </c>
-      <c r="C492" t="s">
+      <c r="C493" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3">
-      <c r="A494" t="s">
-        <v>933</v>
-      </c>
-      <c r="B494" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B495" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B496" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B497" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="498" spans="1:3">
       <c r="A498" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B498" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499" t="s">
+        <v>941</v>
+      </c>
+      <c r="B499" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3">
+      <c r="A500" t="s">
         <v>943</v>
       </c>
-      <c r="B499" t="s">
+      <c r="B500" t="s">
         <v>1141</v>
       </c>
-      <c r="C499" t="s">
+      <c r="C500" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3">
-      <c r="A501" t="s">
-        <v>944</v>
-      </c>
-      <c r="B501" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B502" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B503" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B504" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="505" spans="1:3">
       <c r="A505" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B505" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="506" spans="1:3">
       <c r="A506" t="s">
+        <v>952</v>
+      </c>
+      <c r="B506" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3">
+      <c r="A507" t="s">
         <v>954</v>
       </c>
-      <c r="B506" t="s">
+      <c r="B507" t="s">
         <v>1117</v>
       </c>
-      <c r="C506" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3">
-      <c r="A508" t="s">
-        <v>955</v>
-      </c>
-      <c r="B508" t="s">
-        <v>956</v>
-      </c>
-      <c r="C508" t="s">
+      <c r="C507" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B509" t="s">
-        <v>958</v>
+        <v>956</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B510" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="511" spans="1:3">
       <c r="A511" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B511" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512" t="s">
+        <v>961</v>
+      </c>
+      <c r="B512" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3">
+      <c r="A513" t="s">
         <v>963</v>
       </c>
-      <c r="B512" t="s">
+      <c r="B513" t="s">
         <v>1191</v>
       </c>
-      <c r="C512" t="s">
+      <c r="C513" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3">
-      <c r="A514" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B514" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B515" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B516" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B517" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B518" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B519" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B520" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B521" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B522" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B523" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B524" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B525" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B526" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="527" spans="1:3">
       <c r="A527" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528" t="s">
         <v>1028</v>
       </c>
-      <c r="B527" t="s">
+      <c r="B528" t="s">
         <v>1192</v>
       </c>
-      <c r="C527" t="s">
+      <c r="C528" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="529" spans="1:2">
-      <c r="A529" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B530" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B531" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B532" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B533" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B534" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B535" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B536" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B537" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B538" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B539" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B540" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B541" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B542" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B543" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B544" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B545" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B546" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B547" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B548" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B549" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B550" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="B551" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B552" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B553" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="B554" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="B555" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B556" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B557" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B558" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B559" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B560" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B561" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B562" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B563" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B564" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B565" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B566" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B567" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B568" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B569" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B570" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B571" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B572" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B573" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B574" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B575" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B576" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B577" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B578" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B579" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B580" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B581" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B582" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B583" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B584" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B585" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B586" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B587" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B588" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B589" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B590" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B591" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B592" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B593" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B594" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B595" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B596" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B597" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B598" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B599" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B600" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B601" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B602" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B603" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B604" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B605" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B606" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B607" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B608" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B609" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B610" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B611" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B612" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B613" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B614" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B615" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B616" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B617" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" t="s">
         <v>1391</v>
       </c>
-      <c r="B618" t="s">
+      <c r="B619" t="s">
         <v>1392</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C527" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
-  <conditionalFormatting sqref="A480:A481 A477:A478 A462:A472 A474:A475 A483">
+  <autoFilter ref="A1:C528" xr:uid="{FB30D651-CF18-42CB-8A58-9F597F965D74}"/>
+  <conditionalFormatting sqref="A481:A482 A478:A479 A463:A473 A475:A476 A484">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raluca.ilinca.AzureAI-Jump2\Documents\Git\Application-Review-Process_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F4B661-C6EA-4597-A366-9AD29E0AD47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E141BA89-9856-4851-B091-C0A47A82B201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="13470" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22560" windowHeight="11655" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="1400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="1401">
   <si>
     <t>Name</t>
   </si>
@@ -4243,6 +4243,9 @@
   </si>
   <si>
     <t>The applicant has indicated all household contains all students on the Income Calculation Worksheet. Manual review is needed.</t>
+  </si>
+  <si>
+    <t>COLACalcDate</t>
   </si>
 </sst>
 </file>
@@ -8233,7 +8236,14 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="60" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A60" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1400</v>
+      </c>
+    </row>
     <row r="61" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="62" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="63" spans="1:2" ht="14.25" customHeight="1"/>
